--- a/Qualidade_Sessoes.xlsx
+++ b/Qualidade_Sessoes.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://muvamozorg.sharepoint.com/sites/mis.drive/Documentos Partilhados/PROJECTOS/Sistema de Monitoria/NEXUS/2026/Dash_Nexus/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="11_CA7BA6727B39BFF18534DF48238D9D3350433DF5" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{38739066-1E56-4FF2-9373-B0099C74756B}"/>
+  <xr:revisionPtr revIDLastSave="11" documentId="11_CA7BA6727B39BFF18534DF48238D9D3350433DF5" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{44A05A78-AC65-469D-8BFA-CBF0CF83351F}"/>
   <bookViews>
-    <workbookView xWindow="31860" yWindow="2370" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1254,6 +1254,13 @@
   <dimension ref="A1:K170"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="1" max="2" width="39.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="38.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="42.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="46.5703125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="12.140625" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="46.5703125" bestFit="1" customWidth="1"/>
   </cols>
@@ -1295,31 +1302,31 @@
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="B2" t="s">
         <v>12</v>
       </c>
       <c r="C2" t="s">
-        <v>13</v>
+        <v>103</v>
       </c>
       <c r="D2" t="s">
-        <v>14</v>
+        <v>118</v>
       </c>
       <c r="E2" t="s">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="F2" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="G2" t="s">
-        <v>16</v>
+        <v>100</v>
       </c>
       <c r="H2" t="s">
-        <v>17</v>
+        <v>119</v>
       </c>
       <c r="I2" t="s">
-        <v>18</v>
+        <v>120</v>
       </c>
       <c r="J2" t="s">
         <v>19</v>
@@ -1330,31 +1337,31 @@
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="B3" t="s">
         <v>12</v>
       </c>
       <c r="C3" t="s">
-        <v>21</v>
+        <v>125</v>
       </c>
       <c r="D3" t="s">
-        <v>22</v>
+        <v>118</v>
       </c>
       <c r="E3" t="s">
-        <v>15</v>
+        <v>123</v>
       </c>
       <c r="F3" t="s">
-        <v>12</v>
+        <v>52</v>
       </c>
       <c r="G3" t="s">
-        <v>23</v>
+        <v>100</v>
       </c>
       <c r="H3" t="s">
-        <v>24</v>
+        <v>133</v>
       </c>
       <c r="I3" t="s">
-        <v>25</v>
+        <v>142</v>
       </c>
       <c r="J3" t="s">
         <v>19</v>
@@ -1365,31 +1372,31 @@
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="B4" t="s">
         <v>12</v>
       </c>
       <c r="C4" t="s">
-        <v>21</v>
+        <v>122</v>
       </c>
       <c r="D4" t="s">
-        <v>14</v>
+        <v>118</v>
       </c>
       <c r="E4" t="s">
-        <v>15</v>
+        <v>123</v>
       </c>
       <c r="F4" t="s">
         <v>12</v>
       </c>
       <c r="G4" t="s">
-        <v>26</v>
+        <v>173</v>
       </c>
       <c r="H4" t="s">
-        <v>27</v>
+        <v>101</v>
       </c>
       <c r="I4" t="s">
-        <v>28</v>
+        <v>174</v>
       </c>
       <c r="J4" t="s">
         <v>19</v>
@@ -1400,66 +1407,66 @@
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="B5" t="s">
         <v>12</v>
       </c>
       <c r="C5" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="D5" t="s">
-        <v>31</v>
+        <v>118</v>
       </c>
       <c r="E5" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="F5" t="s">
         <v>12</v>
       </c>
       <c r="G5" t="s">
-        <v>33</v>
+        <v>173</v>
       </c>
       <c r="H5" t="s">
-        <v>34</v>
+        <v>121</v>
       </c>
       <c r="I5" t="s">
-        <v>35</v>
+        <v>195</v>
       </c>
       <c r="J5" t="s">
         <v>19</v>
       </c>
       <c r="K5" t="s">
-        <v>12</v>
+        <v>38</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>12</v>
+        <v>52</v>
       </c>
       <c r="C6" t="s">
         <v>21</v>
       </c>
       <c r="D6" t="s">
-        <v>31</v>
+        <v>118</v>
       </c>
       <c r="E6" t="s">
         <v>15</v>
       </c>
       <c r="F6" t="s">
-        <v>12</v>
+        <v>38</v>
       </c>
       <c r="G6" t="s">
-        <v>36</v>
+        <v>100</v>
       </c>
       <c r="H6" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="I6" t="s">
-        <v>37</v>
+        <v>208</v>
       </c>
       <c r="J6" t="s">
         <v>19</v>
@@ -1470,7 +1477,7 @@
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>38</v>
+        <v>193</v>
       </c>
       <c r="B7" t="s">
         <v>12</v>
@@ -1479,22 +1486,22 @@
         <v>39</v>
       </c>
       <c r="D7" t="s">
-        <v>31</v>
+        <v>118</v>
       </c>
       <c r="E7" t="s">
         <v>40</v>
       </c>
       <c r="F7" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="G7" t="s">
-        <v>36</v>
+        <v>217</v>
       </c>
       <c r="H7" t="s">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="I7" t="s">
-        <v>42</v>
+        <v>218</v>
       </c>
       <c r="J7" t="s">
         <v>43</v>
@@ -1505,31 +1512,31 @@
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>20</v>
+        <v>63</v>
       </c>
       <c r="B8" t="s">
         <v>12</v>
       </c>
       <c r="C8" t="s">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="D8" t="s">
-        <v>31</v>
+        <v>118</v>
       </c>
       <c r="E8" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="F8" t="s">
         <v>12</v>
       </c>
       <c r="G8" t="s">
-        <v>36</v>
+        <v>222</v>
       </c>
       <c r="H8" t="s">
-        <v>46</v>
+        <v>133</v>
       </c>
       <c r="I8" t="s">
-        <v>47</v>
+        <v>223</v>
       </c>
       <c r="J8" t="s">
         <v>43</v>
@@ -1540,31 +1547,31 @@
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>12</v>
+        <v>52</v>
       </c>
       <c r="B9" t="s">
         <v>12</v>
       </c>
       <c r="C9" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="D9" t="s">
-        <v>31</v>
+        <v>118</v>
       </c>
       <c r="E9" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="F9" t="s">
         <v>12</v>
       </c>
       <c r="G9" t="s">
-        <v>36</v>
+        <v>222</v>
       </c>
       <c r="H9" t="s">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="I9" t="s">
-        <v>51</v>
+        <v>229</v>
       </c>
       <c r="J9" t="s">
         <v>43</v>
@@ -1575,34 +1582,34 @@
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
       <c r="B10" t="s">
         <v>12</v>
       </c>
       <c r="C10" t="s">
-        <v>13</v>
+        <v>44</v>
       </c>
       <c r="D10" t="s">
-        <v>31</v>
+        <v>118</v>
       </c>
       <c r="E10" t="s">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="F10" t="s">
-        <v>52</v>
+        <v>12</v>
       </c>
       <c r="G10" t="s">
-        <v>53</v>
+        <v>173</v>
       </c>
       <c r="H10" t="s">
-        <v>54</v>
+        <v>38</v>
       </c>
       <c r="I10" t="s">
-        <v>55</v>
+        <v>235</v>
       </c>
       <c r="J10" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="K10" t="s">
         <v>12</v>
@@ -1610,31 +1617,31 @@
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>12</v>
+        <v>59</v>
       </c>
       <c r="B11" t="s">
         <v>12</v>
       </c>
       <c r="C11" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="D11" t="s">
-        <v>31</v>
+        <v>118</v>
       </c>
       <c r="E11" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="F11" t="s">
         <v>12</v>
       </c>
       <c r="G11" t="s">
-        <v>33</v>
+        <v>222</v>
       </c>
       <c r="H11" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="I11" t="s">
-        <v>58</v>
+        <v>237</v>
       </c>
       <c r="J11" t="s">
         <v>43</v>
@@ -1645,34 +1652,34 @@
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>59</v>
+        <v>144</v>
       </c>
       <c r="B12" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="C12" t="s">
-        <v>60</v>
+        <v>145</v>
       </c>
       <c r="D12" t="s">
-        <v>31</v>
+        <v>118</v>
       </c>
       <c r="E12" t="s">
-        <v>45</v>
+        <v>146</v>
       </c>
       <c r="F12" t="s">
-        <v>12</v>
+        <v>38</v>
       </c>
       <c r="G12" t="s">
-        <v>53</v>
+        <v>77</v>
       </c>
       <c r="H12" t="s">
-        <v>61</v>
+        <v>101</v>
       </c>
       <c r="I12" t="s">
-        <v>62</v>
+        <v>247</v>
       </c>
       <c r="J12" t="s">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="K12" t="s">
         <v>12</v>
@@ -1680,31 +1687,31 @@
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>63</v>
+        <v>140</v>
       </c>
       <c r="B13" t="s">
         <v>12</v>
       </c>
       <c r="C13" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="D13" t="s">
-        <v>31</v>
+        <v>118</v>
       </c>
       <c r="E13" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="F13" t="s">
         <v>12</v>
       </c>
       <c r="G13" t="s">
-        <v>53</v>
+        <v>159</v>
       </c>
       <c r="H13" t="s">
-        <v>61</v>
+        <v>193</v>
       </c>
       <c r="I13" t="s">
-        <v>64</v>
+        <v>269</v>
       </c>
       <c r="J13" t="s">
         <v>43</v>
@@ -1721,25 +1728,25 @@
         <v>12</v>
       </c>
       <c r="C14" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="D14" t="s">
-        <v>31</v>
+        <v>118</v>
       </c>
       <c r="E14" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="F14" t="s">
         <v>12</v>
       </c>
       <c r="G14" t="s">
-        <v>53</v>
+        <v>222</v>
       </c>
       <c r="H14" t="s">
-        <v>65</v>
+        <v>105</v>
       </c>
       <c r="I14" t="s">
-        <v>66</v>
+        <v>278</v>
       </c>
       <c r="J14" t="s">
         <v>43</v>
@@ -1750,31 +1757,31 @@
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="B15" t="s">
         <v>12</v>
       </c>
       <c r="C15" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="D15" t="s">
-        <v>67</v>
+        <v>22</v>
       </c>
       <c r="E15" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="F15" t="s">
         <v>12</v>
       </c>
       <c r="G15" t="s">
-        <v>68</v>
+        <v>23</v>
       </c>
       <c r="H15" t="s">
-        <v>69</v>
+        <v>24</v>
       </c>
       <c r="I15" t="s">
-        <v>70</v>
+        <v>25</v>
       </c>
       <c r="J15" t="s">
         <v>19</v>
@@ -1820,16 +1827,16 @@
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>12</v>
+        <v>52</v>
       </c>
       <c r="B17" t="s">
         <v>12</v>
       </c>
       <c r="C17" t="s">
-        <v>30</v>
+        <v>103</v>
       </c>
       <c r="D17" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="E17" t="s">
         <v>32</v>
@@ -1838,13 +1845,13 @@
         <v>12</v>
       </c>
       <c r="G17" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="H17" t="s">
-        <v>34</v>
+        <v>61</v>
       </c>
       <c r="I17" t="s">
-        <v>75</v>
+        <v>107</v>
       </c>
       <c r="J17" t="s">
         <v>19</v>
@@ -1855,31 +1862,31 @@
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>12</v>
+        <v>38</v>
       </c>
       <c r="B18" t="s">
-        <v>12</v>
+        <v>52</v>
       </c>
       <c r="C18" t="s">
-        <v>30</v>
+        <v>125</v>
       </c>
       <c r="D18" t="s">
-        <v>76</v>
+        <v>22</v>
       </c>
       <c r="E18" t="s">
-        <v>32</v>
+        <v>123</v>
       </c>
       <c r="F18" t="s">
-        <v>12</v>
+        <v>63</v>
       </c>
       <c r="G18" t="s">
-        <v>77</v>
+        <v>128</v>
       </c>
       <c r="H18" t="s">
-        <v>72</v>
+        <v>119</v>
       </c>
       <c r="I18" t="s">
-        <v>78</v>
+        <v>129</v>
       </c>
       <c r="J18" t="s">
         <v>19</v>
@@ -1890,31 +1897,31 @@
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>12</v>
+        <v>54</v>
       </c>
       <c r="B19" t="s">
         <v>12</v>
       </c>
       <c r="C19" t="s">
-        <v>30</v>
+        <v>145</v>
       </c>
       <c r="D19" t="s">
-        <v>79</v>
+        <v>22</v>
       </c>
       <c r="E19" t="s">
-        <v>32</v>
+        <v>146</v>
       </c>
       <c r="F19" t="s">
         <v>12</v>
       </c>
       <c r="G19" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="H19" t="s">
-        <v>81</v>
+        <v>98</v>
       </c>
       <c r="I19" t="s">
-        <v>82</v>
+        <v>148</v>
       </c>
       <c r="J19" t="s">
         <v>19</v>
@@ -1925,31 +1932,31 @@
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B20" t="s">
         <v>12</v>
       </c>
       <c r="C20" t="s">
-        <v>30</v>
+        <v>122</v>
       </c>
       <c r="D20" t="s">
-        <v>83</v>
+        <v>22</v>
       </c>
       <c r="E20" t="s">
-        <v>32</v>
+        <v>123</v>
       </c>
       <c r="F20" t="s">
         <v>12</v>
       </c>
       <c r="G20" t="s">
-        <v>84</v>
+        <v>71</v>
       </c>
       <c r="H20" t="s">
-        <v>81</v>
+        <v>65</v>
       </c>
       <c r="I20" t="s">
-        <v>85</v>
+        <v>156</v>
       </c>
       <c r="J20" t="s">
         <v>19</v>
@@ -1960,34 +1967,34 @@
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>59</v>
+        <v>29</v>
       </c>
       <c r="B21" t="s">
         <v>12</v>
       </c>
       <c r="C21" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="D21" t="s">
-        <v>86</v>
+        <v>22</v>
       </c>
       <c r="E21" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="F21" t="s">
         <v>12</v>
       </c>
       <c r="G21" t="s">
-        <v>87</v>
+        <v>71</v>
       </c>
       <c r="H21" t="s">
-        <v>88</v>
+        <v>162</v>
       </c>
       <c r="I21" t="s">
-        <v>89</v>
+        <v>180</v>
       </c>
       <c r="J21" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="K21" t="s">
         <v>12</v>
@@ -1995,34 +2002,34 @@
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>12</v>
+        <v>52</v>
       </c>
       <c r="B22" t="s">
         <v>12</v>
       </c>
       <c r="C22" t="s">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="D22" t="s">
-        <v>90</v>
+        <v>22</v>
       </c>
       <c r="E22" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="F22" t="s">
         <v>12</v>
       </c>
       <c r="G22" t="s">
-        <v>91</v>
+        <v>182</v>
       </c>
       <c r="H22" t="s">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="I22" t="s">
-        <v>92</v>
+        <v>183</v>
       </c>
       <c r="J22" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="K22" t="s">
         <v>12</v>
@@ -2030,34 +2037,34 @@
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="B23" t="s">
         <v>12</v>
       </c>
       <c r="C23" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="D23" t="s">
-        <v>93</v>
+        <v>22</v>
       </c>
       <c r="E23" t="s">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="F23" t="s">
         <v>12</v>
       </c>
       <c r="G23" t="s">
-        <v>94</v>
+        <v>128</v>
       </c>
       <c r="H23" t="s">
-        <v>81</v>
+        <v>46</v>
       </c>
       <c r="I23" t="s">
-        <v>95</v>
+        <v>184</v>
       </c>
       <c r="J23" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="K23" t="s">
         <v>12</v>
@@ -2065,31 +2072,31 @@
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>20</v>
+        <v>52</v>
       </c>
       <c r="B24" t="s">
         <v>12</v>
       </c>
       <c r="C24" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="D24" t="s">
-        <v>96</v>
+        <v>22</v>
       </c>
       <c r="E24" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="F24" t="s">
         <v>12</v>
       </c>
       <c r="G24" t="s">
-        <v>97</v>
+        <v>71</v>
       </c>
       <c r="H24" t="s">
-        <v>98</v>
+        <v>133</v>
       </c>
       <c r="I24" t="s">
-        <v>99</v>
+        <v>196</v>
       </c>
       <c r="J24" t="s">
         <v>19</v>
@@ -2100,31 +2107,31 @@
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="B25" t="s">
         <v>12</v>
       </c>
       <c r="C25" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="D25" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="E25" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="F25" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="G25" t="s">
-        <v>100</v>
+        <v>197</v>
       </c>
       <c r="H25" t="s">
-        <v>101</v>
+        <v>54</v>
       </c>
       <c r="I25" t="s">
-        <v>102</v>
+        <v>198</v>
       </c>
       <c r="J25" t="s">
         <v>19</v>
@@ -2141,28 +2148,28 @@
         <v>12</v>
       </c>
       <c r="C26" t="s">
-        <v>103</v>
+        <v>48</v>
       </c>
       <c r="D26" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="E26" t="s">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="F26" t="s">
         <v>12</v>
       </c>
       <c r="G26" t="s">
-        <v>33</v>
+        <v>128</v>
       </c>
       <c r="H26" t="s">
-        <v>61</v>
+        <v>98</v>
       </c>
       <c r="I26" t="s">
-        <v>104</v>
+        <v>209</v>
       </c>
       <c r="J26" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="K26" t="s">
         <v>12</v>
@@ -2176,28 +2183,28 @@
         <v>12</v>
       </c>
       <c r="C27" t="s">
-        <v>103</v>
+        <v>56</v>
       </c>
       <c r="D27" t="s">
-        <v>67</v>
+        <v>22</v>
       </c>
       <c r="E27" t="s">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="F27" t="s">
         <v>12</v>
       </c>
       <c r="G27" t="s">
-        <v>68</v>
+        <v>197</v>
       </c>
       <c r="H27" t="s">
-        <v>105</v>
+        <v>57</v>
       </c>
       <c r="I27" t="s">
-        <v>106</v>
+        <v>210</v>
       </c>
       <c r="J27" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="K27" t="s">
         <v>12</v>
@@ -2205,19 +2212,19 @@
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="B28" t="s">
         <v>12</v>
       </c>
       <c r="C28" t="s">
-        <v>103</v>
+        <v>60</v>
       </c>
       <c r="D28" t="s">
         <v>22</v>
       </c>
       <c r="E28" t="s">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="F28" t="s">
         <v>12</v>
@@ -2226,13 +2233,13 @@
         <v>71</v>
       </c>
       <c r="H28" t="s">
-        <v>61</v>
+        <v>162</v>
       </c>
       <c r="I28" t="s">
-        <v>107</v>
+        <v>231</v>
       </c>
       <c r="J28" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="K28" t="s">
         <v>12</v>
@@ -2240,16 +2247,16 @@
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>63</v>
+        <v>12</v>
       </c>
       <c r="B29" t="s">
         <v>12</v>
       </c>
       <c r="C29" t="s">
-        <v>103</v>
+        <v>30</v>
       </c>
       <c r="D29" t="s">
-        <v>14</v>
+        <v>67</v>
       </c>
       <c r="E29" t="s">
         <v>32</v>
@@ -2258,13 +2265,13 @@
         <v>12</v>
       </c>
       <c r="G29" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="H29" t="s">
-        <v>108</v>
+        <v>69</v>
       </c>
       <c r="I29" t="s">
-        <v>109</v>
+        <v>70</v>
       </c>
       <c r="J29" t="s">
         <v>19</v>
@@ -2284,7 +2291,7 @@
         <v>103</v>
       </c>
       <c r="D30" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="E30" t="s">
         <v>32</v>
@@ -2293,13 +2300,13 @@
         <v>12</v>
       </c>
       <c r="G30" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="H30" t="s">
-        <v>65</v>
+        <v>105</v>
       </c>
       <c r="I30" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="J30" t="s">
         <v>19</v>
@@ -2310,37 +2317,37 @@
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B31" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="C31" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D31" t="s">
-        <v>79</v>
+        <v>67</v>
       </c>
       <c r="E31" t="s">
-        <v>32</v>
+        <v>123</v>
       </c>
       <c r="F31" t="s">
-        <v>12</v>
+        <v>59</v>
       </c>
       <c r="G31" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="H31" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="I31" t="s">
-        <v>111</v>
+        <v>127</v>
       </c>
       <c r="J31" t="s">
         <v>19</v>
       </c>
       <c r="K31" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.25">
@@ -2351,28 +2358,28 @@
         <v>12</v>
       </c>
       <c r="C32" t="s">
-        <v>103</v>
+        <v>56</v>
       </c>
       <c r="D32" t="s">
-        <v>83</v>
+        <v>67</v>
       </c>
       <c r="E32" t="s">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="F32" t="s">
         <v>12</v>
       </c>
       <c r="G32" t="s">
-        <v>112</v>
+        <v>68</v>
       </c>
       <c r="H32" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="I32" t="s">
-        <v>113</v>
+        <v>143</v>
       </c>
       <c r="J32" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="K32" t="s">
         <v>12</v>
@@ -2380,31 +2387,31 @@
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>29</v>
+        <v>144</v>
       </c>
       <c r="B33" t="s">
         <v>12</v>
       </c>
       <c r="C33" t="s">
-        <v>103</v>
+        <v>145</v>
       </c>
       <c r="D33" t="s">
-        <v>86</v>
+        <v>67</v>
       </c>
       <c r="E33" t="s">
-        <v>32</v>
+        <v>146</v>
       </c>
       <c r="F33" t="s">
         <v>12</v>
       </c>
       <c r="G33" t="s">
-        <v>87</v>
+        <v>68</v>
       </c>
       <c r="H33" t="s">
-        <v>105</v>
+        <v>88</v>
       </c>
       <c r="I33" t="s">
-        <v>114</v>
+        <v>147</v>
       </c>
       <c r="J33" t="s">
         <v>19</v>
@@ -2415,31 +2422,31 @@
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="B34" t="s">
         <v>12</v>
       </c>
       <c r="C34" t="s">
-        <v>103</v>
+        <v>21</v>
       </c>
       <c r="D34" t="s">
-        <v>90</v>
+        <v>67</v>
       </c>
       <c r="E34" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="F34" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="G34" t="s">
-        <v>91</v>
+        <v>150</v>
       </c>
       <c r="H34" t="s">
-        <v>105</v>
+        <v>140</v>
       </c>
       <c r="I34" t="s">
-        <v>115</v>
+        <v>151</v>
       </c>
       <c r="J34" t="s">
         <v>19</v>
@@ -2450,31 +2457,31 @@
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="B35" t="s">
         <v>12</v>
       </c>
       <c r="C35" t="s">
-        <v>103</v>
+        <v>13</v>
       </c>
       <c r="D35" t="s">
-        <v>93</v>
+        <v>67</v>
       </c>
       <c r="E35" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="F35" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="G35" t="s">
-        <v>94</v>
+        <v>152</v>
       </c>
       <c r="H35" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="I35" t="s">
-        <v>116</v>
+        <v>153</v>
       </c>
       <c r="J35" t="s">
         <v>19</v>
@@ -2485,66 +2492,66 @@
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="B36" t="s">
         <v>12</v>
       </c>
       <c r="C36" t="s">
-        <v>103</v>
+        <v>44</v>
       </c>
       <c r="D36" t="s">
-        <v>96</v>
+        <v>67</v>
       </c>
       <c r="E36" t="s">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="F36" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="G36" t="s">
-        <v>97</v>
+        <v>150</v>
       </c>
       <c r="H36" t="s">
-        <v>108</v>
+        <v>17</v>
       </c>
       <c r="I36" t="s">
-        <v>117</v>
+        <v>154</v>
       </c>
       <c r="J36" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="K36" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="B37" t="s">
         <v>12</v>
       </c>
       <c r="C37" t="s">
-        <v>103</v>
+        <v>122</v>
       </c>
       <c r="D37" t="s">
-        <v>118</v>
+        <v>67</v>
       </c>
       <c r="E37" t="s">
-        <v>32</v>
+        <v>123</v>
       </c>
       <c r="F37" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="G37" t="s">
-        <v>100</v>
+        <v>152</v>
       </c>
       <c r="H37" t="s">
-        <v>119</v>
+        <v>105</v>
       </c>
       <c r="I37" t="s">
-        <v>120</v>
+        <v>155</v>
       </c>
       <c r="J37" t="s">
         <v>19</v>
@@ -2555,34 +2562,34 @@
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>121</v>
+        <v>63</v>
       </c>
       <c r="B38" t="s">
         <v>12</v>
       </c>
       <c r="C38" t="s">
-        <v>122</v>
+        <v>39</v>
       </c>
       <c r="D38" t="s">
-        <v>31</v>
+        <v>67</v>
       </c>
       <c r="E38" t="s">
-        <v>123</v>
+        <v>40</v>
       </c>
       <c r="F38" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="G38" t="s">
-        <v>53</v>
+        <v>150</v>
       </c>
       <c r="H38" t="s">
-        <v>101</v>
+        <v>46</v>
       </c>
       <c r="I38" t="s">
-        <v>124</v>
+        <v>175</v>
       </c>
       <c r="J38" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="K38" t="s">
         <v>12</v>
@@ -2590,34 +2597,34 @@
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>38</v>
+        <v>12</v>
       </c>
       <c r="B39" t="s">
         <v>12</v>
       </c>
       <c r="C39" t="s">
-        <v>125</v>
+        <v>60</v>
       </c>
       <c r="D39" t="s">
-        <v>31</v>
+        <v>67</v>
       </c>
       <c r="E39" t="s">
-        <v>123</v>
+        <v>40</v>
       </c>
       <c r="F39" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="G39" t="s">
-        <v>33</v>
+        <v>152</v>
       </c>
       <c r="H39" t="s">
-        <v>108</v>
+        <v>65</v>
       </c>
       <c r="I39" t="s">
-        <v>126</v>
+        <v>176</v>
       </c>
       <c r="J39" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="K39" t="s">
         <v>12</v>
@@ -2625,69 +2632,69 @@
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>27</v>
+        <v>52</v>
       </c>
       <c r="B40" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="C40" t="s">
-        <v>125</v>
+        <v>60</v>
       </c>
       <c r="D40" t="s">
         <v>67</v>
       </c>
       <c r="E40" t="s">
-        <v>123</v>
+        <v>40</v>
       </c>
       <c r="F40" t="s">
-        <v>59</v>
+        <v>12</v>
       </c>
       <c r="G40" t="s">
-        <v>68</v>
+        <v>152</v>
       </c>
       <c r="H40" t="s">
-        <v>54</v>
+        <v>105</v>
       </c>
       <c r="I40" t="s">
-        <v>127</v>
+        <v>177</v>
       </c>
       <c r="J40" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="K40" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>38</v>
+        <v>59</v>
       </c>
       <c r="B41" t="s">
-        <v>52</v>
+        <v>12</v>
       </c>
       <c r="C41" t="s">
-        <v>125</v>
+        <v>60</v>
       </c>
       <c r="D41" t="s">
-        <v>22</v>
+        <v>67</v>
       </c>
       <c r="E41" t="s">
-        <v>123</v>
+        <v>45</v>
       </c>
       <c r="F41" t="s">
-        <v>63</v>
+        <v>12</v>
       </c>
       <c r="G41" t="s">
-        <v>128</v>
+        <v>152</v>
       </c>
       <c r="H41" t="s">
-        <v>119</v>
+        <v>61</v>
       </c>
       <c r="I41" t="s">
-        <v>129</v>
+        <v>178</v>
       </c>
       <c r="J41" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="K41" t="s">
         <v>12</v>
@@ -2695,34 +2702,34 @@
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>54</v>
+        <v>12</v>
       </c>
       <c r="B42" t="s">
         <v>12</v>
       </c>
       <c r="C42" t="s">
-        <v>125</v>
+        <v>48</v>
       </c>
       <c r="D42" t="s">
-        <v>14</v>
+        <v>67</v>
       </c>
       <c r="E42" t="s">
-        <v>123</v>
+        <v>49</v>
       </c>
       <c r="F42" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="G42" t="s">
-        <v>74</v>
+        <v>152</v>
       </c>
       <c r="H42" t="s">
-        <v>121</v>
+        <v>50</v>
       </c>
       <c r="I42" t="s">
-        <v>130</v>
+        <v>179</v>
       </c>
       <c r="J42" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="K42" t="s">
         <v>12</v>
@@ -2730,31 +2737,31 @@
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>59</v>
+        <v>29</v>
       </c>
       <c r="B43" t="s">
         <v>12</v>
       </c>
       <c r="C43" t="s">
-        <v>125</v>
+        <v>30</v>
       </c>
       <c r="D43" t="s">
-        <v>76</v>
+        <v>31</v>
       </c>
       <c r="E43" t="s">
-        <v>123</v>
+        <v>32</v>
       </c>
       <c r="F43" t="s">
         <v>12</v>
       </c>
       <c r="G43" t="s">
-        <v>77</v>
+        <v>33</v>
       </c>
       <c r="H43" t="s">
-        <v>61</v>
+        <v>34</v>
       </c>
       <c r="I43" t="s">
-        <v>131</v>
+        <v>35</v>
       </c>
       <c r="J43" t="s">
         <v>19</v>
@@ -2765,31 +2772,31 @@
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>121</v>
+        <v>20</v>
       </c>
       <c r="B44" t="s">
         <v>12</v>
       </c>
       <c r="C44" t="s">
-        <v>125</v>
+        <v>21</v>
       </c>
       <c r="D44" t="s">
-        <v>79</v>
+        <v>31</v>
       </c>
       <c r="E44" t="s">
-        <v>123</v>
+        <v>15</v>
       </c>
       <c r="F44" t="s">
         <v>12</v>
       </c>
       <c r="G44" t="s">
-        <v>132</v>
+        <v>36</v>
       </c>
       <c r="H44" t="s">
-        <v>133</v>
+        <v>27</v>
       </c>
       <c r="I44" t="s">
-        <v>134</v>
+        <v>37</v>
       </c>
       <c r="J44" t="s">
         <v>19</v>
@@ -2800,34 +2807,34 @@
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="B45" t="s">
         <v>12</v>
       </c>
       <c r="C45" t="s">
-        <v>125</v>
+        <v>39</v>
       </c>
       <c r="D45" t="s">
-        <v>83</v>
+        <v>31</v>
       </c>
       <c r="E45" t="s">
-        <v>123</v>
+        <v>40</v>
       </c>
       <c r="F45" t="s">
         <v>29</v>
       </c>
       <c r="G45" t="s">
-        <v>135</v>
+        <v>36</v>
       </c>
       <c r="H45" t="s">
-        <v>65</v>
+        <v>41</v>
       </c>
       <c r="I45" t="s">
-        <v>136</v>
+        <v>42</v>
       </c>
       <c r="J45" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="K45" t="s">
         <v>12</v>
@@ -2835,34 +2842,34 @@
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>63</v>
+        <v>20</v>
       </c>
       <c r="B46" t="s">
         <v>12</v>
       </c>
       <c r="C46" t="s">
-        <v>125</v>
+        <v>44</v>
       </c>
       <c r="D46" t="s">
-        <v>86</v>
+        <v>31</v>
       </c>
       <c r="E46" t="s">
-        <v>123</v>
+        <v>45</v>
       </c>
       <c r="F46" t="s">
         <v>12</v>
       </c>
       <c r="G46" t="s">
-        <v>87</v>
+        <v>36</v>
       </c>
       <c r="H46" t="s">
-        <v>105</v>
+        <v>46</v>
       </c>
       <c r="I46" t="s">
-        <v>137</v>
+        <v>47</v>
       </c>
       <c r="J46" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="K46" t="s">
         <v>12</v>
@@ -2870,34 +2877,34 @@
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B47" t="s">
         <v>12</v>
       </c>
       <c r="C47" t="s">
-        <v>125</v>
+        <v>48</v>
       </c>
       <c r="D47" t="s">
-        <v>90</v>
+        <v>31</v>
       </c>
       <c r="E47" t="s">
-        <v>123</v>
+        <v>49</v>
       </c>
       <c r="F47" t="s">
         <v>12</v>
       </c>
       <c r="G47" t="s">
-        <v>91</v>
+        <v>36</v>
       </c>
       <c r="H47" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="I47" t="s">
-        <v>138</v>
+        <v>51</v>
       </c>
       <c r="J47" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="K47" t="s">
         <v>12</v>
@@ -2905,31 +2912,31 @@
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="B48" t="s">
         <v>12</v>
       </c>
       <c r="C48" t="s">
-        <v>125</v>
+        <v>13</v>
       </c>
       <c r="D48" t="s">
-        <v>93</v>
+        <v>31</v>
       </c>
       <c r="E48" t="s">
-        <v>123</v>
+        <v>15</v>
       </c>
       <c r="F48" t="s">
-        <v>12</v>
+        <v>52</v>
       </c>
       <c r="G48" t="s">
-        <v>94</v>
+        <v>53</v>
       </c>
       <c r="H48" t="s">
         <v>54</v>
       </c>
       <c r="I48" t="s">
-        <v>139</v>
+        <v>55</v>
       </c>
       <c r="J48" t="s">
         <v>19</v>
@@ -2940,34 +2947,34 @@
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>140</v>
+        <v>12</v>
       </c>
       <c r="B49" t="s">
         <v>12</v>
       </c>
       <c r="C49" t="s">
-        <v>125</v>
+        <v>56</v>
       </c>
       <c r="D49" t="s">
-        <v>96</v>
+        <v>31</v>
       </c>
       <c r="E49" t="s">
-        <v>123</v>
+        <v>49</v>
       </c>
       <c r="F49" t="s">
         <v>12</v>
       </c>
       <c r="G49" t="s">
-        <v>97</v>
+        <v>33</v>
       </c>
       <c r="H49" t="s">
-        <v>119</v>
+        <v>57</v>
       </c>
       <c r="I49" t="s">
-        <v>141</v>
+        <v>58</v>
       </c>
       <c r="J49" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="K49" t="s">
         <v>12</v>
@@ -2975,34 +2982,34 @@
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>27</v>
+        <v>59</v>
       </c>
       <c r="B50" t="s">
         <v>12</v>
       </c>
       <c r="C50" t="s">
-        <v>125</v>
+        <v>60</v>
       </c>
       <c r="D50" t="s">
-        <v>118</v>
+        <v>31</v>
       </c>
       <c r="E50" t="s">
-        <v>123</v>
+        <v>45</v>
       </c>
       <c r="F50" t="s">
-        <v>52</v>
+        <v>12</v>
       </c>
       <c r="G50" t="s">
-        <v>100</v>
+        <v>53</v>
       </c>
       <c r="H50" t="s">
-        <v>133</v>
+        <v>61</v>
       </c>
       <c r="I50" t="s">
-        <v>142</v>
+        <v>62</v>
       </c>
       <c r="J50" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="K50" t="s">
         <v>12</v>
@@ -3010,31 +3017,31 @@
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>12</v>
+        <v>63</v>
       </c>
       <c r="B51" t="s">
         <v>12</v>
       </c>
       <c r="C51" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="D51" t="s">
-        <v>67</v>
+        <v>31</v>
       </c>
       <c r="E51" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="F51" t="s">
         <v>12</v>
       </c>
       <c r="G51" t="s">
-        <v>68</v>
+        <v>53</v>
       </c>
       <c r="H51" t="s">
         <v>61</v>
       </c>
       <c r="I51" t="s">
-        <v>143</v>
+        <v>64</v>
       </c>
       <c r="J51" t="s">
         <v>43</v>
@@ -3045,34 +3052,34 @@
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>144</v>
+        <v>12</v>
       </c>
       <c r="B52" t="s">
         <v>12</v>
       </c>
       <c r="C52" t="s">
-        <v>145</v>
+        <v>60</v>
       </c>
       <c r="D52" t="s">
-        <v>67</v>
+        <v>31</v>
       </c>
       <c r="E52" t="s">
-        <v>146</v>
+        <v>40</v>
       </c>
       <c r="F52" t="s">
         <v>12</v>
       </c>
       <c r="G52" t="s">
-        <v>68</v>
+        <v>53</v>
       </c>
       <c r="H52" t="s">
-        <v>88</v>
+        <v>65</v>
       </c>
       <c r="I52" t="s">
-        <v>147</v>
+        <v>66</v>
       </c>
       <c r="J52" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="K52" t="s">
         <v>12</v>
@@ -3080,31 +3087,31 @@
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="B53" t="s">
         <v>12</v>
       </c>
       <c r="C53" t="s">
-        <v>145</v>
+        <v>30</v>
       </c>
       <c r="D53" t="s">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="E53" t="s">
-        <v>146</v>
+        <v>32</v>
       </c>
       <c r="F53" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="G53" t="s">
-        <v>68</v>
+        <v>100</v>
       </c>
       <c r="H53" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="I53" t="s">
-        <v>148</v>
+        <v>102</v>
       </c>
       <c r="J53" t="s">
         <v>19</v>
@@ -3115,31 +3122,31 @@
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>41</v>
+        <v>12</v>
       </c>
       <c r="B54" t="s">
         <v>12</v>
       </c>
       <c r="C54" t="s">
-        <v>145</v>
+        <v>103</v>
       </c>
       <c r="D54" t="s">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="E54" t="s">
-        <v>146</v>
+        <v>32</v>
       </c>
       <c r="F54" t="s">
         <v>12</v>
       </c>
       <c r="G54" t="s">
-        <v>68</v>
+        <v>33</v>
       </c>
       <c r="H54" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="I54" t="s">
-        <v>149</v>
+        <v>104</v>
       </c>
       <c r="J54" t="s">
         <v>19</v>
@@ -3150,31 +3157,31 @@
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>63</v>
+        <v>121</v>
       </c>
       <c r="B55" t="s">
         <v>12</v>
       </c>
       <c r="C55" t="s">
-        <v>21</v>
+        <v>122</v>
       </c>
       <c r="D55" t="s">
-        <v>67</v>
+        <v>31</v>
       </c>
       <c r="E55" t="s">
-        <v>15</v>
+        <v>123</v>
       </c>
       <c r="F55" t="s">
         <v>29</v>
       </c>
       <c r="G55" t="s">
-        <v>150</v>
+        <v>53</v>
       </c>
       <c r="H55" t="s">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="I55" t="s">
-        <v>151</v>
+        <v>124</v>
       </c>
       <c r="J55" t="s">
         <v>19</v>
@@ -3185,31 +3192,31 @@
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="B56" t="s">
         <v>12</v>
       </c>
       <c r="C56" t="s">
-        <v>13</v>
+        <v>125</v>
       </c>
       <c r="D56" t="s">
-        <v>67</v>
+        <v>31</v>
       </c>
       <c r="E56" t="s">
-        <v>15</v>
+        <v>123</v>
       </c>
       <c r="F56" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="G56" t="s">
-        <v>152</v>
+        <v>33</v>
       </c>
       <c r="H56" t="s">
-        <v>54</v>
+        <v>108</v>
       </c>
       <c r="I56" t="s">
-        <v>153</v>
+        <v>126</v>
       </c>
       <c r="J56" t="s">
         <v>19</v>
@@ -3220,34 +3227,34 @@
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="B57" t="s">
         <v>12</v>
       </c>
       <c r="C57" t="s">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="D57" t="s">
-        <v>67</v>
+        <v>96</v>
       </c>
       <c r="E57" t="s">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="F57" t="s">
         <v>12</v>
       </c>
       <c r="G57" t="s">
-        <v>150</v>
+        <v>97</v>
       </c>
       <c r="H57" t="s">
-        <v>17</v>
+        <v>98</v>
       </c>
       <c r="I57" t="s">
-        <v>154</v>
+        <v>99</v>
       </c>
       <c r="J57" t="s">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="K57" t="s">
         <v>12</v>
@@ -3255,51 +3262,51 @@
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="B58" t="s">
         <v>12</v>
       </c>
       <c r="C58" t="s">
-        <v>122</v>
+        <v>103</v>
       </c>
       <c r="D58" t="s">
-        <v>67</v>
+        <v>96</v>
       </c>
       <c r="E58" t="s">
-        <v>123</v>
+        <v>32</v>
       </c>
       <c r="F58" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="G58" t="s">
-        <v>152</v>
+        <v>97</v>
       </c>
       <c r="H58" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="I58" t="s">
-        <v>155</v>
+        <v>117</v>
       </c>
       <c r="J58" t="s">
         <v>19</v>
       </c>
       <c r="K58" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>11</v>
+        <v>140</v>
       </c>
       <c r="B59" t="s">
         <v>12</v>
       </c>
       <c r="C59" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="D59" t="s">
-        <v>22</v>
+        <v>96</v>
       </c>
       <c r="E59" t="s">
         <v>123</v>
@@ -3308,13 +3315,13 @@
         <v>12</v>
       </c>
       <c r="G59" t="s">
-        <v>71</v>
+        <v>97</v>
       </c>
       <c r="H59" t="s">
-        <v>65</v>
+        <v>119</v>
       </c>
       <c r="I59" t="s">
-        <v>156</v>
+        <v>141</v>
       </c>
       <c r="J59" t="s">
         <v>19</v>
@@ -3325,7 +3332,7 @@
     </row>
     <row r="60" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="B60" t="s">
         <v>12</v>
@@ -3334,7 +3341,7 @@
         <v>122</v>
       </c>
       <c r="D60" t="s">
-        <v>14</v>
+        <v>96</v>
       </c>
       <c r="E60" t="s">
         <v>123</v>
@@ -3343,13 +3350,13 @@
         <v>12</v>
       </c>
       <c r="G60" t="s">
-        <v>157</v>
+        <v>171</v>
       </c>
       <c r="H60" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="I60" t="s">
-        <v>158</v>
+        <v>172</v>
       </c>
       <c r="J60" t="s">
         <v>19</v>
@@ -3360,31 +3367,31 @@
     </row>
     <row r="61" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B61" t="s">
         <v>12</v>
       </c>
       <c r="C61" t="s">
-        <v>122</v>
+        <v>13</v>
       </c>
       <c r="D61" t="s">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="E61" t="s">
-        <v>123</v>
+        <v>15</v>
       </c>
       <c r="F61" t="s">
         <v>12</v>
       </c>
       <c r="G61" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
       <c r="H61" t="s">
-        <v>105</v>
+        <v>193</v>
       </c>
       <c r="I61" t="s">
-        <v>160</v>
+        <v>194</v>
       </c>
       <c r="J61" t="s">
         <v>19</v>
@@ -3395,31 +3402,31 @@
     </row>
     <row r="62" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="B62" t="s">
-        <v>12</v>
+        <v>52</v>
       </c>
       <c r="C62" t="s">
-        <v>122</v>
+        <v>21</v>
       </c>
       <c r="D62" t="s">
-        <v>79</v>
+        <v>96</v>
       </c>
       <c r="E62" t="s">
-        <v>123</v>
+        <v>15</v>
       </c>
       <c r="F62" t="s">
         <v>12</v>
       </c>
       <c r="G62" t="s">
-        <v>161</v>
+        <v>97</v>
       </c>
       <c r="H62" t="s">
-        <v>162</v>
+        <v>121</v>
       </c>
       <c r="I62" t="s">
-        <v>163</v>
+        <v>207</v>
       </c>
       <c r="J62" t="s">
         <v>19</v>
@@ -3430,34 +3437,34 @@
     </row>
     <row r="63" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>11</v>
+        <v>119</v>
       </c>
       <c r="B63" t="s">
         <v>12</v>
       </c>
       <c r="C63" t="s">
-        <v>122</v>
+        <v>39</v>
       </c>
       <c r="D63" t="s">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="E63" t="s">
-        <v>123</v>
+        <v>40</v>
       </c>
       <c r="F63" t="s">
         <v>12</v>
       </c>
       <c r="G63" t="s">
-        <v>164</v>
+        <v>215</v>
       </c>
       <c r="H63" t="s">
-        <v>61</v>
+        <v>38</v>
       </c>
       <c r="I63" t="s">
-        <v>165</v>
+        <v>216</v>
       </c>
       <c r="J63" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="K63" t="s">
         <v>12</v>
@@ -3465,34 +3472,34 @@
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>27</v>
+        <v>52</v>
       </c>
       <c r="B64" t="s">
         <v>12</v>
       </c>
       <c r="C64" t="s">
-        <v>122</v>
+        <v>60</v>
       </c>
       <c r="D64" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="E64" t="s">
-        <v>123</v>
+        <v>40</v>
       </c>
       <c r="F64" t="s">
         <v>12</v>
       </c>
       <c r="G64" t="s">
-        <v>166</v>
+        <v>220</v>
       </c>
       <c r="H64" t="s">
-        <v>101</v>
+        <v>46</v>
       </c>
       <c r="I64" t="s">
-        <v>167</v>
+        <v>221</v>
       </c>
       <c r="J64" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="K64" t="s">
         <v>12</v>
@@ -3500,34 +3507,34 @@
     </row>
     <row r="65" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B65" t="s">
         <v>12</v>
       </c>
       <c r="C65" t="s">
-        <v>122</v>
+        <v>60</v>
       </c>
       <c r="D65" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="E65" t="s">
-        <v>123</v>
+        <v>40</v>
       </c>
       <c r="F65" t="s">
         <v>12</v>
       </c>
       <c r="G65" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="H65" t="s">
-        <v>65</v>
+        <v>105</v>
       </c>
       <c r="I65" t="s">
-        <v>169</v>
+        <v>228</v>
       </c>
       <c r="J65" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="K65" t="s">
         <v>12</v>
@@ -3535,31 +3542,31 @@
     </row>
     <row r="66" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>24</v>
+        <v>140</v>
       </c>
       <c r="B66" t="s">
-        <v>12</v>
+        <v>52</v>
       </c>
       <c r="C66" t="s">
-        <v>122</v>
+        <v>145</v>
       </c>
       <c r="D66" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="E66" t="s">
-        <v>123</v>
+        <v>146</v>
       </c>
       <c r="F66" t="s">
-        <v>12</v>
+        <v>38</v>
       </c>
       <c r="G66" t="s">
-        <v>161</v>
+        <v>77</v>
       </c>
       <c r="H66" t="s">
-        <v>61</v>
+        <v>133</v>
       </c>
       <c r="I66" t="s">
-        <v>170</v>
+        <v>246</v>
       </c>
       <c r="J66" t="s">
         <v>19</v>
@@ -3570,34 +3577,34 @@
     </row>
     <row r="67" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="B67" t="s">
         <v>12</v>
       </c>
       <c r="C67" t="s">
-        <v>122</v>
+        <v>48</v>
       </c>
       <c r="D67" t="s">
         <v>96</v>
       </c>
       <c r="E67" t="s">
-        <v>123</v>
+        <v>49</v>
       </c>
       <c r="F67" t="s">
         <v>12</v>
       </c>
       <c r="G67" t="s">
-        <v>171</v>
+        <v>159</v>
       </c>
       <c r="H67" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="I67" t="s">
-        <v>172</v>
+        <v>268</v>
       </c>
       <c r="J67" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="K67" t="s">
         <v>12</v>
@@ -3605,34 +3612,34 @@
     </row>
     <row r="68" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="B68" t="s">
         <v>12</v>
       </c>
       <c r="C68" t="s">
-        <v>122</v>
+        <v>56</v>
       </c>
       <c r="D68" t="s">
-        <v>118</v>
+        <v>96</v>
       </c>
       <c r="E68" t="s">
-        <v>123</v>
+        <v>49</v>
       </c>
       <c r="F68" t="s">
         <v>12</v>
       </c>
       <c r="G68" t="s">
-        <v>173</v>
+        <v>97</v>
       </c>
       <c r="H68" t="s">
-        <v>101</v>
+        <v>61</v>
       </c>
       <c r="I68" t="s">
-        <v>174</v>
+        <v>277</v>
       </c>
       <c r="J68" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="K68" t="s">
         <v>12</v>
@@ -3640,31 +3647,31 @@
     </row>
     <row r="69" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>63</v>
+        <v>20</v>
       </c>
       <c r="B69" t="s">
         <v>12</v>
       </c>
       <c r="C69" t="s">
-        <v>39</v>
+        <v>60</v>
       </c>
       <c r="D69" t="s">
-        <v>67</v>
+        <v>96</v>
       </c>
       <c r="E69" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="F69" t="s">
         <v>12</v>
       </c>
       <c r="G69" t="s">
-        <v>150</v>
+        <v>171</v>
       </c>
       <c r="H69" t="s">
-        <v>46</v>
+        <v>101</v>
       </c>
       <c r="I69" t="s">
-        <v>175</v>
+        <v>285</v>
       </c>
       <c r="J69" t="s">
         <v>43</v>
@@ -3675,31 +3682,31 @@
     </row>
     <row r="70" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="B70" t="s">
         <v>12</v>
       </c>
       <c r="C70" t="s">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="D70" t="s">
-        <v>67</v>
+        <v>96</v>
       </c>
       <c r="E70" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="F70" t="s">
         <v>12</v>
       </c>
       <c r="G70" t="s">
-        <v>152</v>
+        <v>215</v>
       </c>
       <c r="H70" t="s">
-        <v>65</v>
+        <v>193</v>
       </c>
       <c r="I70" t="s">
-        <v>176</v>
+        <v>288</v>
       </c>
       <c r="J70" t="s">
         <v>43</v>
@@ -3710,34 +3717,34 @@
     </row>
     <row r="71" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>52</v>
+        <v>29</v>
       </c>
       <c r="B71" t="s">
         <v>12</v>
       </c>
       <c r="C71" t="s">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="D71" t="s">
-        <v>67</v>
+        <v>93</v>
       </c>
       <c r="E71" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="F71" t="s">
         <v>12</v>
       </c>
       <c r="G71" t="s">
-        <v>152</v>
+        <v>94</v>
       </c>
       <c r="H71" t="s">
-        <v>105</v>
+        <v>81</v>
       </c>
       <c r="I71" t="s">
-        <v>177</v>
+        <v>95</v>
       </c>
       <c r="J71" t="s">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="K71" t="s">
         <v>12</v>
@@ -3745,34 +3752,34 @@
     </row>
     <row r="72" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>59</v>
+        <v>11</v>
       </c>
       <c r="B72" t="s">
         <v>12</v>
       </c>
       <c r="C72" t="s">
-        <v>60</v>
+        <v>103</v>
       </c>
       <c r="D72" t="s">
-        <v>67</v>
+        <v>93</v>
       </c>
       <c r="E72" t="s">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="F72" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="G72" t="s">
-        <v>152</v>
+        <v>94</v>
       </c>
       <c r="H72" t="s">
-        <v>61</v>
+        <v>46</v>
       </c>
       <c r="I72" t="s">
-        <v>178</v>
+        <v>116</v>
       </c>
       <c r="J72" t="s">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="K72" t="s">
         <v>12</v>
@@ -3780,34 +3787,34 @@
     </row>
     <row r="73" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B73" t="s">
         <v>12</v>
       </c>
       <c r="C73" t="s">
-        <v>48</v>
+        <v>125</v>
       </c>
       <c r="D73" t="s">
-        <v>67</v>
+        <v>93</v>
       </c>
       <c r="E73" t="s">
-        <v>49</v>
+        <v>123</v>
       </c>
       <c r="F73" t="s">
         <v>12</v>
       </c>
       <c r="G73" t="s">
-        <v>152</v>
+        <v>94</v>
       </c>
       <c r="H73" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="I73" t="s">
-        <v>179</v>
+        <v>139</v>
       </c>
       <c r="J73" t="s">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="K73" t="s">
         <v>12</v>
@@ -3815,34 +3822,34 @@
     </row>
     <row r="74" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="B74" t="s">
         <v>12</v>
       </c>
       <c r="C74" t="s">
-        <v>39</v>
+        <v>122</v>
       </c>
       <c r="D74" t="s">
-        <v>22</v>
+        <v>93</v>
       </c>
       <c r="E74" t="s">
-        <v>40</v>
+        <v>123</v>
       </c>
       <c r="F74" t="s">
         <v>12</v>
       </c>
       <c r="G74" t="s">
-        <v>71</v>
+        <v>161</v>
       </c>
       <c r="H74" t="s">
-        <v>162</v>
+        <v>61</v>
       </c>
       <c r="I74" t="s">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="J74" t="s">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="K74" t="s">
         <v>12</v>
@@ -3850,34 +3857,34 @@
     </row>
     <row r="75" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>12</v>
+        <v>140</v>
       </c>
       <c r="B75" t="s">
         <v>12</v>
       </c>
       <c r="C75" t="s">
-        <v>60</v>
+        <v>13</v>
       </c>
       <c r="D75" t="s">
-        <v>14</v>
+        <v>93</v>
       </c>
       <c r="E75" t="s">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="F75" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="G75" t="s">
-        <v>71</v>
+        <v>191</v>
       </c>
       <c r="H75" t="s">
-        <v>105</v>
+        <v>24</v>
       </c>
       <c r="I75" t="s">
-        <v>181</v>
+        <v>192</v>
       </c>
       <c r="J75" t="s">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="K75" t="s">
         <v>12</v>
@@ -3885,34 +3892,34 @@
     </row>
     <row r="76" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="B76" t="s">
         <v>12</v>
       </c>
       <c r="C76" t="s">
-        <v>60</v>
+        <v>200</v>
       </c>
       <c r="D76" t="s">
-        <v>22</v>
+        <v>93</v>
       </c>
       <c r="E76" t="s">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="F76" t="s">
         <v>12</v>
       </c>
       <c r="G76" t="s">
-        <v>182</v>
+        <v>94</v>
       </c>
       <c r="H76" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="I76" t="s">
-        <v>183</v>
+        <v>206</v>
       </c>
       <c r="J76" t="s">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="K76" t="s">
         <v>12</v>
@@ -3920,31 +3927,31 @@
     </row>
     <row r="77" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="B77" t="s">
         <v>12</v>
       </c>
       <c r="C77" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="D77" t="s">
-        <v>22</v>
+        <v>93</v>
       </c>
       <c r="E77" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="F77" t="s">
         <v>12</v>
       </c>
       <c r="G77" t="s">
-        <v>128</v>
+        <v>211</v>
       </c>
       <c r="H77" t="s">
-        <v>46</v>
+        <v>101</v>
       </c>
       <c r="I77" t="s">
-        <v>184</v>
+        <v>212</v>
       </c>
       <c r="J77" t="s">
         <v>43</v>
@@ -3955,34 +3962,34 @@
     </row>
     <row r="78" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>52</v>
+        <v>12</v>
       </c>
       <c r="B78" t="s">
         <v>12</v>
       </c>
       <c r="C78" t="s">
-        <v>13</v>
+        <v>60</v>
       </c>
       <c r="D78" t="s">
-        <v>14</v>
+        <v>93</v>
       </c>
       <c r="E78" t="s">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="F78" t="s">
         <v>12</v>
       </c>
       <c r="G78" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="H78" t="s">
-        <v>41</v>
+        <v>162</v>
       </c>
       <c r="I78" t="s">
-        <v>185</v>
+        <v>219</v>
       </c>
       <c r="J78" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="K78" t="s">
         <v>12</v>
@@ -3990,34 +3997,34 @@
     </row>
     <row r="79" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>63</v>
+        <v>12</v>
       </c>
       <c r="B79" t="s">
         <v>12</v>
       </c>
       <c r="C79" t="s">
-        <v>13</v>
+        <v>60</v>
       </c>
       <c r="D79" t="s">
-        <v>76</v>
+        <v>93</v>
       </c>
       <c r="E79" t="s">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="F79" t="s">
         <v>12</v>
       </c>
       <c r="G79" t="s">
-        <v>159</v>
+        <v>191</v>
       </c>
       <c r="H79" t="s">
-        <v>46</v>
+        <v>226</v>
       </c>
       <c r="I79" t="s">
-        <v>186</v>
+        <v>227</v>
       </c>
       <c r="J79" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="K79" t="s">
         <v>12</v>
@@ -4025,31 +4032,31 @@
     </row>
     <row r="80" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>52</v>
+        <v>121</v>
       </c>
       <c r="B80" t="s">
-        <v>12</v>
+        <v>63</v>
       </c>
       <c r="C80" t="s">
-        <v>13</v>
+        <v>145</v>
       </c>
       <c r="D80" t="s">
-        <v>79</v>
+        <v>93</v>
       </c>
       <c r="E80" t="s">
-        <v>15</v>
+        <v>146</v>
       </c>
       <c r="F80" t="s">
-        <v>29</v>
+        <v>59</v>
       </c>
       <c r="G80" t="s">
-        <v>161</v>
+        <v>77</v>
       </c>
       <c r="H80" t="s">
-        <v>41</v>
+        <v>133</v>
       </c>
       <c r="I80" t="s">
-        <v>187</v>
+        <v>245</v>
       </c>
       <c r="J80" t="s">
         <v>19</v>
@@ -4060,34 +4067,34 @@
     </row>
     <row r="81" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>63</v>
+        <v>12</v>
       </c>
       <c r="B81" t="s">
         <v>12</v>
       </c>
       <c r="C81" t="s">
-        <v>13</v>
+        <v>48</v>
       </c>
       <c r="D81" t="s">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="E81" t="s">
-        <v>15</v>
+        <v>49</v>
       </c>
       <c r="F81" t="s">
-        <v>52</v>
+        <v>12</v>
       </c>
       <c r="G81" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="H81" t="s">
-        <v>54</v>
+        <v>98</v>
       </c>
       <c r="I81" t="s">
-        <v>188</v>
+        <v>267</v>
       </c>
       <c r="J81" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="K81" t="s">
         <v>12</v>
@@ -4095,34 +4102,34 @@
     </row>
     <row r="82" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>140</v>
+        <v>12</v>
       </c>
       <c r="B82" t="s">
         <v>12</v>
       </c>
       <c r="C82" t="s">
-        <v>13</v>
+        <v>56</v>
       </c>
       <c r="D82" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="E82" t="s">
-        <v>15</v>
+        <v>49</v>
       </c>
       <c r="F82" t="s">
         <v>12</v>
       </c>
       <c r="G82" t="s">
-        <v>166</v>
+        <v>94</v>
       </c>
       <c r="H82" t="s">
-        <v>24</v>
+        <v>57</v>
       </c>
       <c r="I82" t="s">
-        <v>189</v>
+        <v>276</v>
       </c>
       <c r="J82" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="K82" t="s">
         <v>12</v>
@@ -4130,34 +4137,34 @@
     </row>
     <row r="83" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>54</v>
+        <v>11</v>
       </c>
       <c r="B83" t="s">
         <v>12</v>
       </c>
       <c r="C83" t="s">
-        <v>13</v>
+        <v>60</v>
       </c>
       <c r="D83" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="E83" t="s">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="F83" t="s">
         <v>12</v>
       </c>
       <c r="G83" t="s">
-        <v>168</v>
+        <v>191</v>
       </c>
       <c r="H83" t="s">
-        <v>27</v>
+        <v>193</v>
       </c>
       <c r="I83" t="s">
-        <v>190</v>
+        <v>286</v>
       </c>
       <c r="J83" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="K83" t="s">
         <v>12</v>
@@ -4165,34 +4172,34 @@
     </row>
     <row r="84" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>140</v>
+        <v>52</v>
       </c>
       <c r="B84" t="s">
         <v>12</v>
       </c>
       <c r="C84" t="s">
-        <v>13</v>
+        <v>44</v>
       </c>
       <c r="D84" t="s">
         <v>93</v>
       </c>
       <c r="E84" t="s">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="F84" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="G84" t="s">
-        <v>191</v>
+        <v>211</v>
       </c>
       <c r="H84" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="I84" t="s">
-        <v>192</v>
+        <v>289</v>
       </c>
       <c r="J84" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="K84" t="s">
         <v>12</v>
@@ -4200,31 +4207,31 @@
     </row>
     <row r="85" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="B85" t="s">
         <v>12</v>
       </c>
       <c r="C85" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="D85" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="E85" t="s">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="F85" t="s">
         <v>12</v>
       </c>
       <c r="G85" t="s">
-        <v>171</v>
+        <v>91</v>
       </c>
       <c r="H85" t="s">
-        <v>193</v>
+        <v>34</v>
       </c>
       <c r="I85" t="s">
-        <v>194</v>
+        <v>92</v>
       </c>
       <c r="J85" t="s">
         <v>19</v>
@@ -4235,66 +4242,66 @@
     </row>
     <row r="86" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>20</v>
+        <v>52</v>
       </c>
       <c r="B86" t="s">
         <v>12</v>
       </c>
       <c r="C86" t="s">
-        <v>13</v>
+        <v>103</v>
       </c>
       <c r="D86" t="s">
-        <v>118</v>
+        <v>90</v>
       </c>
       <c r="E86" t="s">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="F86" t="s">
         <v>12</v>
       </c>
       <c r="G86" t="s">
-        <v>173</v>
+        <v>91</v>
       </c>
       <c r="H86" t="s">
-        <v>121</v>
+        <v>105</v>
       </c>
       <c r="I86" t="s">
-        <v>195</v>
+        <v>115</v>
       </c>
       <c r="J86" t="s">
         <v>19</v>
       </c>
       <c r="K86" t="s">
-        <v>38</v>
+        <v>12</v>
       </c>
     </row>
     <row r="87" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>52</v>
+        <v>11</v>
       </c>
       <c r="B87" t="s">
         <v>12</v>
       </c>
       <c r="C87" t="s">
-        <v>13</v>
+        <v>125</v>
       </c>
       <c r="D87" t="s">
-        <v>22</v>
+        <v>90</v>
       </c>
       <c r="E87" t="s">
-        <v>15</v>
+        <v>123</v>
       </c>
       <c r="F87" t="s">
         <v>12</v>
       </c>
       <c r="G87" t="s">
-        <v>71</v>
+        <v>91</v>
       </c>
       <c r="H87" t="s">
-        <v>133</v>
+        <v>46</v>
       </c>
       <c r="I87" t="s">
-        <v>196</v>
+        <v>138</v>
       </c>
       <c r="J87" t="s">
         <v>19</v>
@@ -4305,31 +4312,31 @@
     </row>
     <row r="88" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>63</v>
+        <v>27</v>
       </c>
       <c r="B88" t="s">
         <v>12</v>
       </c>
       <c r="C88" t="s">
-        <v>21</v>
+        <v>122</v>
       </c>
       <c r="D88" t="s">
-        <v>22</v>
+        <v>90</v>
       </c>
       <c r="E88" t="s">
-        <v>15</v>
+        <v>123</v>
       </c>
       <c r="F88" t="s">
         <v>12</v>
       </c>
       <c r="G88" t="s">
-        <v>197</v>
+        <v>168</v>
       </c>
       <c r="H88" t="s">
-        <v>54</v>
+        <v>65</v>
       </c>
       <c r="I88" t="s">
-        <v>198</v>
+        <v>169</v>
       </c>
       <c r="J88" t="s">
         <v>19</v>
@@ -4340,16 +4347,16 @@
     </row>
     <row r="89" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>24</v>
+        <v>54</v>
       </c>
       <c r="B89" t="s">
-        <v>52</v>
+        <v>12</v>
       </c>
       <c r="C89" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="D89" t="s">
-        <v>14</v>
+        <v>90</v>
       </c>
       <c r="E89" t="s">
         <v>15</v>
@@ -4358,48 +4365,48 @@
         <v>12</v>
       </c>
       <c r="G89" t="s">
-        <v>74</v>
+        <v>168</v>
       </c>
       <c r="H89" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="I89" t="s">
-        <v>199</v>
+        <v>190</v>
       </c>
       <c r="J89" t="s">
         <v>19</v>
       </c>
       <c r="K89" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
     </row>
     <row r="90" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="B90" t="s">
         <v>12</v>
       </c>
       <c r="C90" t="s">
-        <v>200</v>
+        <v>21</v>
       </c>
       <c r="D90" t="s">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="E90" t="s">
         <v>15</v>
       </c>
       <c r="F90" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="G90" t="s">
-        <v>77</v>
+        <v>91</v>
       </c>
       <c r="H90" t="s">
-        <v>140</v>
+        <v>27</v>
       </c>
       <c r="I90" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="J90" t="s">
         <v>19</v>
@@ -4410,34 +4417,34 @@
     </row>
     <row r="91" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="B91" t="s">
         <v>12</v>
       </c>
       <c r="C91" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="D91" t="s">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="E91" t="s">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="F91" t="s">
         <v>12</v>
       </c>
       <c r="G91" t="s">
-        <v>80</v>
+        <v>213</v>
       </c>
       <c r="H91" t="s">
-        <v>24</v>
+        <v>133</v>
       </c>
       <c r="I91" t="s">
-        <v>202</v>
+        <v>214</v>
       </c>
       <c r="J91" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="K91" t="s">
         <v>12</v>
@@ -4445,34 +4452,34 @@
     </row>
     <row r="92" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="B92" t="s">
         <v>12</v>
       </c>
       <c r="C92" t="s">
-        <v>21</v>
+        <v>60</v>
       </c>
       <c r="D92" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="E92" t="s">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="F92" t="s">
-        <v>52</v>
+        <v>12</v>
       </c>
       <c r="G92" t="s">
-        <v>135</v>
+        <v>168</v>
       </c>
       <c r="H92" t="s">
-        <v>59</v>
+        <v>193</v>
       </c>
       <c r="I92" t="s">
-        <v>203</v>
+        <v>224</v>
       </c>
       <c r="J92" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="K92" t="s">
         <v>12</v>
@@ -4480,34 +4487,34 @@
     </row>
     <row r="93" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>63</v>
+        <v>12</v>
       </c>
       <c r="B93" t="s">
         <v>12</v>
       </c>
       <c r="C93" t="s">
-        <v>21</v>
+        <v>60</v>
       </c>
       <c r="D93" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="E93" t="s">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="F93" t="s">
         <v>12</v>
       </c>
       <c r="G93" t="s">
-        <v>87</v>
+        <v>168</v>
       </c>
       <c r="H93" t="s">
-        <v>11</v>
+        <v>57</v>
       </c>
       <c r="I93" t="s">
-        <v>204</v>
+        <v>225</v>
       </c>
       <c r="J93" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="K93" t="s">
         <v>12</v>
@@ -4515,31 +4522,31 @@
     </row>
     <row r="94" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>59</v>
+        <v>121</v>
       </c>
       <c r="B94" t="s">
-        <v>12</v>
+        <v>52</v>
       </c>
       <c r="C94" t="s">
-        <v>21</v>
+        <v>145</v>
       </c>
       <c r="D94" t="s">
         <v>90</v>
       </c>
       <c r="E94" t="s">
-        <v>15</v>
+        <v>146</v>
       </c>
       <c r="F94" t="s">
-        <v>29</v>
+        <v>52</v>
       </c>
       <c r="G94" t="s">
-        <v>91</v>
+        <v>77</v>
       </c>
       <c r="H94" t="s">
-        <v>27</v>
+        <v>133</v>
       </c>
       <c r="I94" t="s">
-        <v>205</v>
+        <v>244</v>
       </c>
       <c r="J94" t="s">
         <v>19</v>
@@ -4550,34 +4557,34 @@
     </row>
     <row r="95" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>63</v>
+        <v>121</v>
       </c>
       <c r="B95" t="s">
         <v>12</v>
       </c>
       <c r="C95" t="s">
-        <v>200</v>
+        <v>48</v>
       </c>
       <c r="D95" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="E95" t="s">
-        <v>15</v>
+        <v>49</v>
       </c>
       <c r="F95" t="s">
         <v>12</v>
       </c>
       <c r="G95" t="s">
-        <v>94</v>
+        <v>159</v>
       </c>
       <c r="H95" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="I95" t="s">
-        <v>206</v>
+        <v>266</v>
       </c>
       <c r="J95" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="K95" t="s">
         <v>12</v>
@@ -4585,34 +4592,34 @@
     </row>
     <row r="96" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>38</v>
+        <v>12</v>
       </c>
       <c r="B96" t="s">
-        <v>52</v>
+        <v>12</v>
       </c>
       <c r="C96" t="s">
-        <v>21</v>
+        <v>56</v>
       </c>
       <c r="D96" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="E96" t="s">
-        <v>15</v>
+        <v>49</v>
       </c>
       <c r="F96" t="s">
         <v>12</v>
       </c>
       <c r="G96" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="H96" t="s">
-        <v>121</v>
+        <v>65</v>
       </c>
       <c r="I96" t="s">
-        <v>207</v>
+        <v>275</v>
       </c>
       <c r="J96" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="K96" t="s">
         <v>12</v>
@@ -4623,31 +4630,31 @@
         <v>11</v>
       </c>
       <c r="B97" t="s">
-        <v>52</v>
+        <v>12</v>
       </c>
       <c r="C97" t="s">
-        <v>21</v>
+        <v>60</v>
       </c>
       <c r="D97" t="s">
-        <v>118</v>
+        <v>90</v>
       </c>
       <c r="E97" t="s">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="F97" t="s">
-        <v>38</v>
+        <v>12</v>
       </c>
       <c r="G97" t="s">
-        <v>100</v>
+        <v>168</v>
       </c>
       <c r="H97" t="s">
-        <v>20</v>
+        <v>162</v>
       </c>
       <c r="I97" t="s">
-        <v>208</v>
+        <v>287</v>
       </c>
       <c r="J97" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="K97" t="s">
         <v>12</v>
@@ -4655,31 +4662,31 @@
     </row>
     <row r="98" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="B98" t="s">
         <v>12</v>
       </c>
       <c r="C98" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="D98" t="s">
-        <v>22</v>
+        <v>90</v>
       </c>
       <c r="E98" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="F98" t="s">
         <v>12</v>
       </c>
       <c r="G98" t="s">
-        <v>128</v>
+        <v>112</v>
       </c>
       <c r="H98" t="s">
-        <v>98</v>
+        <v>41</v>
       </c>
       <c r="I98" t="s">
-        <v>209</v>
+        <v>292</v>
       </c>
       <c r="J98" t="s">
         <v>43</v>
@@ -4690,34 +4697,34 @@
     </row>
     <row r="99" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>12</v>
+        <v>59</v>
       </c>
       <c r="B99" t="s">
         <v>12</v>
       </c>
       <c r="C99" t="s">
-        <v>56</v>
+        <v>30</v>
       </c>
       <c r="D99" t="s">
-        <v>22</v>
+        <v>86</v>
       </c>
       <c r="E99" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="F99" t="s">
         <v>12</v>
       </c>
       <c r="G99" t="s">
-        <v>197</v>
+        <v>87</v>
       </c>
       <c r="H99" t="s">
-        <v>57</v>
+        <v>88</v>
       </c>
       <c r="I99" t="s">
-        <v>210</v>
+        <v>89</v>
       </c>
       <c r="J99" t="s">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="K99" t="s">
         <v>12</v>
@@ -4725,34 +4732,34 @@
     </row>
     <row r="100" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="B100" t="s">
         <v>12</v>
       </c>
       <c r="C100" t="s">
-        <v>39</v>
+        <v>103</v>
       </c>
       <c r="D100" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="E100" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="F100" t="s">
         <v>12</v>
       </c>
       <c r="G100" t="s">
-        <v>211</v>
+        <v>87</v>
       </c>
       <c r="H100" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="I100" t="s">
-        <v>212</v>
+        <v>114</v>
       </c>
       <c r="J100" t="s">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="K100" t="s">
         <v>12</v>
@@ -4760,34 +4767,34 @@
     </row>
     <row r="101" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="B101" t="s">
         <v>12</v>
       </c>
       <c r="C101" t="s">
-        <v>39</v>
+        <v>125</v>
       </c>
       <c r="D101" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="E101" t="s">
-        <v>40</v>
+        <v>123</v>
       </c>
       <c r="F101" t="s">
         <v>12</v>
       </c>
       <c r="G101" t="s">
-        <v>213</v>
+        <v>87</v>
       </c>
       <c r="H101" t="s">
-        <v>133</v>
+        <v>105</v>
       </c>
       <c r="I101" t="s">
-        <v>214</v>
+        <v>137</v>
       </c>
       <c r="J101" t="s">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="K101" t="s">
         <v>12</v>
@@ -4795,34 +4802,34 @@
     </row>
     <row r="102" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>119</v>
+        <v>27</v>
       </c>
       <c r="B102" t="s">
         <v>12</v>
       </c>
       <c r="C102" t="s">
-        <v>39</v>
+        <v>122</v>
       </c>
       <c r="D102" t="s">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="E102" t="s">
-        <v>40</v>
+        <v>123</v>
       </c>
       <c r="F102" t="s">
         <v>12</v>
       </c>
       <c r="G102" t="s">
-        <v>215</v>
+        <v>166</v>
       </c>
       <c r="H102" t="s">
-        <v>38</v>
+        <v>101</v>
       </c>
       <c r="I102" t="s">
-        <v>216</v>
+        <v>167</v>
       </c>
       <c r="J102" t="s">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="K102" t="s">
         <v>12</v>
@@ -4830,34 +4837,34 @@
     </row>
     <row r="103" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>193</v>
+        <v>140</v>
       </c>
       <c r="B103" t="s">
         <v>12</v>
       </c>
       <c r="C103" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
       <c r="D103" t="s">
-        <v>118</v>
+        <v>86</v>
       </c>
       <c r="E103" t="s">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="F103" t="s">
         <v>12</v>
       </c>
       <c r="G103" t="s">
-        <v>217</v>
+        <v>166</v>
       </c>
       <c r="H103" t="s">
-        <v>52</v>
+        <v>24</v>
       </c>
       <c r="I103" t="s">
-        <v>218</v>
+        <v>189</v>
       </c>
       <c r="J103" t="s">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="K103" t="s">
         <v>12</v>
@@ -4865,34 +4872,34 @@
     </row>
     <row r="104" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>12</v>
+        <v>63</v>
       </c>
       <c r="B104" t="s">
         <v>12</v>
       </c>
       <c r="C104" t="s">
-        <v>60</v>
+        <v>21</v>
       </c>
       <c r="D104" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="E104" t="s">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="F104" t="s">
         <v>12</v>
       </c>
       <c r="G104" t="s">
-        <v>161</v>
+        <v>87</v>
       </c>
       <c r="H104" t="s">
-        <v>162</v>
+        <v>11</v>
       </c>
       <c r="I104" t="s">
-        <v>219</v>
+        <v>204</v>
       </c>
       <c r="J104" t="s">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="K104" t="s">
         <v>12</v>
@@ -4900,34 +4907,34 @@
     </row>
     <row r="105" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
+        <v>24</v>
+      </c>
+      <c r="B105" t="s">
+        <v>63</v>
+      </c>
+      <c r="C105" t="s">
+        <v>145</v>
+      </c>
+      <c r="D105" t="s">
+        <v>86</v>
+      </c>
+      <c r="E105" t="s">
+        <v>146</v>
+      </c>
+      <c r="F105" t="s">
         <v>52</v>
       </c>
-      <c r="B105" t="s">
-        <v>12</v>
-      </c>
-      <c r="C105" t="s">
-        <v>60</v>
-      </c>
-      <c r="D105" t="s">
-        <v>96</v>
-      </c>
-      <c r="E105" t="s">
-        <v>40</v>
-      </c>
-      <c r="F105" t="s">
-        <v>12</v>
-      </c>
       <c r="G105" t="s">
-        <v>220</v>
+        <v>77</v>
       </c>
       <c r="H105" t="s">
-        <v>46</v>
+        <v>119</v>
       </c>
       <c r="I105" t="s">
-        <v>221</v>
+        <v>243</v>
       </c>
       <c r="J105" t="s">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="K105" t="s">
         <v>12</v>
@@ -4935,7 +4942,7 @@
     </row>
     <row r="106" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="B106" t="s">
         <v>12</v>
@@ -4944,7 +4951,7 @@
         <v>60</v>
       </c>
       <c r="D106" t="s">
-        <v>118</v>
+        <v>86</v>
       </c>
       <c r="E106" t="s">
         <v>40</v>
@@ -4953,13 +4960,13 @@
         <v>12</v>
       </c>
       <c r="G106" t="s">
-        <v>222</v>
+        <v>166</v>
       </c>
       <c r="H106" t="s">
-        <v>133</v>
+        <v>101</v>
       </c>
       <c r="I106" t="s">
-        <v>223</v>
+        <v>256</v>
       </c>
       <c r="J106" t="s">
         <v>43</v>
@@ -4970,7 +4977,7 @@
     </row>
     <row r="107" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>29</v>
+        <v>52</v>
       </c>
       <c r="B107" t="s">
         <v>12</v>
@@ -4979,7 +4986,7 @@
         <v>60</v>
       </c>
       <c r="D107" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="E107" t="s">
         <v>40</v>
@@ -4988,13 +4995,13 @@
         <v>12</v>
       </c>
       <c r="G107" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="H107" t="s">
-        <v>193</v>
+        <v>108</v>
       </c>
       <c r="I107" t="s">
-        <v>224</v>
+        <v>257</v>
       </c>
       <c r="J107" t="s">
         <v>43</v>
@@ -5005,31 +5012,31 @@
     </row>
     <row r="108" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>12</v>
+        <v>38</v>
       </c>
       <c r="B108" t="s">
         <v>12</v>
       </c>
       <c r="C108" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="D108" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="E108" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="F108" t="s">
         <v>12</v>
       </c>
       <c r="G108" t="s">
-        <v>168</v>
+        <v>159</v>
       </c>
       <c r="H108" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="I108" t="s">
-        <v>225</v>
+        <v>265</v>
       </c>
       <c r="J108" t="s">
         <v>43</v>
@@ -5046,25 +5053,25 @@
         <v>12</v>
       </c>
       <c r="C109" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="D109" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="E109" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="F109" t="s">
         <v>12</v>
       </c>
       <c r="G109" t="s">
-        <v>191</v>
+        <v>87</v>
       </c>
       <c r="H109" t="s">
-        <v>226</v>
+        <v>57</v>
       </c>
       <c r="I109" t="s">
-        <v>227</v>
+        <v>274</v>
       </c>
       <c r="J109" t="s">
         <v>43</v>
@@ -5075,31 +5082,31 @@
     </row>
     <row r="110" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>12</v>
+        <v>38</v>
       </c>
       <c r="B110" t="s">
         <v>12</v>
       </c>
       <c r="C110" t="s">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="D110" t="s">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="E110" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="F110" t="s">
         <v>12</v>
       </c>
       <c r="G110" t="s">
-        <v>171</v>
+        <v>132</v>
       </c>
       <c r="H110" t="s">
-        <v>105</v>
+        <v>193</v>
       </c>
       <c r="I110" t="s">
-        <v>228</v>
+        <v>279</v>
       </c>
       <c r="J110" t="s">
         <v>43</v>
@@ -5110,16 +5117,16 @@
     </row>
     <row r="111" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>52</v>
+        <v>20</v>
       </c>
       <c r="B111" t="s">
         <v>12</v>
       </c>
       <c r="C111" t="s">
-        <v>60</v>
+        <v>39</v>
       </c>
       <c r="D111" t="s">
-        <v>118</v>
+        <v>86</v>
       </c>
       <c r="E111" t="s">
         <v>40</v>
@@ -5128,13 +5135,13 @@
         <v>12</v>
       </c>
       <c r="G111" t="s">
-        <v>222</v>
+        <v>283</v>
       </c>
       <c r="H111" t="s">
-        <v>65</v>
+        <v>119</v>
       </c>
       <c r="I111" t="s">
-        <v>229</v>
+        <v>284</v>
       </c>
       <c r="J111" t="s">
         <v>43</v>
@@ -5145,31 +5152,31 @@
     </row>
     <row r="112" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B112" t="s">
         <v>12</v>
       </c>
       <c r="C112" t="s">
-        <v>39</v>
+        <v>60</v>
       </c>
       <c r="D112" t="s">
-        <v>14</v>
+        <v>86</v>
       </c>
       <c r="E112" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="F112" t="s">
         <v>12</v>
       </c>
       <c r="G112" t="s">
-        <v>197</v>
+        <v>166</v>
       </c>
       <c r="H112" t="s">
-        <v>46</v>
+        <v>108</v>
       </c>
       <c r="I112" t="s">
-        <v>230</v>
+        <v>290</v>
       </c>
       <c r="J112" t="s">
         <v>43</v>
@@ -5180,34 +5187,34 @@
     </row>
     <row r="113" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>38</v>
+        <v>12</v>
       </c>
       <c r="B113" t="s">
         <v>12</v>
       </c>
       <c r="C113" t="s">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="D113" t="s">
-        <v>22</v>
+        <v>83</v>
       </c>
       <c r="E113" t="s">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="F113" t="s">
         <v>12</v>
       </c>
       <c r="G113" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="H113" t="s">
-        <v>162</v>
+        <v>81</v>
       </c>
       <c r="I113" t="s">
-        <v>231</v>
+        <v>85</v>
       </c>
       <c r="J113" t="s">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="K113" t="s">
         <v>12</v>
@@ -5215,34 +5222,34 @@
     </row>
     <row r="114" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>38</v>
+        <v>12</v>
       </c>
       <c r="B114" t="s">
         <v>12</v>
       </c>
       <c r="C114" t="s">
-        <v>44</v>
+        <v>103</v>
       </c>
       <c r="D114" t="s">
-        <v>14</v>
+        <v>83</v>
       </c>
       <c r="E114" t="s">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="F114" t="s">
         <v>12</v>
       </c>
       <c r="G114" t="s">
-        <v>197</v>
+        <v>112</v>
       </c>
       <c r="H114" t="s">
-        <v>193</v>
+        <v>65</v>
       </c>
       <c r="I114" t="s">
-        <v>232</v>
+        <v>113</v>
       </c>
       <c r="J114" t="s">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="K114" t="s">
         <v>12</v>
@@ -5250,34 +5257,34 @@
     </row>
     <row r="115" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>59</v>
+        <v>29</v>
       </c>
       <c r="B115" t="s">
         <v>12</v>
       </c>
       <c r="C115" t="s">
-        <v>44</v>
+        <v>125</v>
       </c>
       <c r="D115" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="E115" t="s">
-        <v>45</v>
+        <v>123</v>
       </c>
       <c r="F115" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="G115" t="s">
-        <v>233</v>
+        <v>135</v>
       </c>
       <c r="H115" t="s">
-        <v>193</v>
+        <v>65</v>
       </c>
       <c r="I115" t="s">
-        <v>234</v>
+        <v>136</v>
       </c>
       <c r="J115" t="s">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="K115" t="s">
         <v>12</v>
@@ -5285,34 +5292,34 @@
     </row>
     <row r="116" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>101</v>
+        <v>11</v>
       </c>
       <c r="B116" t="s">
         <v>12</v>
       </c>
       <c r="C116" t="s">
-        <v>44</v>
+        <v>122</v>
       </c>
       <c r="D116" t="s">
-        <v>118</v>
+        <v>83</v>
       </c>
       <c r="E116" t="s">
-        <v>45</v>
+        <v>123</v>
       </c>
       <c r="F116" t="s">
         <v>12</v>
       </c>
       <c r="G116" t="s">
-        <v>173</v>
+        <v>164</v>
       </c>
       <c r="H116" t="s">
-        <v>38</v>
+        <v>61</v>
       </c>
       <c r="I116" t="s">
-        <v>235</v>
+        <v>165</v>
       </c>
       <c r="J116" t="s">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="K116" t="s">
         <v>12</v>
@@ -5320,34 +5327,34 @@
     </row>
     <row r="117" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>38</v>
+        <v>63</v>
       </c>
       <c r="B117" t="s">
         <v>12</v>
       </c>
       <c r="C117" t="s">
-        <v>60</v>
+        <v>13</v>
       </c>
       <c r="D117" t="s">
-        <v>14</v>
+        <v>83</v>
       </c>
       <c r="E117" t="s">
-        <v>45</v>
+        <v>15</v>
       </c>
       <c r="F117" t="s">
-        <v>12</v>
+        <v>52</v>
       </c>
       <c r="G117" t="s">
-        <v>157</v>
+        <v>164</v>
       </c>
       <c r="H117" t="s">
-        <v>193</v>
+        <v>54</v>
       </c>
       <c r="I117" t="s">
-        <v>236</v>
+        <v>188</v>
       </c>
       <c r="J117" t="s">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="K117" t="s">
         <v>12</v>
@@ -5355,34 +5362,34 @@
     </row>
     <row r="118" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
+        <v>38</v>
+      </c>
+      <c r="B118" t="s">
+        <v>12</v>
+      </c>
+      <c r="C118" t="s">
+        <v>21</v>
+      </c>
+      <c r="D118" t="s">
+        <v>83</v>
+      </c>
+      <c r="E118" t="s">
+        <v>15</v>
+      </c>
+      <c r="F118" t="s">
+        <v>52</v>
+      </c>
+      <c r="G118" t="s">
+        <v>135</v>
+      </c>
+      <c r="H118" t="s">
         <v>59</v>
       </c>
-      <c r="B118" t="s">
-        <v>12</v>
-      </c>
-      <c r="C118" t="s">
-        <v>60</v>
-      </c>
-      <c r="D118" t="s">
-        <v>118</v>
-      </c>
-      <c r="E118" t="s">
-        <v>45</v>
-      </c>
-      <c r="F118" t="s">
-        <v>12</v>
-      </c>
-      <c r="G118" t="s">
-        <v>222</v>
-      </c>
-      <c r="H118" t="s">
-        <v>65</v>
-      </c>
       <c r="I118" t="s">
-        <v>237</v>
+        <v>203</v>
       </c>
       <c r="J118" t="s">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="K118" t="s">
         <v>12</v>
@@ -5390,34 +5397,34 @@
     </row>
     <row r="119" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="B119" t="s">
-        <v>12</v>
+        <v>52</v>
       </c>
       <c r="C119" t="s">
-        <v>44</v>
+        <v>145</v>
       </c>
       <c r="D119" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="E119" t="s">
-        <v>45</v>
+        <v>146</v>
       </c>
       <c r="F119" t="s">
-        <v>12</v>
+        <v>52</v>
       </c>
       <c r="G119" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="H119" t="s">
         <v>193</v>
       </c>
       <c r="I119" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="J119" t="s">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="K119" t="s">
         <v>12</v>
@@ -5425,31 +5432,31 @@
     </row>
     <row r="120" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>12</v>
+        <v>59</v>
       </c>
       <c r="B120" t="s">
         <v>12</v>
       </c>
       <c r="C120" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="D120" t="s">
-        <v>14</v>
+        <v>83</v>
       </c>
       <c r="E120" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="F120" t="s">
         <v>12</v>
       </c>
       <c r="G120" t="s">
-        <v>74</v>
+        <v>161</v>
       </c>
       <c r="H120" t="s">
-        <v>226</v>
+        <v>108</v>
       </c>
       <c r="I120" t="s">
-        <v>239</v>
+        <v>255</v>
       </c>
       <c r="J120" t="s">
         <v>43</v>
@@ -5460,34 +5467,34 @@
     </row>
     <row r="121" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>121</v>
+        <v>63</v>
       </c>
       <c r="B121" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="C121" t="s">
-        <v>145</v>
+        <v>44</v>
       </c>
       <c r="D121" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="E121" t="s">
-        <v>146</v>
+        <v>45</v>
       </c>
       <c r="F121" t="s">
-        <v>59</v>
+        <v>12</v>
       </c>
       <c r="G121" t="s">
-        <v>77</v>
+        <v>258</v>
       </c>
       <c r="H121" t="s">
-        <v>108</v>
+        <v>46</v>
       </c>
       <c r="I121" t="s">
-        <v>240</v>
+        <v>261</v>
       </c>
       <c r="J121" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="K121" t="s">
         <v>12</v>
@@ -5495,34 +5502,34 @@
     </row>
     <row r="122" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>24</v>
+        <v>121</v>
       </c>
       <c r="B122" t="s">
-        <v>63</v>
+        <v>12</v>
       </c>
       <c r="C122" t="s">
-        <v>145</v>
+        <v>48</v>
       </c>
       <c r="D122" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="E122" t="s">
-        <v>146</v>
+        <v>49</v>
       </c>
       <c r="F122" t="s">
-        <v>52</v>
+        <v>12</v>
       </c>
       <c r="G122" t="s">
-        <v>77</v>
+        <v>157</v>
       </c>
       <c r="H122" t="s">
-        <v>193</v>
+        <v>133</v>
       </c>
       <c r="I122" t="s">
-        <v>241</v>
+        <v>264</v>
       </c>
       <c r="J122" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="K122" t="s">
         <v>12</v>
@@ -5530,34 +5537,34 @@
     </row>
     <row r="123" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="B123" t="s">
-        <v>52</v>
+        <v>12</v>
       </c>
       <c r="C123" t="s">
-        <v>145</v>
+        <v>56</v>
       </c>
       <c r="D123" t="s">
         <v>83</v>
       </c>
       <c r="E123" t="s">
-        <v>146</v>
+        <v>49</v>
       </c>
       <c r="F123" t="s">
-        <v>52</v>
+        <v>12</v>
       </c>
       <c r="G123" t="s">
-        <v>77</v>
+        <v>135</v>
       </c>
       <c r="H123" t="s">
-        <v>193</v>
+        <v>65</v>
       </c>
       <c r="I123" t="s">
-        <v>242</v>
+        <v>273</v>
       </c>
       <c r="J123" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="K123" t="s">
         <v>12</v>
@@ -5565,34 +5572,34 @@
     </row>
     <row r="124" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>24</v>
+        <v>59</v>
       </c>
       <c r="B124" t="s">
-        <v>63</v>
+        <v>12</v>
       </c>
       <c r="C124" t="s">
-        <v>145</v>
+        <v>60</v>
       </c>
       <c r="D124" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="E124" t="s">
-        <v>146</v>
+        <v>40</v>
       </c>
       <c r="F124" t="s">
-        <v>52</v>
+        <v>12</v>
       </c>
       <c r="G124" t="s">
-        <v>77</v>
+        <v>161</v>
       </c>
       <c r="H124" t="s">
-        <v>119</v>
+        <v>133</v>
       </c>
       <c r="I124" t="s">
-        <v>243</v>
+        <v>281</v>
       </c>
       <c r="J124" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="K124" t="s">
         <v>12</v>
@@ -5600,34 +5607,34 @@
     </row>
     <row r="125" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>121</v>
+        <v>59</v>
       </c>
       <c r="B125" t="s">
-        <v>52</v>
+        <v>12</v>
       </c>
       <c r="C125" t="s">
-        <v>145</v>
+        <v>39</v>
       </c>
       <c r="D125" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="E125" t="s">
-        <v>146</v>
+        <v>40</v>
       </c>
       <c r="F125" t="s">
-        <v>52</v>
+        <v>12</v>
       </c>
       <c r="G125" t="s">
-        <v>77</v>
+        <v>112</v>
       </c>
       <c r="H125" t="s">
-        <v>133</v>
+        <v>193</v>
       </c>
       <c r="I125" t="s">
-        <v>244</v>
+        <v>282</v>
       </c>
       <c r="J125" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="K125" t="s">
         <v>12</v>
@@ -5635,34 +5642,34 @@
     </row>
     <row r="126" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>121</v>
+        <v>12</v>
       </c>
       <c r="B126" t="s">
-        <v>63</v>
+        <v>12</v>
       </c>
       <c r="C126" t="s">
-        <v>145</v>
+        <v>60</v>
       </c>
       <c r="D126" t="s">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="E126" t="s">
-        <v>146</v>
+        <v>45</v>
       </c>
       <c r="F126" t="s">
-        <v>59</v>
+        <v>12</v>
       </c>
       <c r="G126" t="s">
-        <v>77</v>
+        <v>135</v>
       </c>
       <c r="H126" t="s">
-        <v>133</v>
+        <v>226</v>
       </c>
       <c r="I126" t="s">
-        <v>245</v>
+        <v>291</v>
       </c>
       <c r="J126" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="K126" t="s">
         <v>12</v>
@@ -5670,31 +5677,31 @@
     </row>
     <row r="127" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>140</v>
+        <v>12</v>
       </c>
       <c r="B127" t="s">
-        <v>52</v>
+        <v>12</v>
       </c>
       <c r="C127" t="s">
-        <v>145</v>
+        <v>30</v>
       </c>
       <c r="D127" t="s">
-        <v>96</v>
+        <v>79</v>
       </c>
       <c r="E127" t="s">
-        <v>146</v>
+        <v>32</v>
       </c>
       <c r="F127" t="s">
-        <v>38</v>
+        <v>12</v>
       </c>
       <c r="G127" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="H127" t="s">
-        <v>133</v>
+        <v>81</v>
       </c>
       <c r="I127" t="s">
-        <v>246</v>
+        <v>82</v>
       </c>
       <c r="J127" t="s">
         <v>19</v>
@@ -5705,31 +5712,31 @@
     </row>
     <row r="128" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>144</v>
+        <v>12</v>
       </c>
       <c r="B128" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="C128" t="s">
-        <v>145</v>
+        <v>103</v>
       </c>
       <c r="D128" t="s">
-        <v>118</v>
+        <v>79</v>
       </c>
       <c r="E128" t="s">
-        <v>146</v>
+        <v>32</v>
       </c>
       <c r="F128" t="s">
-        <v>38</v>
+        <v>12</v>
       </c>
       <c r="G128" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="H128" t="s">
-        <v>101</v>
+        <v>65</v>
       </c>
       <c r="I128" t="s">
-        <v>247</v>
+        <v>111</v>
       </c>
       <c r="J128" t="s">
         <v>19</v>
@@ -5740,34 +5747,34 @@
     </row>
     <row r="129" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>12</v>
+        <v>121</v>
       </c>
       <c r="B129" t="s">
         <v>12</v>
       </c>
       <c r="C129" t="s">
-        <v>56</v>
+        <v>125</v>
       </c>
       <c r="D129" t="s">
-        <v>14</v>
+        <v>79</v>
       </c>
       <c r="E129" t="s">
-        <v>49</v>
+        <v>123</v>
       </c>
       <c r="F129" t="s">
         <v>12</v>
       </c>
       <c r="G129" t="s">
-        <v>157</v>
+        <v>132</v>
       </c>
       <c r="H129" t="s">
-        <v>61</v>
+        <v>133</v>
       </c>
       <c r="I129" t="s">
-        <v>248</v>
+        <v>134</v>
       </c>
       <c r="J129" t="s">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="K129" t="s">
         <v>12</v>
@@ -5775,34 +5782,34 @@
     </row>
     <row r="130" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="B130" t="s">
         <v>12</v>
       </c>
       <c r="C130" t="s">
-        <v>60</v>
+        <v>122</v>
       </c>
       <c r="D130" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="E130" t="s">
-        <v>40</v>
+        <v>123</v>
       </c>
       <c r="F130" t="s">
         <v>12</v>
       </c>
       <c r="G130" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="H130" t="s">
-        <v>101</v>
+        <v>162</v>
       </c>
       <c r="I130" t="s">
-        <v>249</v>
+        <v>163</v>
       </c>
       <c r="J130" t="s">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="K130" t="s">
         <v>12</v>
@@ -5810,34 +5817,34 @@
     </row>
     <row r="131" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>12</v>
+        <v>52</v>
       </c>
       <c r="B131" t="s">
         <v>12</v>
       </c>
       <c r="C131" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
       <c r="D131" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="E131" t="s">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="F131" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="G131" t="s">
-        <v>74</v>
+        <v>161</v>
       </c>
       <c r="H131" t="s">
-        <v>133</v>
+        <v>41</v>
       </c>
       <c r="I131" t="s">
-        <v>250</v>
+        <v>187</v>
       </c>
       <c r="J131" t="s">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="K131" t="s">
         <v>12</v>
@@ -5845,34 +5852,34 @@
     </row>
     <row r="132" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="B132" t="s">
         <v>12</v>
       </c>
       <c r="C132" t="s">
-        <v>60</v>
+        <v>21</v>
       </c>
       <c r="D132" t="s">
-        <v>14</v>
+        <v>79</v>
       </c>
       <c r="E132" t="s">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="F132" t="s">
         <v>12</v>
       </c>
       <c r="G132" t="s">
-        <v>233</v>
+        <v>80</v>
       </c>
       <c r="H132" t="s">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="I132" t="s">
-        <v>251</v>
+        <v>202</v>
       </c>
       <c r="J132" t="s">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="K132" t="s">
         <v>12</v>
@@ -5880,31 +5887,31 @@
     </row>
     <row r="133" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>12</v>
+        <v>38</v>
       </c>
       <c r="B133" t="s">
         <v>12</v>
       </c>
       <c r="C133" t="s">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="D133" t="s">
         <v>79</v>
       </c>
       <c r="E133" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="F133" t="s">
         <v>12</v>
       </c>
       <c r="G133" t="s">
-        <v>252</v>
+        <v>74</v>
       </c>
       <c r="H133" t="s">
-        <v>101</v>
+        <v>193</v>
       </c>
       <c r="I133" t="s">
-        <v>253</v>
+        <v>238</v>
       </c>
       <c r="J133" t="s">
         <v>43</v>
@@ -5915,34 +5922,34 @@
     </row>
     <row r="134" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
+        <v>24</v>
+      </c>
+      <c r="B134" t="s">
         <v>63</v>
       </c>
-      <c r="B134" t="s">
-        <v>12</v>
-      </c>
       <c r="C134" t="s">
-        <v>60</v>
+        <v>145</v>
       </c>
       <c r="D134" t="s">
         <v>79</v>
       </c>
       <c r="E134" t="s">
-        <v>40</v>
+        <v>146</v>
       </c>
       <c r="F134" t="s">
-        <v>12</v>
+        <v>52</v>
       </c>
       <c r="G134" t="s">
-        <v>161</v>
+        <v>77</v>
       </c>
       <c r="H134" t="s">
-        <v>61</v>
+        <v>193</v>
       </c>
       <c r="I134" t="s">
-        <v>254</v>
+        <v>241</v>
       </c>
       <c r="J134" t="s">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="K134" t="s">
         <v>12</v>
@@ -5950,7 +5957,7 @@
     </row>
     <row r="135" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>59</v>
+        <v>12</v>
       </c>
       <c r="B135" t="s">
         <v>12</v>
@@ -5959,7 +5966,7 @@
         <v>60</v>
       </c>
       <c r="D135" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="E135" t="s">
         <v>40</v>
@@ -5968,13 +5975,13 @@
         <v>12</v>
       </c>
       <c r="G135" t="s">
-        <v>161</v>
+        <v>252</v>
       </c>
       <c r="H135" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="I135" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="J135" t="s">
         <v>43</v>
@@ -5985,7 +5992,7 @@
     </row>
     <row r="136" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="B136" t="s">
         <v>12</v>
@@ -5994,7 +6001,7 @@
         <v>60</v>
       </c>
       <c r="D136" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="E136" t="s">
         <v>40</v>
@@ -6003,13 +6010,13 @@
         <v>12</v>
       </c>
       <c r="G136" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="H136" t="s">
-        <v>101</v>
+        <v>61</v>
       </c>
       <c r="I136" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="J136" t="s">
         <v>43</v>
@@ -6026,10 +6033,10 @@
         <v>12</v>
       </c>
       <c r="C137" t="s">
-        <v>60</v>
+        <v>39</v>
       </c>
       <c r="D137" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="E137" t="s">
         <v>40</v>
@@ -6038,13 +6045,13 @@
         <v>12</v>
       </c>
       <c r="G137" t="s">
-        <v>166</v>
+        <v>258</v>
       </c>
       <c r="H137" t="s">
-        <v>108</v>
+        <v>41</v>
       </c>
       <c r="I137" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="J137" t="s">
         <v>43</v>
@@ -6055,31 +6062,31 @@
     </row>
     <row r="138" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>52</v>
+        <v>29</v>
       </c>
       <c r="B138" t="s">
         <v>12</v>
       </c>
       <c r="C138" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="D138" t="s">
         <v>79</v>
       </c>
       <c r="E138" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="F138" t="s">
         <v>12</v>
       </c>
       <c r="G138" t="s">
-        <v>258</v>
+        <v>159</v>
       </c>
       <c r="H138" t="s">
-        <v>41</v>
+        <v>226</v>
       </c>
       <c r="I138" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="J138" t="s">
         <v>43</v>
@@ -6096,10 +6103,10 @@
         <v>12</v>
       </c>
       <c r="C139" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="D139" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="E139" t="s">
         <v>49</v>
@@ -6108,13 +6115,13 @@
         <v>12</v>
       </c>
       <c r="G139" t="s">
-        <v>258</v>
+        <v>80</v>
       </c>
       <c r="H139" t="s">
-        <v>226</v>
+        <v>57</v>
       </c>
       <c r="I139" t="s">
-        <v>260</v>
+        <v>272</v>
       </c>
       <c r="J139" t="s">
         <v>43</v>
@@ -6125,16 +6132,16 @@
     </row>
     <row r="140" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="B140" t="s">
         <v>12</v>
       </c>
       <c r="C140" t="s">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="D140" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="E140" t="s">
         <v>45</v>
@@ -6143,13 +6150,13 @@
         <v>12</v>
       </c>
       <c r="G140" t="s">
-        <v>258</v>
+        <v>161</v>
       </c>
       <c r="H140" t="s">
-        <v>46</v>
+        <v>101</v>
       </c>
       <c r="I140" t="s">
-        <v>261</v>
+        <v>280</v>
       </c>
       <c r="J140" t="s">
         <v>43</v>
@@ -6160,34 +6167,34 @@
     </row>
     <row r="141" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B141" t="s">
         <v>12</v>
       </c>
       <c r="C141" t="s">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="D141" t="s">
         <v>76</v>
       </c>
       <c r="E141" t="s">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="F141" t="s">
         <v>12</v>
       </c>
       <c r="G141" t="s">
-        <v>159</v>
+        <v>77</v>
       </c>
       <c r="H141" t="s">
-        <v>46</v>
+        <v>72</v>
       </c>
       <c r="I141" t="s">
-        <v>262</v>
+        <v>78</v>
       </c>
       <c r="J141" t="s">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="K141" t="s">
         <v>12</v>
@@ -6195,34 +6202,34 @@
     </row>
     <row r="142" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="B142" t="s">
         <v>12</v>
       </c>
       <c r="C142" t="s">
-        <v>48</v>
+        <v>103</v>
       </c>
       <c r="D142" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="E142" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="F142" t="s">
         <v>12</v>
       </c>
       <c r="G142" t="s">
-        <v>159</v>
+        <v>77</v>
       </c>
       <c r="H142" t="s">
-        <v>226</v>
+        <v>65</v>
       </c>
       <c r="I142" t="s">
-        <v>263</v>
+        <v>110</v>
       </c>
       <c r="J142" t="s">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="K142" t="s">
         <v>12</v>
@@ -6230,34 +6237,34 @@
     </row>
     <row r="143" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>121</v>
+        <v>59</v>
       </c>
       <c r="B143" t="s">
         <v>12</v>
       </c>
       <c r="C143" t="s">
-        <v>48</v>
+        <v>125</v>
       </c>
       <c r="D143" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="E143" t="s">
-        <v>49</v>
+        <v>123</v>
       </c>
       <c r="F143" t="s">
         <v>12</v>
       </c>
       <c r="G143" t="s">
-        <v>157</v>
+        <v>77</v>
       </c>
       <c r="H143" t="s">
-        <v>133</v>
+        <v>61</v>
       </c>
       <c r="I143" t="s">
-        <v>264</v>
+        <v>131</v>
       </c>
       <c r="J143" t="s">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="K143" t="s">
         <v>12</v>
@@ -6265,19 +6272,19 @@
     </row>
     <row r="144" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="B144" t="s">
         <v>12</v>
       </c>
       <c r="C144" t="s">
-        <v>48</v>
+        <v>122</v>
       </c>
       <c r="D144" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="E144" t="s">
-        <v>49</v>
+        <v>123</v>
       </c>
       <c r="F144" t="s">
         <v>12</v>
@@ -6286,13 +6293,13 @@
         <v>159</v>
       </c>
       <c r="H144" t="s">
-        <v>46</v>
+        <v>105</v>
       </c>
       <c r="I144" t="s">
-        <v>265</v>
+        <v>160</v>
       </c>
       <c r="J144" t="s">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="K144" t="s">
         <v>12</v>
@@ -6300,19 +6307,19 @@
     </row>
     <row r="145" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>121</v>
+        <v>63</v>
       </c>
       <c r="B145" t="s">
         <v>12</v>
       </c>
       <c r="C145" t="s">
-        <v>48</v>
+        <v>13</v>
       </c>
       <c r="D145" t="s">
-        <v>90</v>
+        <v>76</v>
       </c>
       <c r="E145" t="s">
-        <v>49</v>
+        <v>15</v>
       </c>
       <c r="F145" t="s">
         <v>12</v>
@@ -6324,10 +6331,10 @@
         <v>46</v>
       </c>
       <c r="I145" t="s">
-        <v>266</v>
+        <v>186</v>
       </c>
       <c r="J145" t="s">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="K145" t="s">
         <v>12</v>
@@ -6335,34 +6342,34 @@
     </row>
     <row r="146" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>12</v>
+        <v>52</v>
       </c>
       <c r="B146" t="s">
         <v>12</v>
       </c>
       <c r="C146" t="s">
-        <v>48</v>
+        <v>200</v>
       </c>
       <c r="D146" t="s">
-        <v>93</v>
+        <v>76</v>
       </c>
       <c r="E146" t="s">
-        <v>49</v>
+        <v>15</v>
       </c>
       <c r="F146" t="s">
         <v>12</v>
       </c>
       <c r="G146" t="s">
-        <v>159</v>
+        <v>77</v>
       </c>
       <c r="H146" t="s">
-        <v>98</v>
+        <v>140</v>
       </c>
       <c r="I146" t="s">
-        <v>267</v>
+        <v>201</v>
       </c>
       <c r="J146" t="s">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="K146" t="s">
         <v>12</v>
@@ -6370,31 +6377,31 @@
     </row>
     <row r="147" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>29</v>
+        <v>59</v>
       </c>
       <c r="B147" t="s">
         <v>12</v>
       </c>
       <c r="C147" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="D147" t="s">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="E147" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="F147" t="s">
         <v>12</v>
       </c>
       <c r="G147" t="s">
-        <v>159</v>
+        <v>233</v>
       </c>
       <c r="H147" t="s">
-        <v>98</v>
+        <v>193</v>
       </c>
       <c r="I147" t="s">
-        <v>268</v>
+        <v>234</v>
       </c>
       <c r="J147" t="s">
         <v>43</v>
@@ -6405,34 +6412,34 @@
     </row>
     <row r="148" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>140</v>
+        <v>121</v>
       </c>
       <c r="B148" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="C148" t="s">
-        <v>48</v>
+        <v>145</v>
       </c>
       <c r="D148" t="s">
-        <v>118</v>
+        <v>76</v>
       </c>
       <c r="E148" t="s">
-        <v>49</v>
+        <v>146</v>
       </c>
       <c r="F148" t="s">
-        <v>12</v>
+        <v>59</v>
       </c>
       <c r="G148" t="s">
-        <v>159</v>
+        <v>77</v>
       </c>
       <c r="H148" t="s">
-        <v>193</v>
+        <v>108</v>
       </c>
       <c r="I148" t="s">
-        <v>269</v>
+        <v>240</v>
       </c>
       <c r="J148" t="s">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="K148" t="s">
         <v>12</v>
@@ -6440,31 +6447,31 @@
     </row>
     <row r="149" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="B149" t="s">
         <v>12</v>
       </c>
       <c r="C149" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="D149" t="s">
         <v>76</v>
       </c>
       <c r="E149" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="F149" t="s">
         <v>12</v>
       </c>
       <c r="G149" t="s">
-        <v>77</v>
+        <v>157</v>
       </c>
       <c r="H149" t="s">
-        <v>61</v>
+        <v>101</v>
       </c>
       <c r="I149" t="s">
-        <v>270</v>
+        <v>249</v>
       </c>
       <c r="J149" t="s">
         <v>43</v>
@@ -6475,13 +6482,13 @@
     </row>
     <row r="150" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>63</v>
+        <v>12</v>
       </c>
       <c r="B150" t="s">
         <v>12</v>
       </c>
       <c r="C150" t="s">
-        <v>60</v>
+        <v>39</v>
       </c>
       <c r="D150" t="s">
         <v>76</v>
@@ -6493,13 +6500,13 @@
         <v>12</v>
       </c>
       <c r="G150" t="s">
-        <v>159</v>
+        <v>74</v>
       </c>
       <c r="H150" t="s">
-        <v>46</v>
+        <v>133</v>
       </c>
       <c r="I150" t="s">
-        <v>271</v>
+        <v>250</v>
       </c>
       <c r="J150" t="s">
         <v>43</v>
@@ -6516,10 +6523,10 @@
         <v>12</v>
       </c>
       <c r="C151" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="D151" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="E151" t="s">
         <v>49</v>
@@ -6528,13 +6535,13 @@
         <v>12</v>
       </c>
       <c r="G151" t="s">
-        <v>80</v>
+        <v>258</v>
       </c>
       <c r="H151" t="s">
-        <v>57</v>
+        <v>226</v>
       </c>
       <c r="I151" t="s">
-        <v>272</v>
+        <v>260</v>
       </c>
       <c r="J151" t="s">
         <v>43</v>
@@ -6545,31 +6552,31 @@
     </row>
     <row r="152" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B152" t="s">
         <v>12</v>
       </c>
       <c r="C152" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="D152" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="E152" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="F152" t="s">
         <v>12</v>
       </c>
       <c r="G152" t="s">
-        <v>135</v>
+        <v>159</v>
       </c>
       <c r="H152" t="s">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="I152" t="s">
-        <v>273</v>
+        <v>262</v>
       </c>
       <c r="J152" t="s">
         <v>43</v>
@@ -6589,7 +6596,7 @@
         <v>56</v>
       </c>
       <c r="D153" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="E153" t="s">
         <v>49</v>
@@ -6598,13 +6605,13 @@
         <v>12</v>
       </c>
       <c r="G153" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="H153" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="I153" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="J153" t="s">
         <v>43</v>
@@ -6615,31 +6622,31 @@
     </row>
     <row r="154" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>12</v>
+        <v>63</v>
       </c>
       <c r="B154" t="s">
         <v>12</v>
       </c>
       <c r="C154" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="D154" t="s">
-        <v>90</v>
+        <v>76</v>
       </c>
       <c r="E154" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="F154" t="s">
         <v>12</v>
       </c>
       <c r="G154" t="s">
-        <v>91</v>
+        <v>159</v>
       </c>
       <c r="H154" t="s">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="I154" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="J154" t="s">
         <v>43</v>
@@ -6650,34 +6657,34 @@
     </row>
     <row r="155" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B155" t="s">
         <v>12</v>
       </c>
       <c r="C155" t="s">
-        <v>56</v>
+        <v>13</v>
       </c>
       <c r="D155" t="s">
-        <v>93</v>
+        <v>14</v>
       </c>
       <c r="E155" t="s">
-        <v>49</v>
+        <v>15</v>
       </c>
       <c r="F155" t="s">
         <v>12</v>
       </c>
       <c r="G155" t="s">
-        <v>94</v>
+        <v>16</v>
       </c>
       <c r="H155" t="s">
-        <v>57</v>
+        <v>17</v>
       </c>
       <c r="I155" t="s">
-        <v>276</v>
+        <v>18</v>
       </c>
       <c r="J155" t="s">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="K155" t="s">
         <v>12</v>
@@ -6685,34 +6692,34 @@
     </row>
     <row r="156" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="B156" t="s">
         <v>12</v>
       </c>
       <c r="C156" t="s">
-        <v>56</v>
+        <v>21</v>
       </c>
       <c r="D156" t="s">
-        <v>96</v>
+        <v>14</v>
       </c>
       <c r="E156" t="s">
-        <v>49</v>
+        <v>15</v>
       </c>
       <c r="F156" t="s">
         <v>12</v>
       </c>
       <c r="G156" t="s">
-        <v>97</v>
+        <v>26</v>
       </c>
       <c r="H156" t="s">
-        <v>61</v>
+        <v>27</v>
       </c>
       <c r="I156" t="s">
-        <v>277</v>
+        <v>28</v>
       </c>
       <c r="J156" t="s">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="K156" t="s">
         <v>12</v>
@@ -6726,28 +6733,28 @@
         <v>12</v>
       </c>
       <c r="C157" t="s">
-        <v>56</v>
+        <v>30</v>
       </c>
       <c r="D157" t="s">
-        <v>118</v>
+        <v>14</v>
       </c>
       <c r="E157" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="F157" t="s">
         <v>12</v>
       </c>
       <c r="G157" t="s">
-        <v>222</v>
+        <v>74</v>
       </c>
       <c r="H157" t="s">
-        <v>105</v>
+        <v>34</v>
       </c>
       <c r="I157" t="s">
-        <v>278</v>
+        <v>75</v>
       </c>
       <c r="J157" t="s">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="K157" t="s">
         <v>12</v>
@@ -6755,34 +6762,34 @@
     </row>
     <row r="158" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>38</v>
+        <v>63</v>
       </c>
       <c r="B158" t="s">
         <v>12</v>
       </c>
       <c r="C158" t="s">
-        <v>44</v>
+        <v>103</v>
       </c>
       <c r="D158" t="s">
-        <v>86</v>
+        <v>14</v>
       </c>
       <c r="E158" t="s">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="F158" t="s">
         <v>12</v>
       </c>
       <c r="G158" t="s">
-        <v>132</v>
+        <v>74</v>
       </c>
       <c r="H158" t="s">
-        <v>193</v>
+        <v>108</v>
       </c>
       <c r="I158" t="s">
-        <v>279</v>
+        <v>109</v>
       </c>
       <c r="J158" t="s">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="K158" t="s">
         <v>12</v>
@@ -6790,34 +6797,34 @@
     </row>
     <row r="159" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="B159" t="s">
         <v>12</v>
       </c>
       <c r="C159" t="s">
-        <v>60</v>
+        <v>125</v>
       </c>
       <c r="D159" t="s">
-        <v>79</v>
+        <v>14</v>
       </c>
       <c r="E159" t="s">
-        <v>45</v>
+        <v>123</v>
       </c>
       <c r="F159" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="G159" t="s">
-        <v>161</v>
+        <v>74</v>
       </c>
       <c r="H159" t="s">
-        <v>101</v>
+        <v>121</v>
       </c>
       <c r="I159" t="s">
-        <v>280</v>
+        <v>130</v>
       </c>
       <c r="J159" t="s">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="K159" t="s">
         <v>12</v>
@@ -6825,34 +6832,34 @@
     </row>
     <row r="160" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>59</v>
+        <v>41</v>
       </c>
       <c r="B160" t="s">
         <v>12</v>
       </c>
       <c r="C160" t="s">
-        <v>60</v>
+        <v>145</v>
       </c>
       <c r="D160" t="s">
-        <v>83</v>
+        <v>14</v>
       </c>
       <c r="E160" t="s">
-        <v>40</v>
+        <v>146</v>
       </c>
       <c r="F160" t="s">
         <v>12</v>
       </c>
       <c r="G160" t="s">
-        <v>161</v>
+        <v>68</v>
       </c>
       <c r="H160" t="s">
-        <v>133</v>
+        <v>69</v>
       </c>
       <c r="I160" t="s">
-        <v>281</v>
+        <v>149</v>
       </c>
       <c r="J160" t="s">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="K160" t="s">
         <v>12</v>
@@ -6860,34 +6867,34 @@
     </row>
     <row r="161" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>59</v>
+        <v>38</v>
       </c>
       <c r="B161" t="s">
         <v>12</v>
       </c>
       <c r="C161" t="s">
-        <v>39</v>
+        <v>122</v>
       </c>
       <c r="D161" t="s">
-        <v>83</v>
+        <v>14</v>
       </c>
       <c r="E161" t="s">
-        <v>40</v>
+        <v>123</v>
       </c>
       <c r="F161" t="s">
         <v>12</v>
       </c>
       <c r="G161" t="s">
-        <v>112</v>
+        <v>157</v>
       </c>
       <c r="H161" t="s">
-        <v>193</v>
+        <v>108</v>
       </c>
       <c r="I161" t="s">
-        <v>282</v>
+        <v>158</v>
       </c>
       <c r="J161" t="s">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="K161" t="s">
         <v>12</v>
@@ -6895,16 +6902,16 @@
     </row>
     <row r="162" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="B162" t="s">
         <v>12</v>
       </c>
       <c r="C162" t="s">
-        <v>39</v>
+        <v>60</v>
       </c>
       <c r="D162" t="s">
-        <v>86</v>
+        <v>14</v>
       </c>
       <c r="E162" t="s">
         <v>40</v>
@@ -6913,13 +6920,13 @@
         <v>12</v>
       </c>
       <c r="G162" t="s">
-        <v>283</v>
+        <v>71</v>
       </c>
       <c r="H162" t="s">
-        <v>119</v>
+        <v>105</v>
       </c>
       <c r="I162" t="s">
-        <v>284</v>
+        <v>181</v>
       </c>
       <c r="J162" t="s">
         <v>43</v>
@@ -6930,34 +6937,34 @@
     </row>
     <row r="163" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>20</v>
+        <v>52</v>
       </c>
       <c r="B163" t="s">
         <v>12</v>
       </c>
       <c r="C163" t="s">
-        <v>60</v>
+        <v>13</v>
       </c>
       <c r="D163" t="s">
-        <v>96</v>
+        <v>14</v>
       </c>
       <c r="E163" t="s">
-        <v>45</v>
+        <v>15</v>
       </c>
       <c r="F163" t="s">
         <v>12</v>
       </c>
       <c r="G163" t="s">
-        <v>171</v>
+        <v>157</v>
       </c>
       <c r="H163" t="s">
-        <v>101</v>
+        <v>41</v>
       </c>
       <c r="I163" t="s">
-        <v>285</v>
+        <v>185</v>
       </c>
       <c r="J163" t="s">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="K163" t="s">
         <v>12</v>
@@ -6965,66 +6972,66 @@
     </row>
     <row r="164" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="B164" t="s">
-        <v>12</v>
+        <v>52</v>
       </c>
       <c r="C164" t="s">
-        <v>60</v>
+        <v>21</v>
       </c>
       <c r="D164" t="s">
-        <v>93</v>
+        <v>14</v>
       </c>
       <c r="E164" t="s">
-        <v>45</v>
+        <v>15</v>
       </c>
       <c r="F164" t="s">
         <v>12</v>
       </c>
       <c r="G164" t="s">
-        <v>191</v>
+        <v>74</v>
       </c>
       <c r="H164" t="s">
-        <v>193</v>
+        <v>29</v>
       </c>
       <c r="I164" t="s">
-        <v>286</v>
+        <v>199</v>
       </c>
       <c r="J164" t="s">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="K164" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
     </row>
     <row r="165" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B165" t="s">
         <v>12</v>
       </c>
       <c r="C165" t="s">
-        <v>60</v>
+        <v>39</v>
       </c>
       <c r="D165" t="s">
-        <v>90</v>
+        <v>14</v>
       </c>
       <c r="E165" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="F165" t="s">
         <v>12</v>
       </c>
       <c r="G165" t="s">
-        <v>168</v>
+        <v>197</v>
       </c>
       <c r="H165" t="s">
-        <v>162</v>
+        <v>46</v>
       </c>
       <c r="I165" t="s">
-        <v>287</v>
+        <v>230</v>
       </c>
       <c r="J165" t="s">
         <v>43</v>
@@ -7035,7 +7042,7 @@
     </row>
     <row r="166" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="B166" t="s">
         <v>12</v>
@@ -7044,7 +7051,7 @@
         <v>44</v>
       </c>
       <c r="D166" t="s">
-        <v>96</v>
+        <v>14</v>
       </c>
       <c r="E166" t="s">
         <v>45</v>
@@ -7053,13 +7060,13 @@
         <v>12</v>
       </c>
       <c r="G166" t="s">
-        <v>215</v>
+        <v>197</v>
       </c>
       <c r="H166" t="s">
         <v>193</v>
       </c>
       <c r="I166" t="s">
-        <v>288</v>
+        <v>232</v>
       </c>
       <c r="J166" t="s">
         <v>43</v>
@@ -7070,16 +7077,16 @@
     </row>
     <row r="167" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="B167" t="s">
         <v>12</v>
       </c>
       <c r="C167" t="s">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="D167" t="s">
-        <v>93</v>
+        <v>14</v>
       </c>
       <c r="E167" t="s">
         <v>45</v>
@@ -7088,13 +7095,13 @@
         <v>12</v>
       </c>
       <c r="G167" t="s">
-        <v>211</v>
+        <v>157</v>
       </c>
       <c r="H167" t="s">
-        <v>17</v>
+        <v>193</v>
       </c>
       <c r="I167" t="s">
-        <v>289</v>
+        <v>236</v>
       </c>
       <c r="J167" t="s">
         <v>43</v>
@@ -7105,31 +7112,31 @@
     </row>
     <row r="168" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B168" t="s">
         <v>12</v>
       </c>
       <c r="C168" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="D168" t="s">
-        <v>86</v>
+        <v>14</v>
       </c>
       <c r="E168" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="F168" t="s">
         <v>12</v>
       </c>
       <c r="G168" t="s">
-        <v>166</v>
+        <v>74</v>
       </c>
       <c r="H168" t="s">
-        <v>108</v>
+        <v>226</v>
       </c>
       <c r="I168" t="s">
-        <v>290</v>
+        <v>239</v>
       </c>
       <c r="J168" t="s">
         <v>43</v>
@@ -7146,25 +7153,25 @@
         <v>12</v>
       </c>
       <c r="C169" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="D169" t="s">
-        <v>83</v>
+        <v>14</v>
       </c>
       <c r="E169" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="F169" t="s">
         <v>12</v>
       </c>
       <c r="G169" t="s">
-        <v>135</v>
+        <v>157</v>
       </c>
       <c r="H169" t="s">
-        <v>226</v>
+        <v>61</v>
       </c>
       <c r="I169" t="s">
-        <v>291</v>
+        <v>248</v>
       </c>
       <c r="J169" t="s">
         <v>43</v>
@@ -7175,31 +7182,31 @@
     </row>
     <row r="170" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>24</v>
+        <v>59</v>
       </c>
       <c r="B170" t="s">
         <v>12</v>
       </c>
       <c r="C170" t="s">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="D170" t="s">
-        <v>90</v>
+        <v>14</v>
       </c>
       <c r="E170" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="F170" t="s">
         <v>12</v>
       </c>
       <c r="G170" t="s">
-        <v>112</v>
+        <v>233</v>
       </c>
       <c r="H170" t="s">
         <v>41</v>
       </c>
       <c r="I170" t="s">
-        <v>292</v>
+        <v>251</v>
       </c>
       <c r="J170" t="s">
         <v>43</v>
@@ -7209,11 +7216,23 @@
       </c>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K170">
+    <sortCondition ref="D1:D170"/>
+  </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <TaxCatchAll xmlns="54c5ab46-7543-4aba-b0fa-79d6a199bef5" xsi:nil="true"/>
@@ -7222,15 +7241,6 @@
     </lcf76f155ced4ddcb4097134ff3c332f>
   </documentManagement>
 </p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -7469,6 +7479,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FB788E5D-2D79-4363-AF59-D9AE6FBE16C9}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{73DE38E5-A439-4DFE-870D-009DEC8E8546}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -7479,14 +7497,21 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FB788E5D-2D79-4363-AF59-D9AE6FBE16C9}">
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{03C74B1E-6305-431E-B65A-AECD2878EEED}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="20d57abc-823c-4051-a81a-1a0a01a8f39e"/>
+    <ds:schemaRef ds:uri="54c5ab46-7543-4aba-b0fa-79d6a199bef5"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{03C74B1E-6305-431E-B65A-AECD2878EEED}"/>
 </file>
--- a/Qualidade_Sessoes.xlsx
+++ b/Qualidade_Sessoes.xlsx
@@ -8,14 +8,30 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://muvamozorg.sharepoint.com/sites/mis.drive/Documentos Partilhados/PROJECTOS/Sistema de Monitoria/NEXUS/2026/Dash_Nexus/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="11" documentId="11_CA7BA6727B39BFF18534DF48238D9D3350433DF5" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{44A05A78-AC65-469D-8BFA-CBF0CF83351F}"/>
+  <xr:revisionPtr revIDLastSave="24" documentId="11_CA7BA6727B39BFF18534DF48238D9D3350433DF5" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DFC1A8FF-40A2-44C2-8C92-D808AB483225}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$K$170</definedName>
+  </definedNames>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -1251,6 +1267,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:K170"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1302,31 +1319,31 @@
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>144</v>
+      </c>
+      <c r="B2" t="s">
         <v>20</v>
       </c>
-      <c r="B2" t="s">
-        <v>12</v>
-      </c>
       <c r="C2" t="s">
-        <v>103</v>
+        <v>145</v>
       </c>
       <c r="D2" t="s">
         <v>118</v>
       </c>
       <c r="E2" t="s">
-        <v>32</v>
+        <v>146</v>
       </c>
       <c r="F2" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="G2" t="s">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="H2" t="s">
-        <v>119</v>
+        <v>101</v>
       </c>
       <c r="I2" t="s">
-        <v>120</v>
+        <v>247</v>
       </c>
       <c r="J2" t="s">
         <v>19</v>
@@ -1337,66 +1354,66 @@
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="B3" t="s">
         <v>12</v>
       </c>
       <c r="C3" t="s">
-        <v>125</v>
+        <v>13</v>
       </c>
       <c r="D3" t="s">
         <v>118</v>
       </c>
       <c r="E3" t="s">
-        <v>123</v>
+        <v>15</v>
       </c>
       <c r="F3" t="s">
-        <v>52</v>
+        <v>12</v>
       </c>
       <c r="G3" t="s">
-        <v>100</v>
+        <v>173</v>
       </c>
       <c r="H3" t="s">
-        <v>133</v>
+        <v>121</v>
       </c>
       <c r="I3" t="s">
-        <v>142</v>
+        <v>195</v>
       </c>
       <c r="J3" t="s">
         <v>19</v>
       </c>
       <c r="K3" t="s">
-        <v>12</v>
+        <v>38</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>12</v>
+        <v>52</v>
       </c>
       <c r="C4" t="s">
-        <v>122</v>
+        <v>21</v>
       </c>
       <c r="D4" t="s">
         <v>118</v>
       </c>
       <c r="E4" t="s">
-        <v>123</v>
+        <v>15</v>
       </c>
       <c r="F4" t="s">
-        <v>12</v>
+        <v>38</v>
       </c>
       <c r="G4" t="s">
-        <v>173</v>
+        <v>100</v>
       </c>
       <c r="H4" t="s">
-        <v>101</v>
+        <v>20</v>
       </c>
       <c r="I4" t="s">
-        <v>174</v>
+        <v>208</v>
       </c>
       <c r="J4" t="s">
         <v>19</v>
@@ -1407,66 +1424,66 @@
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="B5" t="s">
         <v>12</v>
       </c>
       <c r="C5" t="s">
-        <v>13</v>
+        <v>125</v>
       </c>
       <c r="D5" t="s">
         <v>118</v>
       </c>
       <c r="E5" t="s">
-        <v>15</v>
+        <v>123</v>
       </c>
       <c r="F5" t="s">
-        <v>12</v>
+        <v>52</v>
       </c>
       <c r="G5" t="s">
-        <v>173</v>
+        <v>100</v>
       </c>
       <c r="H5" t="s">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="I5" t="s">
-        <v>195</v>
+        <v>142</v>
       </c>
       <c r="J5" t="s">
         <v>19</v>
       </c>
       <c r="K5" t="s">
-        <v>38</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="B6" t="s">
-        <v>52</v>
+        <v>12</v>
       </c>
       <c r="C6" t="s">
-        <v>21</v>
+        <v>103</v>
       </c>
       <c r="D6" t="s">
         <v>118</v>
       </c>
       <c r="E6" t="s">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="F6" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="G6" t="s">
         <v>100</v>
       </c>
       <c r="H6" t="s">
-        <v>20</v>
+        <v>119</v>
       </c>
       <c r="I6" t="s">
-        <v>208</v>
+        <v>120</v>
       </c>
       <c r="J6" t="s">
         <v>19</v>
@@ -1475,7 +1492,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>193</v>
       </c>
@@ -1510,7 +1527,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>63</v>
       </c>
@@ -1545,7 +1562,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>52</v>
       </c>
@@ -1580,7 +1597,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>101</v>
       </c>
@@ -1615,7 +1632,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>59</v>
       </c>
@@ -1652,31 +1669,31 @@
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>144</v>
+        <v>24</v>
       </c>
       <c r="B12" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="C12" t="s">
-        <v>145</v>
+        <v>122</v>
       </c>
       <c r="D12" t="s">
         <v>118</v>
       </c>
       <c r="E12" t="s">
-        <v>146</v>
+        <v>123</v>
       </c>
       <c r="F12" t="s">
-        <v>38</v>
+        <v>12</v>
       </c>
       <c r="G12" t="s">
-        <v>77</v>
+        <v>173</v>
       </c>
       <c r="H12" t="s">
         <v>101</v>
       </c>
       <c r="I12" t="s">
-        <v>247</v>
+        <v>174</v>
       </c>
       <c r="J12" t="s">
         <v>19</v>
@@ -1685,7 +1702,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>140</v>
       </c>
@@ -1720,7 +1737,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>12</v>
       </c>
@@ -1757,31 +1774,31 @@
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>20</v>
+        <v>54</v>
       </c>
       <c r="B15" t="s">
         <v>12</v>
       </c>
       <c r="C15" t="s">
-        <v>21</v>
+        <v>145</v>
       </c>
       <c r="D15" t="s">
         <v>22</v>
       </c>
       <c r="E15" t="s">
-        <v>15</v>
+        <v>146</v>
       </c>
       <c r="F15" t="s">
         <v>12</v>
       </c>
       <c r="G15" t="s">
-        <v>23</v>
+        <v>68</v>
       </c>
       <c r="H15" t="s">
-        <v>24</v>
+        <v>98</v>
       </c>
       <c r="I15" t="s">
-        <v>25</v>
+        <v>148</v>
       </c>
       <c r="J15" t="s">
         <v>19</v>
@@ -1792,19 +1809,19 @@
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>12</v>
+        <v>52</v>
       </c>
       <c r="B16" t="s">
         <v>12</v>
       </c>
       <c r="C16" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="D16" t="s">
         <v>22</v>
       </c>
       <c r="E16" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="F16" t="s">
         <v>12</v>
@@ -1813,10 +1830,10 @@
         <v>71</v>
       </c>
       <c r="H16" t="s">
-        <v>72</v>
+        <v>133</v>
       </c>
       <c r="I16" t="s">
-        <v>73</v>
+        <v>196</v>
       </c>
       <c r="J16" t="s">
         <v>19</v>
@@ -1827,31 +1844,31 @@
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>52</v>
+        <v>20</v>
       </c>
       <c r="B17" t="s">
         <v>12</v>
       </c>
       <c r="C17" t="s">
-        <v>103</v>
+        <v>21</v>
       </c>
       <c r="D17" t="s">
         <v>22</v>
       </c>
       <c r="E17" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="F17" t="s">
         <v>12</v>
       </c>
       <c r="G17" t="s">
-        <v>71</v>
+        <v>23</v>
       </c>
       <c r="H17" t="s">
-        <v>61</v>
+        <v>24</v>
       </c>
       <c r="I17" t="s">
-        <v>107</v>
+        <v>25</v>
       </c>
       <c r="J17" t="s">
         <v>19</v>
@@ -1862,31 +1879,31 @@
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>38</v>
+        <v>63</v>
       </c>
       <c r="B18" t="s">
-        <v>52</v>
+        <v>12</v>
       </c>
       <c r="C18" t="s">
-        <v>125</v>
+        <v>21</v>
       </c>
       <c r="D18" t="s">
         <v>22</v>
       </c>
       <c r="E18" t="s">
-        <v>123</v>
+        <v>15</v>
       </c>
       <c r="F18" t="s">
-        <v>63</v>
+        <v>12</v>
       </c>
       <c r="G18" t="s">
-        <v>128</v>
+        <v>197</v>
       </c>
       <c r="H18" t="s">
-        <v>119</v>
+        <v>54</v>
       </c>
       <c r="I18" t="s">
-        <v>129</v>
+        <v>198</v>
       </c>
       <c r="J18" t="s">
         <v>19</v>
@@ -1897,31 +1914,31 @@
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>54</v>
+        <v>38</v>
       </c>
       <c r="B19" t="s">
-        <v>12</v>
+        <v>52</v>
       </c>
       <c r="C19" t="s">
-        <v>145</v>
+        <v>125</v>
       </c>
       <c r="D19" t="s">
         <v>22</v>
       </c>
       <c r="E19" t="s">
-        <v>146</v>
+        <v>123</v>
       </c>
       <c r="F19" t="s">
-        <v>12</v>
+        <v>63</v>
       </c>
       <c r="G19" t="s">
-        <v>68</v>
+        <v>128</v>
       </c>
       <c r="H19" t="s">
-        <v>98</v>
+        <v>119</v>
       </c>
       <c r="I19" t="s">
-        <v>148</v>
+        <v>129</v>
       </c>
       <c r="J19" t="s">
         <v>19</v>
@@ -1932,19 +1949,19 @@
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>11</v>
+        <v>52</v>
       </c>
       <c r="B20" t="s">
         <v>12</v>
       </c>
       <c r="C20" t="s">
-        <v>122</v>
+        <v>103</v>
       </c>
       <c r="D20" t="s">
         <v>22</v>
       </c>
       <c r="E20" t="s">
-        <v>123</v>
+        <v>32</v>
       </c>
       <c r="F20" t="s">
         <v>12</v>
@@ -1953,10 +1970,10 @@
         <v>71</v>
       </c>
       <c r="H20" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="I20" t="s">
-        <v>156</v>
+        <v>107</v>
       </c>
       <c r="J20" t="s">
         <v>19</v>
@@ -1965,7 +1982,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>29</v>
       </c>
@@ -2000,7 +2017,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>52</v>
       </c>
@@ -2035,7 +2052,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>20</v>
       </c>
@@ -2072,19 +2089,19 @@
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>52</v>
+        <v>11</v>
       </c>
       <c r="B24" t="s">
         <v>12</v>
       </c>
       <c r="C24" t="s">
-        <v>13</v>
+        <v>122</v>
       </c>
       <c r="D24" t="s">
         <v>22</v>
       </c>
       <c r="E24" t="s">
-        <v>15</v>
+        <v>123</v>
       </c>
       <c r="F24" t="s">
         <v>12</v>
@@ -2093,10 +2110,10 @@
         <v>71</v>
       </c>
       <c r="H24" t="s">
-        <v>133</v>
+        <v>65</v>
       </c>
       <c r="I24" t="s">
-        <v>196</v>
+        <v>156</v>
       </c>
       <c r="J24" t="s">
         <v>19</v>
@@ -2107,31 +2124,31 @@
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>63</v>
+        <v>12</v>
       </c>
       <c r="B25" t="s">
         <v>12</v>
       </c>
       <c r="C25" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="D25" t="s">
         <v>22</v>
       </c>
       <c r="E25" t="s">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="F25" t="s">
         <v>12</v>
       </c>
       <c r="G25" t="s">
-        <v>197</v>
+        <v>71</v>
       </c>
       <c r="H25" t="s">
-        <v>54</v>
+        <v>72</v>
       </c>
       <c r="I25" t="s">
-        <v>198</v>
+        <v>73</v>
       </c>
       <c r="J25" t="s">
         <v>19</v>
@@ -2140,7 +2157,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>12</v>
       </c>
@@ -2175,7 +2192,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>12</v>
       </c>
@@ -2210,7 +2227,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>38</v>
       </c>
@@ -2247,19 +2264,19 @@
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>12</v>
+        <v>144</v>
       </c>
       <c r="B29" t="s">
         <v>12</v>
       </c>
       <c r="C29" t="s">
-        <v>30</v>
+        <v>145</v>
       </c>
       <c r="D29" t="s">
         <v>67</v>
       </c>
       <c r="E29" t="s">
-        <v>32</v>
+        <v>146</v>
       </c>
       <c r="F29" t="s">
         <v>12</v>
@@ -2268,10 +2285,10 @@
         <v>68</v>
       </c>
       <c r="H29" t="s">
-        <v>69</v>
+        <v>88</v>
       </c>
       <c r="I29" t="s">
-        <v>70</v>
+        <v>147</v>
       </c>
       <c r="J29" t="s">
         <v>19</v>
@@ -2282,31 +2299,31 @@
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="B30" t="s">
         <v>12</v>
       </c>
       <c r="C30" t="s">
-        <v>103</v>
+        <v>13</v>
       </c>
       <c r="D30" t="s">
         <v>67</v>
       </c>
       <c r="E30" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="F30" t="s">
         <v>12</v>
       </c>
       <c r="G30" t="s">
-        <v>68</v>
+        <v>152</v>
       </c>
       <c r="H30" t="s">
-        <v>105</v>
+        <v>54</v>
       </c>
       <c r="I30" t="s">
-        <v>106</v>
+        <v>153</v>
       </c>
       <c r="J30" t="s">
         <v>19</v>
@@ -2317,40 +2334,40 @@
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>27</v>
+        <v>63</v>
       </c>
       <c r="B31" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="C31" t="s">
-        <v>125</v>
+        <v>21</v>
       </c>
       <c r="D31" t="s">
         <v>67</v>
       </c>
       <c r="E31" t="s">
-        <v>123</v>
+        <v>15</v>
       </c>
       <c r="F31" t="s">
-        <v>59</v>
+        <v>29</v>
       </c>
       <c r="G31" t="s">
-        <v>68</v>
+        <v>150</v>
       </c>
       <c r="H31" t="s">
-        <v>54</v>
+        <v>140</v>
       </c>
       <c r="I31" t="s">
-        <v>127</v>
+        <v>151</v>
       </c>
       <c r="J31" t="s">
         <v>19</v>
       </c>
       <c r="K31" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>12</v>
       </c>
@@ -2387,66 +2404,66 @@
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>144</v>
+        <v>27</v>
       </c>
       <c r="B33" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="C33" t="s">
-        <v>145</v>
+        <v>125</v>
       </c>
       <c r="D33" t="s">
         <v>67</v>
       </c>
       <c r="E33" t="s">
-        <v>146</v>
+        <v>123</v>
       </c>
       <c r="F33" t="s">
-        <v>12</v>
+        <v>59</v>
       </c>
       <c r="G33" t="s">
         <v>68</v>
       </c>
       <c r="H33" t="s">
-        <v>88</v>
+        <v>54</v>
       </c>
       <c r="I33" t="s">
-        <v>147</v>
+        <v>127</v>
       </c>
       <c r="J33" t="s">
         <v>19</v>
       </c>
       <c r="K33" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>63</v>
+        <v>12</v>
       </c>
       <c r="B34" t="s">
         <v>12</v>
       </c>
       <c r="C34" t="s">
-        <v>21</v>
+        <v>103</v>
       </c>
       <c r="D34" t="s">
         <v>67</v>
       </c>
       <c r="E34" t="s">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="F34" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="G34" t="s">
-        <v>150</v>
+        <v>68</v>
       </c>
       <c r="H34" t="s">
-        <v>140</v>
+        <v>105</v>
       </c>
       <c r="I34" t="s">
-        <v>151</v>
+        <v>106</v>
       </c>
       <c r="J34" t="s">
         <v>19</v>
@@ -2463,13 +2480,13 @@
         <v>12</v>
       </c>
       <c r="C35" t="s">
-        <v>13</v>
+        <v>122</v>
       </c>
       <c r="D35" t="s">
         <v>67</v>
       </c>
       <c r="E35" t="s">
-        <v>15</v>
+        <v>123</v>
       </c>
       <c r="F35" t="s">
         <v>12</v>
@@ -2478,10 +2495,10 @@
         <v>152</v>
       </c>
       <c r="H35" t="s">
-        <v>54</v>
+        <v>105</v>
       </c>
       <c r="I35" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="J35" t="s">
         <v>19</v>
@@ -2490,7 +2507,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>11</v>
       </c>
@@ -2527,31 +2544,31 @@
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="B37" t="s">
         <v>12</v>
       </c>
       <c r="C37" t="s">
-        <v>122</v>
+        <v>30</v>
       </c>
       <c r="D37" t="s">
         <v>67</v>
       </c>
       <c r="E37" t="s">
-        <v>123</v>
+        <v>32</v>
       </c>
       <c r="F37" t="s">
         <v>12</v>
       </c>
       <c r="G37" t="s">
-        <v>152</v>
+        <v>68</v>
       </c>
       <c r="H37" t="s">
-        <v>105</v>
+        <v>69</v>
       </c>
       <c r="I37" t="s">
-        <v>155</v>
+        <v>70</v>
       </c>
       <c r="J37" t="s">
         <v>19</v>
@@ -2560,7 +2577,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>63</v>
       </c>
@@ -2595,7 +2612,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>12</v>
       </c>
@@ -2630,7 +2647,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>52</v>
       </c>
@@ -2665,7 +2682,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>59</v>
       </c>
@@ -2700,7 +2717,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>12</v>
       </c>
@@ -2737,31 +2754,31 @@
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="B43" t="s">
         <v>12</v>
       </c>
       <c r="C43" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="D43" t="s">
         <v>31</v>
       </c>
       <c r="E43" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="F43" t="s">
-        <v>12</v>
+        <v>52</v>
       </c>
       <c r="G43" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="H43" t="s">
-        <v>34</v>
+        <v>54</v>
       </c>
       <c r="I43" t="s">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="J43" t="s">
         <v>19</v>
@@ -2805,7 +2822,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>38</v>
       </c>
@@ -2840,7 +2857,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>20</v>
       </c>
@@ -2875,7 +2892,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>12</v>
       </c>
@@ -2912,31 +2929,31 @@
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>11</v>
+        <v>38</v>
       </c>
       <c r="B48" t="s">
         <v>12</v>
       </c>
       <c r="C48" t="s">
-        <v>13</v>
+        <v>125</v>
       </c>
       <c r="D48" t="s">
         <v>31</v>
       </c>
       <c r="E48" t="s">
-        <v>15</v>
+        <v>123</v>
       </c>
       <c r="F48" t="s">
-        <v>52</v>
+        <v>29</v>
       </c>
       <c r="G48" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="H48" t="s">
-        <v>54</v>
+        <v>108</v>
       </c>
       <c r="I48" t="s">
-        <v>55</v>
+        <v>126</v>
       </c>
       <c r="J48" t="s">
         <v>19</v>
@@ -2945,7 +2962,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>12</v>
       </c>
@@ -2980,7 +2997,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>59</v>
       </c>
@@ -3015,7 +3032,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>63</v>
       </c>
@@ -3050,7 +3067,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>12</v>
       </c>
@@ -3087,13 +3104,13 @@
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>59</v>
+        <v>12</v>
       </c>
       <c r="B53" t="s">
         <v>12</v>
       </c>
       <c r="C53" t="s">
-        <v>30</v>
+        <v>103</v>
       </c>
       <c r="D53" t="s">
         <v>31</v>
@@ -3102,16 +3119,16 @@
         <v>32</v>
       </c>
       <c r="F53" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="G53" t="s">
-        <v>100</v>
+        <v>33</v>
       </c>
       <c r="H53" t="s">
-        <v>101</v>
+        <v>61</v>
       </c>
       <c r="I53" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="J53" t="s">
         <v>19</v>
@@ -3122,31 +3139,31 @@
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>12</v>
+        <v>121</v>
       </c>
       <c r="B54" t="s">
         <v>12</v>
       </c>
       <c r="C54" t="s">
-        <v>103</v>
+        <v>122</v>
       </c>
       <c r="D54" t="s">
         <v>31</v>
       </c>
       <c r="E54" t="s">
-        <v>32</v>
+        <v>123</v>
       </c>
       <c r="F54" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="G54" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="H54" t="s">
-        <v>61</v>
+        <v>101</v>
       </c>
       <c r="I54" t="s">
-        <v>104</v>
+        <v>124</v>
       </c>
       <c r="J54" t="s">
         <v>19</v>
@@ -3157,31 +3174,31 @@
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>121</v>
+        <v>29</v>
       </c>
       <c r="B55" t="s">
         <v>12</v>
       </c>
       <c r="C55" t="s">
-        <v>122</v>
+        <v>30</v>
       </c>
       <c r="D55" t="s">
         <v>31</v>
       </c>
       <c r="E55" t="s">
-        <v>123</v>
+        <v>32</v>
       </c>
       <c r="F55" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="G55" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="H55" t="s">
-        <v>101</v>
+        <v>34</v>
       </c>
       <c r="I55" t="s">
-        <v>124</v>
+        <v>35</v>
       </c>
       <c r="J55" t="s">
         <v>19</v>
@@ -3192,31 +3209,31 @@
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>38</v>
+        <v>59</v>
       </c>
       <c r="B56" t="s">
         <v>12</v>
       </c>
       <c r="C56" t="s">
-        <v>125</v>
+        <v>30</v>
       </c>
       <c r="D56" t="s">
         <v>31</v>
       </c>
       <c r="E56" t="s">
-        <v>123</v>
+        <v>32</v>
       </c>
       <c r="F56" t="s">
         <v>29</v>
       </c>
       <c r="G56" t="s">
-        <v>33</v>
+        <v>100</v>
       </c>
       <c r="H56" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="I56" t="s">
-        <v>126</v>
+        <v>102</v>
       </c>
       <c r="J56" t="s">
         <v>19</v>
@@ -3227,31 +3244,31 @@
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>20</v>
+        <v>140</v>
       </c>
       <c r="B57" t="s">
-        <v>12</v>
+        <v>52</v>
       </c>
       <c r="C57" t="s">
-        <v>30</v>
+        <v>145</v>
       </c>
       <c r="D57" t="s">
         <v>96</v>
       </c>
       <c r="E57" t="s">
-        <v>32</v>
+        <v>146</v>
       </c>
       <c r="F57" t="s">
-        <v>12</v>
+        <v>38</v>
       </c>
       <c r="G57" t="s">
-        <v>97</v>
+        <v>77</v>
       </c>
       <c r="H57" t="s">
-        <v>98</v>
+        <v>133</v>
       </c>
       <c r="I57" t="s">
-        <v>99</v>
+        <v>246</v>
       </c>
       <c r="J57" t="s">
         <v>19</v>
@@ -3262,54 +3279,54 @@
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="B58" t="s">
         <v>12</v>
       </c>
       <c r="C58" t="s">
-        <v>103</v>
+        <v>13</v>
       </c>
       <c r="D58" t="s">
         <v>96</v>
       </c>
       <c r="E58" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="F58" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="G58" t="s">
-        <v>97</v>
+        <v>171</v>
       </c>
       <c r="H58" t="s">
-        <v>108</v>
+        <v>193</v>
       </c>
       <c r="I58" t="s">
-        <v>117</v>
+        <v>194</v>
       </c>
       <c r="J58" t="s">
         <v>19</v>
       </c>
       <c r="K58" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>140</v>
+        <v>38</v>
       </c>
       <c r="B59" t="s">
-        <v>12</v>
+        <v>52</v>
       </c>
       <c r="C59" t="s">
-        <v>125</v>
+        <v>21</v>
       </c>
       <c r="D59" t="s">
         <v>96</v>
       </c>
       <c r="E59" t="s">
-        <v>123</v>
+        <v>15</v>
       </c>
       <c r="F59" t="s">
         <v>12</v>
@@ -3318,10 +3335,10 @@
         <v>97</v>
       </c>
       <c r="H59" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="I59" t="s">
-        <v>141</v>
+        <v>207</v>
       </c>
       <c r="J59" t="s">
         <v>19</v>
@@ -3332,13 +3349,13 @@
     </row>
     <row r="60" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>24</v>
+        <v>140</v>
       </c>
       <c r="B60" t="s">
         <v>12</v>
       </c>
       <c r="C60" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="D60" t="s">
         <v>96</v>
@@ -3350,13 +3367,13 @@
         <v>12</v>
       </c>
       <c r="G60" t="s">
-        <v>171</v>
+        <v>97</v>
       </c>
       <c r="H60" t="s">
-        <v>105</v>
+        <v>119</v>
       </c>
       <c r="I60" t="s">
-        <v>172</v>
+        <v>141</v>
       </c>
       <c r="J60" t="s">
         <v>19</v>
@@ -3367,66 +3384,66 @@
     </row>
     <row r="61" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="B61" t="s">
         <v>12</v>
       </c>
       <c r="C61" t="s">
-        <v>13</v>
+        <v>103</v>
       </c>
       <c r="D61" t="s">
         <v>96</v>
       </c>
       <c r="E61" t="s">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="F61" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="G61" t="s">
-        <v>171</v>
+        <v>97</v>
       </c>
       <c r="H61" t="s">
-        <v>193</v>
+        <v>108</v>
       </c>
       <c r="I61" t="s">
-        <v>194</v>
+        <v>117</v>
       </c>
       <c r="J61" t="s">
         <v>19</v>
       </c>
       <c r="K61" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
     </row>
     <row r="62" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="B62" t="s">
-        <v>52</v>
+        <v>12</v>
       </c>
       <c r="C62" t="s">
-        <v>21</v>
+        <v>122</v>
       </c>
       <c r="D62" t="s">
         <v>96</v>
       </c>
       <c r="E62" t="s">
-        <v>15</v>
+        <v>123</v>
       </c>
       <c r="F62" t="s">
         <v>12</v>
       </c>
       <c r="G62" t="s">
-        <v>97</v>
+        <v>171</v>
       </c>
       <c r="H62" t="s">
-        <v>121</v>
+        <v>105</v>
       </c>
       <c r="I62" t="s">
-        <v>207</v>
+        <v>172</v>
       </c>
       <c r="J62" t="s">
         <v>19</v>
@@ -3435,7 +3452,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>119</v>
       </c>
@@ -3470,7 +3487,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>52</v>
       </c>
@@ -3505,7 +3522,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>12</v>
       </c>
@@ -3542,31 +3559,31 @@
     </row>
     <row r="66" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>140</v>
+        <v>20</v>
       </c>
       <c r="B66" t="s">
-        <v>52</v>
+        <v>12</v>
       </c>
       <c r="C66" t="s">
-        <v>145</v>
+        <v>30</v>
       </c>
       <c r="D66" t="s">
         <v>96</v>
       </c>
       <c r="E66" t="s">
-        <v>146</v>
+        <v>32</v>
       </c>
       <c r="F66" t="s">
-        <v>38</v>
+        <v>12</v>
       </c>
       <c r="G66" t="s">
-        <v>77</v>
+        <v>97</v>
       </c>
       <c r="H66" t="s">
-        <v>133</v>
+        <v>98</v>
       </c>
       <c r="I66" t="s">
-        <v>246</v>
+        <v>99</v>
       </c>
       <c r="J66" t="s">
         <v>19</v>
@@ -3575,7 +3592,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="67" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>29</v>
       </c>
@@ -3610,7 +3627,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="68" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>12</v>
       </c>
@@ -3645,7 +3662,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="69" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>20</v>
       </c>
@@ -3680,7 +3697,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="70" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>20</v>
       </c>
@@ -3717,31 +3734,31 @@
     </row>
     <row r="71" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>29</v>
+        <v>121</v>
       </c>
       <c r="B71" t="s">
-        <v>12</v>
+        <v>63</v>
       </c>
       <c r="C71" t="s">
-        <v>30</v>
+        <v>145</v>
       </c>
       <c r="D71" t="s">
         <v>93</v>
       </c>
       <c r="E71" t="s">
-        <v>32</v>
+        <v>146</v>
       </c>
       <c r="F71" t="s">
-        <v>12</v>
+        <v>59</v>
       </c>
       <c r="G71" t="s">
-        <v>94</v>
+        <v>77</v>
       </c>
       <c r="H71" t="s">
-        <v>81</v>
+        <v>133</v>
       </c>
       <c r="I71" t="s">
-        <v>95</v>
+        <v>245</v>
       </c>
       <c r="J71" t="s">
         <v>19</v>
@@ -3752,31 +3769,31 @@
     </row>
     <row r="72" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>11</v>
+        <v>140</v>
       </c>
       <c r="B72" t="s">
         <v>12</v>
       </c>
       <c r="C72" t="s">
-        <v>103</v>
+        <v>13</v>
       </c>
       <c r="D72" t="s">
         <v>93</v>
       </c>
       <c r="E72" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="F72" t="s">
         <v>29</v>
       </c>
       <c r="G72" t="s">
-        <v>94</v>
+        <v>191</v>
       </c>
       <c r="H72" t="s">
-        <v>46</v>
+        <v>24</v>
       </c>
       <c r="I72" t="s">
-        <v>116</v>
+        <v>192</v>
       </c>
       <c r="J72" t="s">
         <v>19</v>
@@ -3787,19 +3804,19 @@
     </row>
     <row r="73" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>17</v>
+        <v>63</v>
       </c>
       <c r="B73" t="s">
         <v>12</v>
       </c>
       <c r="C73" t="s">
-        <v>125</v>
+        <v>200</v>
       </c>
       <c r="D73" t="s">
         <v>93</v>
       </c>
       <c r="E73" t="s">
-        <v>123</v>
+        <v>15</v>
       </c>
       <c r="F73" t="s">
         <v>12</v>
@@ -3811,7 +3828,7 @@
         <v>54</v>
       </c>
       <c r="I73" t="s">
-        <v>139</v>
+        <v>206</v>
       </c>
       <c r="J73" t="s">
         <v>19</v>
@@ -3822,13 +3839,13 @@
     </row>
     <row r="74" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="B74" t="s">
         <v>12</v>
       </c>
       <c r="C74" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="D74" t="s">
         <v>93</v>
@@ -3840,13 +3857,13 @@
         <v>12</v>
       </c>
       <c r="G74" t="s">
-        <v>161</v>
+        <v>94</v>
       </c>
       <c r="H74" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="I74" t="s">
-        <v>170</v>
+        <v>139</v>
       </c>
       <c r="J74" t="s">
         <v>19</v>
@@ -3857,31 +3874,31 @@
     </row>
     <row r="75" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>140</v>
+        <v>11</v>
       </c>
       <c r="B75" t="s">
         <v>12</v>
       </c>
       <c r="C75" t="s">
-        <v>13</v>
+        <v>103</v>
       </c>
       <c r="D75" t="s">
         <v>93</v>
       </c>
       <c r="E75" t="s">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="F75" t="s">
         <v>29</v>
       </c>
       <c r="G75" t="s">
-        <v>191</v>
+        <v>94</v>
       </c>
       <c r="H75" t="s">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="I75" t="s">
-        <v>192</v>
+        <v>116</v>
       </c>
       <c r="J75" t="s">
         <v>19</v>
@@ -3892,31 +3909,31 @@
     </row>
     <row r="76" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>63</v>
+        <v>24</v>
       </c>
       <c r="B76" t="s">
         <v>12</v>
       </c>
       <c r="C76" t="s">
-        <v>200</v>
+        <v>122</v>
       </c>
       <c r="D76" t="s">
         <v>93</v>
       </c>
       <c r="E76" t="s">
-        <v>15</v>
+        <v>123</v>
       </c>
       <c r="F76" t="s">
         <v>12</v>
       </c>
       <c r="G76" t="s">
-        <v>94</v>
+        <v>161</v>
       </c>
       <c r="H76" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="I76" t="s">
-        <v>206</v>
+        <v>170</v>
       </c>
       <c r="J76" t="s">
         <v>19</v>
@@ -3925,7 +3942,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="77" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>12</v>
       </c>
@@ -3960,7 +3977,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="78" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>12</v>
       </c>
@@ -3995,7 +4012,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="79" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>12</v>
       </c>
@@ -4032,31 +4049,31 @@
     </row>
     <row r="80" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>121</v>
+        <v>29</v>
       </c>
       <c r="B80" t="s">
-        <v>63</v>
+        <v>12</v>
       </c>
       <c r="C80" t="s">
-        <v>145</v>
+        <v>30</v>
       </c>
       <c r="D80" t="s">
         <v>93</v>
       </c>
       <c r="E80" t="s">
-        <v>146</v>
+        <v>32</v>
       </c>
       <c r="F80" t="s">
-        <v>59</v>
+        <v>12</v>
       </c>
       <c r="G80" t="s">
-        <v>77</v>
+        <v>94</v>
       </c>
       <c r="H80" t="s">
-        <v>133</v>
+        <v>81</v>
       </c>
       <c r="I80" t="s">
-        <v>245</v>
+        <v>95</v>
       </c>
       <c r="J80" t="s">
         <v>19</v>
@@ -4065,7 +4082,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="81" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>12</v>
       </c>
@@ -4100,7 +4117,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="82" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>12</v>
       </c>
@@ -4135,7 +4152,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="83" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>11</v>
       </c>
@@ -4170,7 +4187,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="84" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>52</v>
       </c>
@@ -4207,31 +4224,31 @@
     </row>
     <row r="85" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>12</v>
+        <v>121</v>
       </c>
       <c r="B85" t="s">
-        <v>12</v>
+        <v>52</v>
       </c>
       <c r="C85" t="s">
-        <v>30</v>
+        <v>145</v>
       </c>
       <c r="D85" t="s">
         <v>90</v>
       </c>
       <c r="E85" t="s">
-        <v>32</v>
+        <v>146</v>
       </c>
       <c r="F85" t="s">
-        <v>12</v>
+        <v>52</v>
       </c>
       <c r="G85" t="s">
-        <v>91</v>
+        <v>77</v>
       </c>
       <c r="H85" t="s">
-        <v>34</v>
+        <v>133</v>
       </c>
       <c r="I85" t="s">
-        <v>92</v>
+        <v>244</v>
       </c>
       <c r="J85" t="s">
         <v>19</v>
@@ -4242,31 +4259,31 @@
     </row>
     <row r="86" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B86" t="s">
         <v>12</v>
       </c>
       <c r="C86" t="s">
-        <v>103</v>
+        <v>13</v>
       </c>
       <c r="D86" t="s">
         <v>90</v>
       </c>
       <c r="E86" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="F86" t="s">
         <v>12</v>
       </c>
       <c r="G86" t="s">
-        <v>91</v>
+        <v>168</v>
       </c>
       <c r="H86" t="s">
-        <v>105</v>
+        <v>27</v>
       </c>
       <c r="I86" t="s">
-        <v>115</v>
+        <v>190</v>
       </c>
       <c r="J86" t="s">
         <v>19</v>
@@ -4277,31 +4294,31 @@
     </row>
     <row r="87" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>11</v>
+        <v>59</v>
       </c>
       <c r="B87" t="s">
         <v>12</v>
       </c>
       <c r="C87" t="s">
-        <v>125</v>
+        <v>21</v>
       </c>
       <c r="D87" t="s">
         <v>90</v>
       </c>
       <c r="E87" t="s">
-        <v>123</v>
+        <v>15</v>
       </c>
       <c r="F87" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="G87" t="s">
         <v>91</v>
       </c>
       <c r="H87" t="s">
-        <v>46</v>
+        <v>27</v>
       </c>
       <c r="I87" t="s">
-        <v>138</v>
+        <v>205</v>
       </c>
       <c r="J87" t="s">
         <v>19</v>
@@ -4312,13 +4329,13 @@
     </row>
     <row r="88" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="B88" t="s">
         <v>12</v>
       </c>
       <c r="C88" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="D88" t="s">
         <v>90</v>
@@ -4330,13 +4347,13 @@
         <v>12</v>
       </c>
       <c r="G88" t="s">
-        <v>168</v>
+        <v>91</v>
       </c>
       <c r="H88" t="s">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="I88" t="s">
-        <v>169</v>
+        <v>138</v>
       </c>
       <c r="J88" t="s">
         <v>19</v>
@@ -4347,31 +4364,31 @@
     </row>
     <row r="89" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B89" t="s">
         <v>12</v>
       </c>
       <c r="C89" t="s">
-        <v>13</v>
+        <v>103</v>
       </c>
       <c r="D89" t="s">
         <v>90</v>
       </c>
       <c r="E89" t="s">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="F89" t="s">
         <v>12</v>
       </c>
       <c r="G89" t="s">
-        <v>168</v>
+        <v>91</v>
       </c>
       <c r="H89" t="s">
-        <v>27</v>
+        <v>105</v>
       </c>
       <c r="I89" t="s">
-        <v>190</v>
+        <v>115</v>
       </c>
       <c r="J89" t="s">
         <v>19</v>
@@ -4382,31 +4399,31 @@
     </row>
     <row r="90" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="B90" t="s">
         <v>12</v>
       </c>
       <c r="C90" t="s">
-        <v>21</v>
+        <v>122</v>
       </c>
       <c r="D90" t="s">
         <v>90</v>
       </c>
       <c r="E90" t="s">
-        <v>15</v>
+        <v>123</v>
       </c>
       <c r="F90" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="G90" t="s">
-        <v>91</v>
+        <v>168</v>
       </c>
       <c r="H90" t="s">
-        <v>27</v>
+        <v>65</v>
       </c>
       <c r="I90" t="s">
-        <v>205</v>
+        <v>169</v>
       </c>
       <c r="J90" t="s">
         <v>19</v>
@@ -4415,7 +4432,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="91" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>59</v>
       </c>
@@ -4450,7 +4467,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="92" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>29</v>
       </c>
@@ -4485,7 +4502,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="93" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>12</v>
       </c>
@@ -4522,31 +4539,31 @@
     </row>
     <row r="94" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>121</v>
+        <v>12</v>
       </c>
       <c r="B94" t="s">
-        <v>52</v>
+        <v>12</v>
       </c>
       <c r="C94" t="s">
-        <v>145</v>
+        <v>30</v>
       </c>
       <c r="D94" t="s">
         <v>90</v>
       </c>
       <c r="E94" t="s">
-        <v>146</v>
+        <v>32</v>
       </c>
       <c r="F94" t="s">
-        <v>52</v>
+        <v>12</v>
       </c>
       <c r="G94" t="s">
-        <v>77</v>
+        <v>91</v>
       </c>
       <c r="H94" t="s">
-        <v>133</v>
+        <v>34</v>
       </c>
       <c r="I94" t="s">
-        <v>244</v>
+        <v>92</v>
       </c>
       <c r="J94" t="s">
         <v>19</v>
@@ -4555,7 +4572,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="95" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>121</v>
       </c>
@@ -4590,7 +4607,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="96" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>12</v>
       </c>
@@ -4625,7 +4642,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="97" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>11</v>
       </c>
@@ -4660,7 +4677,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="98" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>24</v>
       </c>
@@ -4697,31 +4714,31 @@
     </row>
     <row r="99" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>59</v>
+        <v>24</v>
       </c>
       <c r="B99" t="s">
-        <v>12</v>
+        <v>63</v>
       </c>
       <c r="C99" t="s">
-        <v>30</v>
+        <v>145</v>
       </c>
       <c r="D99" t="s">
         <v>86</v>
       </c>
       <c r="E99" t="s">
-        <v>32</v>
+        <v>146</v>
       </c>
       <c r="F99" t="s">
-        <v>12</v>
+        <v>52</v>
       </c>
       <c r="G99" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="H99" t="s">
-        <v>88</v>
+        <v>119</v>
       </c>
       <c r="I99" t="s">
-        <v>89</v>
+        <v>243</v>
       </c>
       <c r="J99" t="s">
         <v>19</v>
@@ -4732,31 +4749,31 @@
     </row>
     <row r="100" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>29</v>
+        <v>140</v>
       </c>
       <c r="B100" t="s">
         <v>12</v>
       </c>
       <c r="C100" t="s">
-        <v>103</v>
+        <v>13</v>
       </c>
       <c r="D100" t="s">
         <v>86</v>
       </c>
       <c r="E100" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="F100" t="s">
         <v>12</v>
       </c>
       <c r="G100" t="s">
-        <v>87</v>
+        <v>166</v>
       </c>
       <c r="H100" t="s">
-        <v>105</v>
+        <v>24</v>
       </c>
       <c r="I100" t="s">
-        <v>114</v>
+        <v>189</v>
       </c>
       <c r="J100" t="s">
         <v>19</v>
@@ -4773,13 +4790,13 @@
         <v>12</v>
       </c>
       <c r="C101" t="s">
-        <v>125</v>
+        <v>21</v>
       </c>
       <c r="D101" t="s">
         <v>86</v>
       </c>
       <c r="E101" t="s">
-        <v>123</v>
+        <v>15</v>
       </c>
       <c r="F101" t="s">
         <v>12</v>
@@ -4788,10 +4805,10 @@
         <v>87</v>
       </c>
       <c r="H101" t="s">
-        <v>105</v>
+        <v>11</v>
       </c>
       <c r="I101" t="s">
-        <v>137</v>
+        <v>204</v>
       </c>
       <c r="J101" t="s">
         <v>19</v>
@@ -4802,13 +4819,13 @@
     </row>
     <row r="102" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>27</v>
+        <v>63</v>
       </c>
       <c r="B102" t="s">
         <v>12</v>
       </c>
       <c r="C102" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="D102" t="s">
         <v>86</v>
@@ -4820,13 +4837,13 @@
         <v>12</v>
       </c>
       <c r="G102" t="s">
-        <v>166</v>
+        <v>87</v>
       </c>
       <c r="H102" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="I102" t="s">
-        <v>167</v>
+        <v>137</v>
       </c>
       <c r="J102" t="s">
         <v>19</v>
@@ -4837,31 +4854,31 @@
     </row>
     <row r="103" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>140</v>
+        <v>29</v>
       </c>
       <c r="B103" t="s">
         <v>12</v>
       </c>
       <c r="C103" t="s">
-        <v>13</v>
+        <v>103</v>
       </c>
       <c r="D103" t="s">
         <v>86</v>
       </c>
       <c r="E103" t="s">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="F103" t="s">
         <v>12</v>
       </c>
       <c r="G103" t="s">
-        <v>166</v>
+        <v>87</v>
       </c>
       <c r="H103" t="s">
-        <v>24</v>
+        <v>105</v>
       </c>
       <c r="I103" t="s">
-        <v>189</v>
+        <v>114</v>
       </c>
       <c r="J103" t="s">
         <v>19</v>
@@ -4872,31 +4889,31 @@
     </row>
     <row r="104" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>63</v>
+        <v>27</v>
       </c>
       <c r="B104" t="s">
         <v>12</v>
       </c>
       <c r="C104" t="s">
-        <v>21</v>
+        <v>122</v>
       </c>
       <c r="D104" t="s">
         <v>86</v>
       </c>
       <c r="E104" t="s">
-        <v>15</v>
+        <v>123</v>
       </c>
       <c r="F104" t="s">
         <v>12</v>
       </c>
       <c r="G104" t="s">
-        <v>87</v>
+        <v>166</v>
       </c>
       <c r="H104" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
       <c r="I104" t="s">
-        <v>204</v>
+        <v>167</v>
       </c>
       <c r="J104" t="s">
         <v>19</v>
@@ -4907,31 +4924,31 @@
     </row>
     <row r="105" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>24</v>
+        <v>59</v>
       </c>
       <c r="B105" t="s">
-        <v>63</v>
+        <v>12</v>
       </c>
       <c r="C105" t="s">
-        <v>145</v>
+        <v>30</v>
       </c>
       <c r="D105" t="s">
         <v>86</v>
       </c>
       <c r="E105" t="s">
-        <v>146</v>
+        <v>32</v>
       </c>
       <c r="F105" t="s">
-        <v>52</v>
+        <v>12</v>
       </c>
       <c r="G105" t="s">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="H105" t="s">
-        <v>119</v>
+        <v>88</v>
       </c>
       <c r="I105" t="s">
-        <v>243</v>
+        <v>89</v>
       </c>
       <c r="J105" t="s">
         <v>19</v>
@@ -4940,7 +4957,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="106" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>59</v>
       </c>
@@ -4975,7 +4992,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="107" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>52</v>
       </c>
@@ -5010,7 +5027,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="108" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>38</v>
       </c>
@@ -5045,7 +5062,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="109" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>12</v>
       </c>
@@ -5080,7 +5097,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="110" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>38</v>
       </c>
@@ -5115,7 +5132,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="111" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>20</v>
       </c>
@@ -5150,7 +5167,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="112" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>27</v>
       </c>
@@ -5187,31 +5204,31 @@
     </row>
     <row r="113" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="B113" t="s">
-        <v>12</v>
+        <v>52</v>
       </c>
       <c r="C113" t="s">
-        <v>30</v>
+        <v>145</v>
       </c>
       <c r="D113" t="s">
         <v>83</v>
       </c>
       <c r="E113" t="s">
-        <v>32</v>
+        <v>146</v>
       </c>
       <c r="F113" t="s">
-        <v>12</v>
+        <v>52</v>
       </c>
       <c r="G113" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="H113" t="s">
-        <v>81</v>
+        <v>193</v>
       </c>
       <c r="I113" t="s">
-        <v>85</v>
+        <v>242</v>
       </c>
       <c r="J113" t="s">
         <v>19</v>
@@ -5222,31 +5239,31 @@
     </row>
     <row r="114" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>12</v>
+        <v>63</v>
       </c>
       <c r="B114" t="s">
         <v>12</v>
       </c>
       <c r="C114" t="s">
-        <v>103</v>
+        <v>13</v>
       </c>
       <c r="D114" t="s">
         <v>83</v>
       </c>
       <c r="E114" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="F114" t="s">
-        <v>12</v>
+        <v>52</v>
       </c>
       <c r="G114" t="s">
-        <v>112</v>
+        <v>164</v>
       </c>
       <c r="H114" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="I114" t="s">
-        <v>113</v>
+        <v>188</v>
       </c>
       <c r="J114" t="s">
         <v>19</v>
@@ -5257,31 +5274,31 @@
     </row>
     <row r="115" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="B115" t="s">
         <v>12</v>
       </c>
       <c r="C115" t="s">
-        <v>125</v>
+        <v>21</v>
       </c>
       <c r="D115" t="s">
         <v>83</v>
       </c>
       <c r="E115" t="s">
-        <v>123</v>
+        <v>15</v>
       </c>
       <c r="F115" t="s">
-        <v>29</v>
+        <v>52</v>
       </c>
       <c r="G115" t="s">
         <v>135</v>
       </c>
       <c r="H115" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="I115" t="s">
-        <v>136</v>
+        <v>203</v>
       </c>
       <c r="J115" t="s">
         <v>19</v>
@@ -5292,13 +5309,13 @@
     </row>
     <row r="116" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="B116" t="s">
         <v>12</v>
       </c>
       <c r="C116" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="D116" t="s">
         <v>83</v>
@@ -5307,16 +5324,16 @@
         <v>123</v>
       </c>
       <c r="F116" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="G116" t="s">
-        <v>164</v>
+        <v>135</v>
       </c>
       <c r="H116" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="I116" t="s">
-        <v>165</v>
+        <v>136</v>
       </c>
       <c r="J116" t="s">
         <v>19</v>
@@ -5327,31 +5344,31 @@
     </row>
     <row r="117" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>63</v>
+        <v>12</v>
       </c>
       <c r="B117" t="s">
         <v>12</v>
       </c>
       <c r="C117" t="s">
-        <v>13</v>
+        <v>103</v>
       </c>
       <c r="D117" t="s">
         <v>83</v>
       </c>
       <c r="E117" t="s">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="F117" t="s">
-        <v>52</v>
+        <v>12</v>
       </c>
       <c r="G117" t="s">
-        <v>164</v>
+        <v>112</v>
       </c>
       <c r="H117" t="s">
-        <v>54</v>
+        <v>65</v>
       </c>
       <c r="I117" t="s">
-        <v>188</v>
+        <v>113</v>
       </c>
       <c r="J117" t="s">
         <v>19</v>
@@ -5362,31 +5379,31 @@
     </row>
     <row r="118" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="B118" t="s">
         <v>12</v>
       </c>
       <c r="C118" t="s">
-        <v>21</v>
+        <v>122</v>
       </c>
       <c r="D118" t="s">
         <v>83</v>
       </c>
       <c r="E118" t="s">
-        <v>15</v>
+        <v>123</v>
       </c>
       <c r="F118" t="s">
-        <v>52</v>
+        <v>12</v>
       </c>
       <c r="G118" t="s">
-        <v>135</v>
+        <v>164</v>
       </c>
       <c r="H118" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="I118" t="s">
-        <v>203</v>
+        <v>165</v>
       </c>
       <c r="J118" t="s">
         <v>19</v>
@@ -5397,31 +5414,31 @@
     </row>
     <row r="119" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="B119" t="s">
-        <v>52</v>
+        <v>12</v>
       </c>
       <c r="C119" t="s">
-        <v>145</v>
+        <v>30</v>
       </c>
       <c r="D119" t="s">
         <v>83</v>
       </c>
       <c r="E119" t="s">
-        <v>146</v>
+        <v>32</v>
       </c>
       <c r="F119" t="s">
-        <v>52</v>
+        <v>12</v>
       </c>
       <c r="G119" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H119" t="s">
-        <v>193</v>
+        <v>81</v>
       </c>
       <c r="I119" t="s">
-        <v>242</v>
+        <v>85</v>
       </c>
       <c r="J119" t="s">
         <v>19</v>
@@ -5430,7 +5447,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="120" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>59</v>
       </c>
@@ -5465,7 +5482,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="121" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>63</v>
       </c>
@@ -5500,7 +5517,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="122" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>121</v>
       </c>
@@ -5535,7 +5552,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="123" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>12</v>
       </c>
@@ -5570,7 +5587,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="124" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>59</v>
       </c>
@@ -5605,7 +5622,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="125" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>59</v>
       </c>
@@ -5640,7 +5657,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="126" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>12</v>
       </c>
@@ -5677,31 +5694,31 @@
     </row>
     <row r="127" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="B127" t="s">
-        <v>12</v>
+        <v>63</v>
       </c>
       <c r="C127" t="s">
-        <v>30</v>
+        <v>145</v>
       </c>
       <c r="D127" t="s">
         <v>79</v>
       </c>
       <c r="E127" t="s">
-        <v>32</v>
+        <v>146</v>
       </c>
       <c r="F127" t="s">
-        <v>12</v>
+        <v>52</v>
       </c>
       <c r="G127" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="H127" t="s">
-        <v>81</v>
+        <v>193</v>
       </c>
       <c r="I127" t="s">
-        <v>82</v>
+        <v>241</v>
       </c>
       <c r="J127" t="s">
         <v>19</v>
@@ -5712,31 +5729,31 @@
     </row>
     <row r="128" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>12</v>
+        <v>52</v>
       </c>
       <c r="B128" t="s">
         <v>12</v>
       </c>
       <c r="C128" t="s">
-        <v>103</v>
+        <v>13</v>
       </c>
       <c r="D128" t="s">
         <v>79</v>
       </c>
       <c r="E128" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="F128" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="G128" t="s">
-        <v>80</v>
+        <v>161</v>
       </c>
       <c r="H128" t="s">
-        <v>65</v>
+        <v>41</v>
       </c>
       <c r="I128" t="s">
-        <v>111</v>
+        <v>187</v>
       </c>
       <c r="J128" t="s">
         <v>19</v>
@@ -5747,31 +5764,31 @@
     </row>
     <row r="129" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>121</v>
+        <v>63</v>
       </c>
       <c r="B129" t="s">
         <v>12</v>
       </c>
       <c r="C129" t="s">
-        <v>125</v>
+        <v>21</v>
       </c>
       <c r="D129" t="s">
         <v>79</v>
       </c>
       <c r="E129" t="s">
-        <v>123</v>
+        <v>15</v>
       </c>
       <c r="F129" t="s">
         <v>12</v>
       </c>
       <c r="G129" t="s">
-        <v>132</v>
+        <v>80</v>
       </c>
       <c r="H129" t="s">
-        <v>133</v>
+        <v>24</v>
       </c>
       <c r="I129" t="s">
-        <v>134</v>
+        <v>202</v>
       </c>
       <c r="J129" t="s">
         <v>19</v>
@@ -5782,13 +5799,13 @@
     </row>
     <row r="130" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>24</v>
+        <v>121</v>
       </c>
       <c r="B130" t="s">
         <v>12</v>
       </c>
       <c r="C130" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="D130" t="s">
         <v>79</v>
@@ -5800,13 +5817,13 @@
         <v>12</v>
       </c>
       <c r="G130" t="s">
-        <v>161</v>
+        <v>132</v>
       </c>
       <c r="H130" t="s">
-        <v>162</v>
+        <v>133</v>
       </c>
       <c r="I130" t="s">
-        <v>163</v>
+        <v>134</v>
       </c>
       <c r="J130" t="s">
         <v>19</v>
@@ -5817,31 +5834,31 @@
     </row>
     <row r="131" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>52</v>
+        <v>12</v>
       </c>
       <c r="B131" t="s">
         <v>12</v>
       </c>
       <c r="C131" t="s">
-        <v>13</v>
+        <v>103</v>
       </c>
       <c r="D131" t="s">
         <v>79</v>
       </c>
       <c r="E131" t="s">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="F131" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="G131" t="s">
-        <v>161</v>
+        <v>80</v>
       </c>
       <c r="H131" t="s">
-        <v>41</v>
+        <v>65</v>
       </c>
       <c r="I131" t="s">
-        <v>187</v>
+        <v>111</v>
       </c>
       <c r="J131" t="s">
         <v>19</v>
@@ -5852,31 +5869,31 @@
     </row>
     <row r="132" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>63</v>
+        <v>24</v>
       </c>
       <c r="B132" t="s">
         <v>12</v>
       </c>
       <c r="C132" t="s">
-        <v>21</v>
+        <v>122</v>
       </c>
       <c r="D132" t="s">
         <v>79</v>
       </c>
       <c r="E132" t="s">
-        <v>15</v>
+        <v>123</v>
       </c>
       <c r="F132" t="s">
         <v>12</v>
       </c>
       <c r="G132" t="s">
-        <v>80</v>
+        <v>161</v>
       </c>
       <c r="H132" t="s">
-        <v>24</v>
+        <v>162</v>
       </c>
       <c r="I132" t="s">
-        <v>202</v>
+        <v>163</v>
       </c>
       <c r="J132" t="s">
         <v>19</v>
@@ -5885,7 +5902,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="133" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>38</v>
       </c>
@@ -5922,31 +5939,31 @@
     </row>
     <row r="134" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="B134" t="s">
-        <v>63</v>
+        <v>12</v>
       </c>
       <c r="C134" t="s">
-        <v>145</v>
+        <v>30</v>
       </c>
       <c r="D134" t="s">
         <v>79</v>
       </c>
       <c r="E134" t="s">
-        <v>146</v>
+        <v>32</v>
       </c>
       <c r="F134" t="s">
-        <v>52</v>
+        <v>12</v>
       </c>
       <c r="G134" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="H134" t="s">
-        <v>193</v>
+        <v>81</v>
       </c>
       <c r="I134" t="s">
-        <v>241</v>
+        <v>82</v>
       </c>
       <c r="J134" t="s">
         <v>19</v>
@@ -5955,7 +5972,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="135" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>12</v>
       </c>
@@ -5990,7 +6007,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="136" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>63</v>
       </c>
@@ -6025,7 +6042,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="137" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>52</v>
       </c>
@@ -6060,7 +6077,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="138" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>29</v>
       </c>
@@ -6095,7 +6112,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="139" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>12</v>
       </c>
@@ -6130,7 +6147,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="140" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>59</v>
       </c>
@@ -6167,31 +6184,31 @@
     </row>
     <row r="141" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>12</v>
+        <v>121</v>
       </c>
       <c r="B141" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="C141" t="s">
-        <v>30</v>
+        <v>145</v>
       </c>
       <c r="D141" t="s">
         <v>76</v>
       </c>
       <c r="E141" t="s">
-        <v>32</v>
+        <v>146</v>
       </c>
       <c r="F141" t="s">
-        <v>12</v>
+        <v>59</v>
       </c>
       <c r="G141" t="s">
         <v>77</v>
       </c>
       <c r="H141" t="s">
-        <v>72</v>
+        <v>108</v>
       </c>
       <c r="I141" t="s">
-        <v>78</v>
+        <v>240</v>
       </c>
       <c r="J141" t="s">
         <v>19</v>
@@ -6202,31 +6219,31 @@
     </row>
     <row r="142" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>12</v>
+        <v>63</v>
       </c>
       <c r="B142" t="s">
         <v>12</v>
       </c>
       <c r="C142" t="s">
-        <v>103</v>
+        <v>13</v>
       </c>
       <c r="D142" t="s">
         <v>76</v>
       </c>
       <c r="E142" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="F142" t="s">
         <v>12</v>
       </c>
       <c r="G142" t="s">
-        <v>77</v>
+        <v>159</v>
       </c>
       <c r="H142" t="s">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="I142" t="s">
-        <v>110</v>
+        <v>186</v>
       </c>
       <c r="J142" t="s">
         <v>19</v>
@@ -6237,19 +6254,19 @@
     </row>
     <row r="143" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="B143" t="s">
         <v>12</v>
       </c>
       <c r="C143" t="s">
-        <v>125</v>
+        <v>200</v>
       </c>
       <c r="D143" t="s">
         <v>76</v>
       </c>
       <c r="E143" t="s">
-        <v>123</v>
+        <v>15</v>
       </c>
       <c r="F143" t="s">
         <v>12</v>
@@ -6258,10 +6275,10 @@
         <v>77</v>
       </c>
       <c r="H143" t="s">
-        <v>61</v>
+        <v>140</v>
       </c>
       <c r="I143" t="s">
-        <v>131</v>
+        <v>201</v>
       </c>
       <c r="J143" t="s">
         <v>19</v>
@@ -6272,13 +6289,13 @@
     </row>
     <row r="144" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>27</v>
+        <v>59</v>
       </c>
       <c r="B144" t="s">
         <v>12</v>
       </c>
       <c r="C144" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="D144" t="s">
         <v>76</v>
@@ -6290,13 +6307,13 @@
         <v>12</v>
       </c>
       <c r="G144" t="s">
-        <v>159</v>
+        <v>77</v>
       </c>
       <c r="H144" t="s">
-        <v>105</v>
+        <v>61</v>
       </c>
       <c r="I144" t="s">
-        <v>160</v>
+        <v>131</v>
       </c>
       <c r="J144" t="s">
         <v>19</v>
@@ -6307,31 +6324,31 @@
     </row>
     <row r="145" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>63</v>
+        <v>12</v>
       </c>
       <c r="B145" t="s">
         <v>12</v>
       </c>
       <c r="C145" t="s">
-        <v>13</v>
+        <v>103</v>
       </c>
       <c r="D145" t="s">
         <v>76</v>
       </c>
       <c r="E145" t="s">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="F145" t="s">
         <v>12</v>
       </c>
       <c r="G145" t="s">
-        <v>159</v>
+        <v>77</v>
       </c>
       <c r="H145" t="s">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="I145" t="s">
-        <v>186</v>
+        <v>110</v>
       </c>
       <c r="J145" t="s">
         <v>19</v>
@@ -6342,31 +6359,31 @@
     </row>
     <row r="146" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>52</v>
+        <v>27</v>
       </c>
       <c r="B146" t="s">
         <v>12</v>
       </c>
       <c r="C146" t="s">
-        <v>200</v>
+        <v>122</v>
       </c>
       <c r="D146" t="s">
         <v>76</v>
       </c>
       <c r="E146" t="s">
-        <v>15</v>
+        <v>123</v>
       </c>
       <c r="F146" t="s">
         <v>12</v>
       </c>
       <c r="G146" t="s">
-        <v>77</v>
+        <v>159</v>
       </c>
       <c r="H146" t="s">
-        <v>140</v>
+        <v>105</v>
       </c>
       <c r="I146" t="s">
-        <v>201</v>
+        <v>160</v>
       </c>
       <c r="J146" t="s">
         <v>19</v>
@@ -6375,7 +6392,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="147" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>59</v>
       </c>
@@ -6412,31 +6429,31 @@
     </row>
     <row r="148" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>121</v>
+        <v>12</v>
       </c>
       <c r="B148" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="C148" t="s">
-        <v>145</v>
+        <v>30</v>
       </c>
       <c r="D148" t="s">
         <v>76</v>
       </c>
       <c r="E148" t="s">
-        <v>146</v>
+        <v>32</v>
       </c>
       <c r="F148" t="s">
-        <v>59</v>
+        <v>12</v>
       </c>
       <c r="G148" t="s">
         <v>77</v>
       </c>
       <c r="H148" t="s">
-        <v>108</v>
+        <v>72</v>
       </c>
       <c r="I148" t="s">
-        <v>240</v>
+        <v>78</v>
       </c>
       <c r="J148" t="s">
         <v>19</v>
@@ -6445,7 +6462,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="149" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>29</v>
       </c>
@@ -6480,7 +6497,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="150" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>12</v>
       </c>
@@ -6515,7 +6532,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="151" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>12</v>
       </c>
@@ -6550,7 +6567,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="152" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>27</v>
       </c>
@@ -6585,7 +6602,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="153" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>12</v>
       </c>
@@ -6620,7 +6637,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="154" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>63</v>
       </c>
@@ -6657,31 +6674,31 @@
     </row>
     <row r="155" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>11</v>
+        <v>41</v>
       </c>
       <c r="B155" t="s">
         <v>12</v>
       </c>
       <c r="C155" t="s">
-        <v>13</v>
+        <v>145</v>
       </c>
       <c r="D155" t="s">
         <v>14</v>
       </c>
       <c r="E155" t="s">
-        <v>15</v>
+        <v>146</v>
       </c>
       <c r="F155" t="s">
         <v>12</v>
       </c>
       <c r="G155" t="s">
-        <v>16</v>
+        <v>68</v>
       </c>
       <c r="H155" t="s">
-        <v>17</v>
+        <v>69</v>
       </c>
       <c r="I155" t="s">
-        <v>18</v>
+        <v>149</v>
       </c>
       <c r="J155" t="s">
         <v>19</v>
@@ -6692,13 +6709,13 @@
     </row>
     <row r="156" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="B156" t="s">
         <v>12</v>
       </c>
       <c r="C156" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="D156" t="s">
         <v>14</v>
@@ -6710,13 +6727,13 @@
         <v>12</v>
       </c>
       <c r="G156" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="H156" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="I156" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="J156" t="s">
         <v>19</v>
@@ -6727,31 +6744,31 @@
     </row>
     <row r="157" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>12</v>
+        <v>52</v>
       </c>
       <c r="B157" t="s">
         <v>12</v>
       </c>
       <c r="C157" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="D157" t="s">
         <v>14</v>
       </c>
       <c r="E157" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="F157" t="s">
         <v>12</v>
       </c>
       <c r="G157" t="s">
-        <v>74</v>
+        <v>157</v>
       </c>
       <c r="H157" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="I157" t="s">
-        <v>75</v>
+        <v>185</v>
       </c>
       <c r="J157" t="s">
         <v>19</v>
@@ -6762,31 +6779,31 @@
     </row>
     <row r="158" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>63</v>
+        <v>20</v>
       </c>
       <c r="B158" t="s">
         <v>12</v>
       </c>
       <c r="C158" t="s">
-        <v>103</v>
+        <v>21</v>
       </c>
       <c r="D158" t="s">
         <v>14</v>
       </c>
       <c r="E158" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="F158" t="s">
         <v>12</v>
       </c>
       <c r="G158" t="s">
-        <v>74</v>
+        <v>26</v>
       </c>
       <c r="H158" t="s">
-        <v>108</v>
+        <v>27</v>
       </c>
       <c r="I158" t="s">
-        <v>109</v>
+        <v>28</v>
       </c>
       <c r="J158" t="s">
         <v>19</v>
@@ -6797,66 +6814,66 @@
     </row>
     <row r="159" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>54</v>
+        <v>24</v>
       </c>
       <c r="B159" t="s">
-        <v>12</v>
+        <v>52</v>
       </c>
       <c r="C159" t="s">
-        <v>125</v>
+        <v>21</v>
       </c>
       <c r="D159" t="s">
         <v>14</v>
       </c>
       <c r="E159" t="s">
-        <v>123</v>
+        <v>15</v>
       </c>
       <c r="F159" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="G159" t="s">
         <v>74</v>
       </c>
       <c r="H159" t="s">
-        <v>121</v>
+        <v>29</v>
       </c>
       <c r="I159" t="s">
-        <v>130</v>
+        <v>199</v>
       </c>
       <c r="J159" t="s">
         <v>19</v>
       </c>
       <c r="K159" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
     </row>
     <row r="160" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="B160" t="s">
         <v>12</v>
       </c>
       <c r="C160" t="s">
-        <v>145</v>
+        <v>125</v>
       </c>
       <c r="D160" t="s">
         <v>14</v>
       </c>
       <c r="E160" t="s">
-        <v>146</v>
+        <v>123</v>
       </c>
       <c r="F160" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="G160" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="H160" t="s">
-        <v>69</v>
+        <v>121</v>
       </c>
       <c r="I160" t="s">
-        <v>149</v>
+        <v>130</v>
       </c>
       <c r="J160" t="s">
         <v>19</v>
@@ -6867,31 +6884,31 @@
     </row>
     <row r="161" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>38</v>
+        <v>63</v>
       </c>
       <c r="B161" t="s">
         <v>12</v>
       </c>
       <c r="C161" t="s">
-        <v>122</v>
+        <v>103</v>
       </c>
       <c r="D161" t="s">
         <v>14</v>
       </c>
       <c r="E161" t="s">
-        <v>123</v>
+        <v>32</v>
       </c>
       <c r="F161" t="s">
         <v>12</v>
       </c>
       <c r="G161" t="s">
-        <v>157</v>
+        <v>74</v>
       </c>
       <c r="H161" t="s">
         <v>108</v>
       </c>
       <c r="I161" t="s">
-        <v>158</v>
+        <v>109</v>
       </c>
       <c r="J161" t="s">
         <v>19</v>
@@ -6900,7 +6917,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="162" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
         <v>12</v>
       </c>
@@ -6937,19 +6954,19 @@
     </row>
     <row r="163" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="B163" t="s">
         <v>12</v>
       </c>
       <c r="C163" t="s">
-        <v>13</v>
+        <v>122</v>
       </c>
       <c r="D163" t="s">
         <v>14</v>
       </c>
       <c r="E163" t="s">
-        <v>15</v>
+        <v>123</v>
       </c>
       <c r="F163" t="s">
         <v>12</v>
@@ -6958,10 +6975,10 @@
         <v>157</v>
       </c>
       <c r="H163" t="s">
-        <v>41</v>
+        <v>108</v>
       </c>
       <c r="I163" t="s">
-        <v>185</v>
+        <v>158</v>
       </c>
       <c r="J163" t="s">
         <v>19</v>
@@ -6972,19 +6989,19 @@
     </row>
     <row r="164" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="B164" t="s">
-        <v>52</v>
+        <v>12</v>
       </c>
       <c r="C164" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="D164" t="s">
         <v>14</v>
       </c>
       <c r="E164" t="s">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="F164" t="s">
         <v>12</v>
@@ -6993,19 +7010,19 @@
         <v>74</v>
       </c>
       <c r="H164" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="I164" t="s">
-        <v>199</v>
+        <v>75</v>
       </c>
       <c r="J164" t="s">
         <v>19</v>
       </c>
       <c r="K164" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="165" spans="1:11" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="165" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
         <v>12</v>
       </c>
@@ -7040,7 +7057,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="166" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
         <v>38</v>
       </c>
@@ -7075,7 +7092,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="167" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
         <v>38</v>
       </c>
@@ -7110,7 +7127,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="168" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
         <v>12</v>
       </c>
@@ -7145,7 +7162,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="169" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
         <v>12</v>
       </c>
@@ -7180,7 +7197,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="170" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
         <v>59</v>
       </c>
@@ -7216,6 +7233,16 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:K170" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="9">
+      <filters>
+        <filter val="Nacala Porto"/>
+      </filters>
+    </filterColumn>
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K164">
+      <sortCondition ref="D1:D170"/>
+    </sortState>
+  </autoFilter>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K170">
     <sortCondition ref="D1:D170"/>
   </sortState>
@@ -7224,26 +7251,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="54c5ab46-7543-4aba-b0fa-79d6a199bef5" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="20d57abc-823c-4051-a81a-1a0a01a8f39e">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100DC8BB5B596CFDD4794B3344F0E8F53A4" ma:contentTypeVersion="15" ma:contentTypeDescription="Criar um novo documento." ma:contentTypeScope="" ma:versionID="9a7078cd21229583650f2264465a1c40">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="20d57abc-823c-4051-a81a-1a0a01a8f39e" xmlns:ns3="54c5ab46-7543-4aba-b0fa-79d6a199bef5" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4e45437c47114f519c494620e3e4bb67" ns2:_="" ns3:_="">
     <xsd:import namespace="20d57abc-823c-4051-a81a-1a0a01a8f39e"/>
@@ -7478,10 +7485,41 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="54c5ab46-7543-4aba-b0fa-79d6a199bef5" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="20d57abc-823c-4051-a81a-1a0a01a8f39e">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FB788E5D-2D79-4363-AF59-D9AE6FBE16C9}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{03C74B1E-6305-431E-B65A-AECD2878EEED}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="20d57abc-823c-4051-a81a-1a0a01a8f39e"/>
+    <ds:schemaRef ds:uri="54c5ab46-7543-4aba-b0fa-79d6a199bef5"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -7498,20 +7536,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{03C74B1E-6305-431E-B65A-AECD2878EEED}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FB788E5D-2D79-4363-AF59-D9AE6FBE16C9}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="20d57abc-823c-4051-a81a-1a0a01a8f39e"/>
-    <ds:schemaRef ds:uri="54c5ab46-7543-4aba-b0fa-79d6a199bef5"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/Qualidade_Sessoes.xlsx
+++ b/Qualidade_Sessoes.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://muvamozorg.sharepoint.com/sites/mis.drive/Documentos Partilhados/PROJECTOS/Sistema de Monitoria/NEXUS/2026/Dash_Nexus/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="24" documentId="11_CA7BA6727B39BFF18534DF48238D9D3350433DF5" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DFC1A8FF-40A2-44C2-8C92-D808AB483225}"/>
+  <xr:revisionPtr revIDLastSave="64" documentId="11_CA7BA6727B39BFF18534DF48238D9D3350433DF5" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AD36DF6E-E969-4223-812D-D8DAAADDF790}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1271,5979 +1271,5982 @@
   <dimension ref="A1:K170"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="39.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="38.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="18.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="38.42578125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="42.28515625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="46.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="46.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="39.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="42.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="39.85546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="46.5703125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="46.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>144</v>
+        <v>19</v>
       </c>
       <c r="B2" t="s">
-        <v>20</v>
+        <v>145</v>
       </c>
       <c r="C2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D2" t="s">
         <v>118</v>
       </c>
       <c r="E2" t="s">
-        <v>146</v>
+        <v>12</v>
       </c>
       <c r="F2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G2" t="s">
         <v>38</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
+        <v>144</v>
+      </c>
+      <c r="I2" t="s">
+        <v>101</v>
+      </c>
+      <c r="J2" t="s">
         <v>77</v>
       </c>
-      <c r="H2" t="s">
-        <v>101</v>
-      </c>
-      <c r="I2" t="s">
+      <c r="K2" t="s">
         <v>247</v>
       </c>
-      <c r="J2" t="s">
-        <v>19</v>
-      </c>
-      <c r="K2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D3" t="s">
         <v>118</v>
       </c>
       <c r="E3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G3" t="s">
+        <v>12</v>
+      </c>
+      <c r="H3" t="s">
+        <v>20</v>
+      </c>
+      <c r="I3" t="s">
+        <v>121</v>
+      </c>
+      <c r="J3" t="s">
+        <v>173</v>
+      </c>
+      <c r="K3" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4" t="s">
         <v>15</v>
-      </c>
-      <c r="F3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G3" t="s">
-        <v>173</v>
-      </c>
-      <c r="H3" t="s">
-        <v>121</v>
-      </c>
-      <c r="I3" t="s">
-        <v>195</v>
-      </c>
-      <c r="J3" t="s">
-        <v>19</v>
-      </c>
-      <c r="K3" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4" t="s">
-        <v>52</v>
-      </c>
-      <c r="C4" t="s">
-        <v>21</v>
       </c>
       <c r="D4" t="s">
         <v>118</v>
       </c>
       <c r="E4" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F4" t="s">
+        <v>52</v>
+      </c>
+      <c r="G4" t="s">
         <v>38</v>
       </c>
-      <c r="G4" t="s">
+      <c r="H4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I4" t="s">
+        <v>20</v>
+      </c>
+      <c r="J4" t="s">
         <v>100</v>
       </c>
-      <c r="H4" t="s">
-        <v>20</v>
-      </c>
-      <c r="I4" t="s">
+      <c r="K4" t="s">
         <v>208</v>
       </c>
-      <c r="J4" t="s">
-        <v>19</v>
-      </c>
-      <c r="K4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="5" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="B5" t="s">
-        <v>12</v>
+        <v>125</v>
       </c>
       <c r="C5" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="D5" t="s">
         <v>118</v>
       </c>
       <c r="E5" t="s">
-        <v>123</v>
+        <v>12</v>
       </c>
       <c r="F5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G5" t="s">
         <v>52</v>
       </c>
-      <c r="G5" t="s">
+      <c r="H5" t="s">
+        <v>27</v>
+      </c>
+      <c r="I5" t="s">
+        <v>133</v>
+      </c>
+      <c r="J5" t="s">
         <v>100</v>
       </c>
-      <c r="H5" t="s">
-        <v>133</v>
-      </c>
-      <c r="I5" t="s">
+      <c r="K5" t="s">
         <v>142</v>
       </c>
-      <c r="J5" t="s">
-        <v>19</v>
-      </c>
-      <c r="K5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="6" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B6" t="s">
-        <v>12</v>
+        <v>103</v>
       </c>
       <c r="C6" t="s">
-        <v>103</v>
+        <v>32</v>
       </c>
       <c r="D6" t="s">
         <v>118</v>
       </c>
       <c r="E6" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="F6" t="s">
+        <v>12</v>
+      </c>
+      <c r="G6" t="s">
         <v>29</v>
       </c>
-      <c r="G6" t="s">
+      <c r="H6" t="s">
+        <v>20</v>
+      </c>
+      <c r="I6" t="s">
+        <v>119</v>
+      </c>
+      <c r="J6" t="s">
         <v>100</v>
       </c>
-      <c r="H6" t="s">
-        <v>119</v>
-      </c>
-      <c r="I6" t="s">
+      <c r="K6" t="s">
         <v>120</v>
-      </c>
-      <c r="J6" t="s">
-        <v>19</v>
-      </c>
-      <c r="K6" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>193</v>
+        <v>43</v>
       </c>
       <c r="B7" t="s">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="C7" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D7" t="s">
         <v>118</v>
       </c>
       <c r="E7" t="s">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="F7" t="s">
         <v>12</v>
       </c>
       <c r="G7" t="s">
+        <v>12</v>
+      </c>
+      <c r="H7" t="s">
+        <v>193</v>
+      </c>
+      <c r="I7" t="s">
+        <v>52</v>
+      </c>
+      <c r="J7" t="s">
         <v>217</v>
       </c>
-      <c r="H7" t="s">
-        <v>52</v>
-      </c>
-      <c r="I7" t="s">
+      <c r="K7" t="s">
         <v>218</v>
-      </c>
-      <c r="J7" t="s">
-        <v>43</v>
-      </c>
-      <c r="K7" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>63</v>
+        <v>43</v>
       </c>
       <c r="B8" t="s">
-        <v>12</v>
+        <v>60</v>
       </c>
       <c r="C8" t="s">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="D8" t="s">
         <v>118</v>
       </c>
       <c r="E8" t="s">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="F8" t="s">
         <v>12</v>
       </c>
       <c r="G8" t="s">
+        <v>12</v>
+      </c>
+      <c r="H8" t="s">
+        <v>63</v>
+      </c>
+      <c r="I8" t="s">
+        <v>133</v>
+      </c>
+      <c r="J8" t="s">
         <v>222</v>
       </c>
-      <c r="H8" t="s">
-        <v>133</v>
-      </c>
-      <c r="I8" t="s">
+      <c r="K8" t="s">
         <v>223</v>
-      </c>
-      <c r="J8" t="s">
-        <v>43</v>
-      </c>
-      <c r="K8" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="9" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="B9" t="s">
-        <v>12</v>
+        <v>60</v>
       </c>
       <c r="C9" t="s">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="D9" t="s">
         <v>118</v>
       </c>
       <c r="E9" t="s">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="F9" t="s">
         <v>12</v>
       </c>
       <c r="G9" t="s">
+        <v>12</v>
+      </c>
+      <c r="H9" t="s">
+        <v>52</v>
+      </c>
+      <c r="I9" t="s">
+        <v>65</v>
+      </c>
+      <c r="J9" t="s">
         <v>222</v>
       </c>
-      <c r="H9" t="s">
-        <v>65</v>
-      </c>
-      <c r="I9" t="s">
+      <c r="K9" t="s">
         <v>229</v>
       </c>
-      <c r="J9" t="s">
-        <v>43</v>
-      </c>
-      <c r="K9" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>101</v>
+        <v>43</v>
       </c>
       <c r="B10" t="s">
-        <v>12</v>
+        <v>44</v>
       </c>
       <c r="C10" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D10" t="s">
         <v>118</v>
       </c>
       <c r="E10" t="s">
-        <v>45</v>
+        <v>12</v>
       </c>
       <c r="F10" t="s">
         <v>12</v>
       </c>
       <c r="G10" t="s">
+        <v>12</v>
+      </c>
+      <c r="H10" t="s">
+        <v>101</v>
+      </c>
+      <c r="I10" t="s">
+        <v>38</v>
+      </c>
+      <c r="J10" t="s">
         <v>173</v>
       </c>
-      <c r="H10" t="s">
-        <v>38</v>
-      </c>
-      <c r="I10" t="s">
+      <c r="K10" t="s">
         <v>235</v>
-      </c>
-      <c r="J10" t="s">
-        <v>43</v>
-      </c>
-      <c r="K10" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="11" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>59</v>
+        <v>43</v>
       </c>
       <c r="B11" t="s">
-        <v>12</v>
+        <v>60</v>
       </c>
       <c r="C11" t="s">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="D11" t="s">
         <v>118</v>
       </c>
       <c r="E11" t="s">
-        <v>45</v>
+        <v>12</v>
       </c>
       <c r="F11" t="s">
         <v>12</v>
       </c>
       <c r="G11" t="s">
+        <v>12</v>
+      </c>
+      <c r="H11" t="s">
+        <v>59</v>
+      </c>
+      <c r="I11" t="s">
+        <v>65</v>
+      </c>
+      <c r="J11" t="s">
         <v>222</v>
       </c>
-      <c r="H11" t="s">
-        <v>65</v>
-      </c>
-      <c r="I11" t="s">
+      <c r="K11" t="s">
         <v>237</v>
       </c>
-      <c r="J11" t="s">
-        <v>43</v>
-      </c>
-      <c r="K11" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="12" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="B12" t="s">
-        <v>12</v>
+        <v>122</v>
       </c>
       <c r="C12" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D12" t="s">
         <v>118</v>
       </c>
       <c r="E12" t="s">
-        <v>123</v>
+        <v>12</v>
       </c>
       <c r="F12" t="s">
         <v>12</v>
       </c>
       <c r="G12" t="s">
+        <v>12</v>
+      </c>
+      <c r="H12" t="s">
+        <v>24</v>
+      </c>
+      <c r="I12" t="s">
+        <v>101</v>
+      </c>
+      <c r="J12" t="s">
         <v>173</v>
       </c>
-      <c r="H12" t="s">
-        <v>101</v>
-      </c>
-      <c r="I12" t="s">
+      <c r="K12" t="s">
         <v>174</v>
-      </c>
-      <c r="J12" t="s">
-        <v>19</v>
-      </c>
-      <c r="K12" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="13" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>140</v>
+        <v>43</v>
       </c>
       <c r="B13" t="s">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="C13" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D13" t="s">
         <v>118</v>
       </c>
       <c r="E13" t="s">
-        <v>49</v>
+        <v>12</v>
       </c>
       <c r="F13" t="s">
         <v>12</v>
       </c>
       <c r="G13" t="s">
+        <v>12</v>
+      </c>
+      <c r="H13" t="s">
+        <v>140</v>
+      </c>
+      <c r="I13" t="s">
+        <v>193</v>
+      </c>
+      <c r="J13" t="s">
         <v>159</v>
       </c>
-      <c r="H13" t="s">
-        <v>193</v>
-      </c>
-      <c r="I13" t="s">
+      <c r="K13" t="s">
         <v>269</v>
-      </c>
-      <c r="J13" t="s">
-        <v>43</v>
-      </c>
-      <c r="K13" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="14" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>12</v>
+        <v>43</v>
       </c>
       <c r="B14" t="s">
-        <v>12</v>
+        <v>56</v>
       </c>
       <c r="C14" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="D14" t="s">
         <v>118</v>
       </c>
       <c r="E14" t="s">
-        <v>49</v>
+        <v>12</v>
       </c>
       <c r="F14" t="s">
         <v>12</v>
       </c>
       <c r="G14" t="s">
+        <v>12</v>
+      </c>
+      <c r="H14" t="s">
+        <v>12</v>
+      </c>
+      <c r="I14" t="s">
+        <v>105</v>
+      </c>
+      <c r="J14" t="s">
         <v>222</v>
       </c>
-      <c r="H14" t="s">
-        <v>105</v>
-      </c>
-      <c r="I14" t="s">
+      <c r="K14" t="s">
         <v>278</v>
       </c>
-      <c r="J14" t="s">
-        <v>43</v>
-      </c>
-      <c r="K14" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="15" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>54</v>
+        <v>19</v>
       </c>
       <c r="B15" t="s">
-        <v>12</v>
+        <v>145</v>
       </c>
       <c r="C15" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D15" t="s">
         <v>22</v>
       </c>
       <c r="E15" t="s">
-        <v>146</v>
+        <v>12</v>
       </c>
       <c r="F15" t="s">
         <v>12</v>
       </c>
       <c r="G15" t="s">
+        <v>12</v>
+      </c>
+      <c r="H15" t="s">
+        <v>54</v>
+      </c>
+      <c r="I15" t="s">
+        <v>98</v>
+      </c>
+      <c r="J15" t="s">
         <v>68</v>
       </c>
-      <c r="H15" t="s">
-        <v>98</v>
-      </c>
-      <c r="I15" t="s">
+      <c r="K15" t="s">
         <v>148</v>
       </c>
-      <c r="J15" t="s">
-        <v>19</v>
-      </c>
-      <c r="K15" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="16" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>52</v>
+        <v>19</v>
       </c>
       <c r="B16" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C16" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D16" t="s">
         <v>22</v>
       </c>
       <c r="E16" t="s">
+        <v>12</v>
+      </c>
+      <c r="F16" t="s">
+        <v>12</v>
+      </c>
+      <c r="G16" t="s">
+        <v>12</v>
+      </c>
+      <c r="H16" t="s">
+        <v>52</v>
+      </c>
+      <c r="I16" t="s">
+        <v>133</v>
+      </c>
+      <c r="J16" t="s">
+        <v>71</v>
+      </c>
+      <c r="K16" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>19</v>
+      </c>
+      <c r="B17" t="s">
+        <v>21</v>
+      </c>
+      <c r="C17" t="s">
         <v>15</v>
-      </c>
-      <c r="F16" t="s">
-        <v>12</v>
-      </c>
-      <c r="G16" t="s">
-        <v>71</v>
-      </c>
-      <c r="H16" t="s">
-        <v>133</v>
-      </c>
-      <c r="I16" t="s">
-        <v>196</v>
-      </c>
-      <c r="J16" t="s">
-        <v>19</v>
-      </c>
-      <c r="K16" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>20</v>
-      </c>
-      <c r="B17" t="s">
-        <v>12</v>
-      </c>
-      <c r="C17" t="s">
-        <v>21</v>
       </c>
       <c r="D17" t="s">
         <v>22</v>
       </c>
       <c r="E17" t="s">
+        <v>12</v>
+      </c>
+      <c r="F17" t="s">
+        <v>12</v>
+      </c>
+      <c r="G17" t="s">
+        <v>12</v>
+      </c>
+      <c r="H17" t="s">
+        <v>20</v>
+      </c>
+      <c r="I17" t="s">
+        <v>24</v>
+      </c>
+      <c r="J17" t="s">
+        <v>23</v>
+      </c>
+      <c r="K17" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>19</v>
+      </c>
+      <c r="B18" t="s">
+        <v>21</v>
+      </c>
+      <c r="C18" t="s">
         <v>15</v>
-      </c>
-      <c r="F17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G17" t="s">
-        <v>23</v>
-      </c>
-      <c r="H17" t="s">
-        <v>24</v>
-      </c>
-      <c r="I17" t="s">
-        <v>25</v>
-      </c>
-      <c r="J17" t="s">
-        <v>19</v>
-      </c>
-      <c r="K17" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>63</v>
-      </c>
-      <c r="B18" t="s">
-        <v>12</v>
-      </c>
-      <c r="C18" t="s">
-        <v>21</v>
       </c>
       <c r="D18" t="s">
         <v>22</v>
       </c>
       <c r="E18" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F18" t="s">
         <v>12</v>
       </c>
       <c r="G18" t="s">
+        <v>12</v>
+      </c>
+      <c r="H18" t="s">
+        <v>63</v>
+      </c>
+      <c r="I18" t="s">
+        <v>54</v>
+      </c>
+      <c r="J18" t="s">
         <v>197</v>
       </c>
-      <c r="H18" t="s">
-        <v>54</v>
-      </c>
-      <c r="I18" t="s">
+      <c r="K18" t="s">
         <v>198</v>
       </c>
-      <c r="J18" t="s">
-        <v>19</v>
-      </c>
-      <c r="K18" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="19" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="B19" t="s">
-        <v>52</v>
+        <v>125</v>
       </c>
       <c r="C19" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="D19" t="s">
         <v>22</v>
       </c>
       <c r="E19" t="s">
-        <v>123</v>
+        <v>12</v>
       </c>
       <c r="F19" t="s">
+        <v>52</v>
+      </c>
+      <c r="G19" t="s">
         <v>63</v>
       </c>
-      <c r="G19" t="s">
+      <c r="H19" t="s">
+        <v>38</v>
+      </c>
+      <c r="I19" t="s">
+        <v>119</v>
+      </c>
+      <c r="J19" t="s">
         <v>128</v>
       </c>
-      <c r="H19" t="s">
-        <v>119</v>
-      </c>
-      <c r="I19" t="s">
+      <c r="K19" t="s">
         <v>129</v>
       </c>
-      <c r="J19" t="s">
-        <v>19</v>
-      </c>
-      <c r="K19" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="20" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>52</v>
+        <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>12</v>
+        <v>103</v>
       </c>
       <c r="C20" t="s">
-        <v>103</v>
+        <v>32</v>
       </c>
       <c r="D20" t="s">
         <v>22</v>
       </c>
       <c r="E20" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="F20" t="s">
         <v>12</v>
       </c>
       <c r="G20" t="s">
+        <v>12</v>
+      </c>
+      <c r="H20" t="s">
+        <v>52</v>
+      </c>
+      <c r="I20" t="s">
+        <v>61</v>
+      </c>
+      <c r="J20" t="s">
         <v>71</v>
       </c>
-      <c r="H20" t="s">
-        <v>61</v>
-      </c>
-      <c r="I20" t="s">
+      <c r="K20" t="s">
         <v>107</v>
-      </c>
-      <c r="J20" t="s">
-        <v>19</v>
-      </c>
-      <c r="K20" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="21" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="B21" t="s">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="C21" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D21" t="s">
         <v>22</v>
       </c>
       <c r="E21" t="s">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="F21" t="s">
         <v>12</v>
       </c>
       <c r="G21" t="s">
+        <v>12</v>
+      </c>
+      <c r="H21" t="s">
+        <v>29</v>
+      </c>
+      <c r="I21" t="s">
+        <v>162</v>
+      </c>
+      <c r="J21" t="s">
         <v>71</v>
       </c>
-      <c r="H21" t="s">
-        <v>162</v>
-      </c>
-      <c r="I21" t="s">
+      <c r="K21" t="s">
         <v>180</v>
-      </c>
-      <c r="J21" t="s">
-        <v>43</v>
-      </c>
-      <c r="K21" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="22" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="B22" t="s">
-        <v>12</v>
+        <v>60</v>
       </c>
       <c r="C22" t="s">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="D22" t="s">
         <v>22</v>
       </c>
       <c r="E22" t="s">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="F22" t="s">
         <v>12</v>
       </c>
       <c r="G22" t="s">
+        <v>12</v>
+      </c>
+      <c r="H22" t="s">
+        <v>52</v>
+      </c>
+      <c r="I22" t="s">
+        <v>65</v>
+      </c>
+      <c r="J22" t="s">
         <v>182</v>
       </c>
-      <c r="H22" t="s">
-        <v>65</v>
-      </c>
-      <c r="I22" t="s">
+      <c r="K22" t="s">
         <v>183</v>
       </c>
-      <c r="J22" t="s">
-        <v>43</v>
-      </c>
-      <c r="K22" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="B23" t="s">
-        <v>12</v>
+        <v>44</v>
       </c>
       <c r="C23" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D23" t="s">
         <v>22</v>
       </c>
       <c r="E23" t="s">
-        <v>45</v>
+        <v>12</v>
       </c>
       <c r="F23" t="s">
         <v>12</v>
       </c>
       <c r="G23" t="s">
+        <v>12</v>
+      </c>
+      <c r="H23" t="s">
+        <v>20</v>
+      </c>
+      <c r="I23" t="s">
+        <v>46</v>
+      </c>
+      <c r="J23" t="s">
         <v>128</v>
       </c>
-      <c r="H23" t="s">
-        <v>46</v>
-      </c>
-      <c r="I23" t="s">
+      <c r="K23" t="s">
         <v>184</v>
       </c>
-      <c r="J23" t="s">
-        <v>43</v>
-      </c>
-      <c r="K23" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="24" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="B24" t="s">
-        <v>12</v>
+        <v>122</v>
       </c>
       <c r="C24" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D24" t="s">
         <v>22</v>
       </c>
       <c r="E24" t="s">
-        <v>123</v>
+        <v>12</v>
       </c>
       <c r="F24" t="s">
         <v>12</v>
       </c>
       <c r="G24" t="s">
+        <v>12</v>
+      </c>
+      <c r="H24" t="s">
+        <v>11</v>
+      </c>
+      <c r="I24" t="s">
+        <v>65</v>
+      </c>
+      <c r="J24" t="s">
         <v>71</v>
       </c>
-      <c r="H24" t="s">
-        <v>65</v>
-      </c>
-      <c r="I24" t="s">
+      <c r="K24" t="s">
         <v>156</v>
       </c>
-      <c r="J24" t="s">
-        <v>19</v>
-      </c>
-      <c r="K24" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="25" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="B25" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="C25" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D25" t="s">
         <v>22</v>
       </c>
       <c r="E25" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="F25" t="s">
         <v>12</v>
       </c>
       <c r="G25" t="s">
+        <v>12</v>
+      </c>
+      <c r="H25" t="s">
+        <v>12</v>
+      </c>
+      <c r="I25" t="s">
+        <v>72</v>
+      </c>
+      <c r="J25" t="s">
         <v>71</v>
       </c>
-      <c r="H25" t="s">
-        <v>72</v>
-      </c>
-      <c r="I25" t="s">
+      <c r="K25" t="s">
         <v>73</v>
-      </c>
-      <c r="J25" t="s">
-        <v>19</v>
-      </c>
-      <c r="K25" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="26" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>12</v>
+        <v>43</v>
       </c>
       <c r="B26" t="s">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="C26" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D26" t="s">
         <v>22</v>
       </c>
       <c r="E26" t="s">
-        <v>49</v>
+        <v>12</v>
       </c>
       <c r="F26" t="s">
         <v>12</v>
       </c>
       <c r="G26" t="s">
+        <v>12</v>
+      </c>
+      <c r="H26" t="s">
+        <v>12</v>
+      </c>
+      <c r="I26" t="s">
+        <v>98</v>
+      </c>
+      <c r="J26" t="s">
         <v>128</v>
       </c>
-      <c r="H26" t="s">
-        <v>98</v>
-      </c>
-      <c r="I26" t="s">
+      <c r="K26" t="s">
         <v>209</v>
-      </c>
-      <c r="J26" t="s">
-        <v>43</v>
-      </c>
-      <c r="K26" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="27" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>12</v>
+        <v>43</v>
       </c>
       <c r="B27" t="s">
-        <v>12</v>
+        <v>56</v>
       </c>
       <c r="C27" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="D27" t="s">
         <v>22</v>
       </c>
       <c r="E27" t="s">
-        <v>49</v>
+        <v>12</v>
       </c>
       <c r="F27" t="s">
         <v>12</v>
       </c>
       <c r="G27" t="s">
+        <v>12</v>
+      </c>
+      <c r="H27" t="s">
+        <v>12</v>
+      </c>
+      <c r="I27" t="s">
+        <v>57</v>
+      </c>
+      <c r="J27" t="s">
         <v>197</v>
       </c>
-      <c r="H27" t="s">
-        <v>57</v>
-      </c>
-      <c r="I27" t="s">
+      <c r="K27" t="s">
         <v>210</v>
-      </c>
-      <c r="J27" t="s">
-        <v>43</v>
-      </c>
-      <c r="K27" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="28" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="B28" t="s">
-        <v>12</v>
+        <v>60</v>
       </c>
       <c r="C28" t="s">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="D28" t="s">
         <v>22</v>
       </c>
       <c r="E28" t="s">
-        <v>45</v>
+        <v>12</v>
       </c>
       <c r="F28" t="s">
         <v>12</v>
       </c>
       <c r="G28" t="s">
+        <v>12</v>
+      </c>
+      <c r="H28" t="s">
+        <v>38</v>
+      </c>
+      <c r="I28" t="s">
+        <v>162</v>
+      </c>
+      <c r="J28" t="s">
         <v>71</v>
       </c>
-      <c r="H28" t="s">
-        <v>162</v>
-      </c>
-      <c r="I28" t="s">
+      <c r="K28" t="s">
         <v>231</v>
       </c>
-      <c r="J28" t="s">
-        <v>43</v>
-      </c>
-      <c r="K28" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="29" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>144</v>
+        <v>19</v>
       </c>
       <c r="B29" t="s">
-        <v>12</v>
+        <v>145</v>
       </c>
       <c r="C29" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D29" t="s">
         <v>67</v>
       </c>
       <c r="E29" t="s">
-        <v>146</v>
+        <v>12</v>
       </c>
       <c r="F29" t="s">
         <v>12</v>
       </c>
       <c r="G29" t="s">
+        <v>12</v>
+      </c>
+      <c r="H29" t="s">
+        <v>144</v>
+      </c>
+      <c r="I29" t="s">
+        <v>88</v>
+      </c>
+      <c r="J29" t="s">
         <v>68</v>
       </c>
-      <c r="H29" t="s">
-        <v>88</v>
-      </c>
-      <c r="I29" t="s">
+      <c r="K29" t="s">
         <v>147</v>
       </c>
-      <c r="J29" t="s">
-        <v>19</v>
-      </c>
-      <c r="K29" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="30" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="B30" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C30" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D30" t="s">
         <v>67</v>
       </c>
       <c r="E30" t="s">
+        <v>12</v>
+      </c>
+      <c r="F30" t="s">
+        <v>12</v>
+      </c>
+      <c r="G30" t="s">
+        <v>12</v>
+      </c>
+      <c r="H30" t="s">
+        <v>24</v>
+      </c>
+      <c r="I30" t="s">
+        <v>54</v>
+      </c>
+      <c r="J30" t="s">
+        <v>152</v>
+      </c>
+      <c r="K30" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>19</v>
+      </c>
+      <c r="B31" t="s">
+        <v>21</v>
+      </c>
+      <c r="C31" t="s">
         <v>15</v>
-      </c>
-      <c r="F30" t="s">
-        <v>12</v>
-      </c>
-      <c r="G30" t="s">
-        <v>152</v>
-      </c>
-      <c r="H30" t="s">
-        <v>54</v>
-      </c>
-      <c r="I30" t="s">
-        <v>153</v>
-      </c>
-      <c r="J30" t="s">
-        <v>19</v>
-      </c>
-      <c r="K30" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>63</v>
-      </c>
-      <c r="B31" t="s">
-        <v>12</v>
-      </c>
-      <c r="C31" t="s">
-        <v>21</v>
       </c>
       <c r="D31" t="s">
         <v>67</v>
       </c>
       <c r="E31" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F31" t="s">
+        <v>12</v>
+      </c>
+      <c r="G31" t="s">
         <v>29</v>
       </c>
-      <c r="G31" t="s">
+      <c r="H31" t="s">
+        <v>63</v>
+      </c>
+      <c r="I31" t="s">
+        <v>140</v>
+      </c>
+      <c r="J31" t="s">
         <v>150</v>
       </c>
-      <c r="H31" t="s">
-        <v>140</v>
-      </c>
-      <c r="I31" t="s">
+      <c r="K31" t="s">
         <v>151</v>
-      </c>
-      <c r="J31" t="s">
-        <v>19</v>
-      </c>
-      <c r="K31" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="32" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>12</v>
+        <v>43</v>
       </c>
       <c r="B32" t="s">
-        <v>12</v>
+        <v>56</v>
       </c>
       <c r="C32" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="D32" t="s">
         <v>67</v>
       </c>
       <c r="E32" t="s">
-        <v>49</v>
+        <v>12</v>
       </c>
       <c r="F32" t="s">
         <v>12</v>
       </c>
       <c r="G32" t="s">
+        <v>12</v>
+      </c>
+      <c r="H32" t="s">
+        <v>12</v>
+      </c>
+      <c r="I32" t="s">
+        <v>61</v>
+      </c>
+      <c r="J32" t="s">
         <v>68</v>
       </c>
-      <c r="H32" t="s">
-        <v>61</v>
-      </c>
-      <c r="I32" t="s">
+      <c r="K32" t="s">
         <v>143</v>
       </c>
-      <c r="J32" t="s">
-        <v>43</v>
-      </c>
-      <c r="K32" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="33" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="B33" t="s">
-        <v>29</v>
+        <v>125</v>
       </c>
       <c r="C33" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="D33" t="s">
         <v>67</v>
       </c>
       <c r="E33" t="s">
-        <v>123</v>
+        <v>29</v>
       </c>
       <c r="F33" t="s">
+        <v>29</v>
+      </c>
+      <c r="G33" t="s">
         <v>59</v>
       </c>
-      <c r="G33" t="s">
+      <c r="H33" t="s">
+        <v>27</v>
+      </c>
+      <c r="I33" t="s">
+        <v>54</v>
+      </c>
+      <c r="J33" t="s">
         <v>68</v>
       </c>
-      <c r="H33" t="s">
-        <v>54</v>
-      </c>
-      <c r="I33" t="s">
+      <c r="K33" t="s">
         <v>127</v>
       </c>
-      <c r="J33" t="s">
-        <v>19</v>
-      </c>
-      <c r="K33" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="34" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="B34" t="s">
-        <v>12</v>
+        <v>103</v>
       </c>
       <c r="C34" t="s">
-        <v>103</v>
+        <v>32</v>
       </c>
       <c r="D34" t="s">
         <v>67</v>
       </c>
       <c r="E34" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="F34" t="s">
         <v>12</v>
       </c>
       <c r="G34" t="s">
+        <v>12</v>
+      </c>
+      <c r="H34" t="s">
+        <v>12</v>
+      </c>
+      <c r="I34" t="s">
+        <v>105</v>
+      </c>
+      <c r="J34" t="s">
         <v>68</v>
       </c>
-      <c r="H34" t="s">
-        <v>105</v>
-      </c>
-      <c r="I34" t="s">
+      <c r="K34" t="s">
         <v>106</v>
       </c>
-      <c r="J34" t="s">
-        <v>19</v>
-      </c>
-      <c r="K34" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="35" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="B35" t="s">
-        <v>12</v>
+        <v>122</v>
       </c>
       <c r="C35" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D35" t="s">
         <v>67</v>
       </c>
       <c r="E35" t="s">
-        <v>123</v>
+        <v>12</v>
       </c>
       <c r="F35" t="s">
         <v>12</v>
       </c>
       <c r="G35" t="s">
+        <v>12</v>
+      </c>
+      <c r="H35" t="s">
+        <v>24</v>
+      </c>
+      <c r="I35" t="s">
+        <v>105</v>
+      </c>
+      <c r="J35" t="s">
         <v>152</v>
       </c>
-      <c r="H35" t="s">
-        <v>105</v>
-      </c>
-      <c r="I35" t="s">
+      <c r="K35" t="s">
         <v>155</v>
       </c>
-      <c r="J35" t="s">
-        <v>19</v>
-      </c>
-      <c r="K35" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="36" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>11</v>
+        <v>43</v>
       </c>
       <c r="B36" t="s">
-        <v>12</v>
+        <v>44</v>
       </c>
       <c r="C36" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D36" t="s">
         <v>67</v>
       </c>
       <c r="E36" t="s">
-        <v>45</v>
+        <v>12</v>
       </c>
       <c r="F36" t="s">
         <v>12</v>
       </c>
       <c r="G36" t="s">
+        <v>12</v>
+      </c>
+      <c r="H36" t="s">
+        <v>11</v>
+      </c>
+      <c r="I36" t="s">
+        <v>17</v>
+      </c>
+      <c r="J36" t="s">
         <v>150</v>
       </c>
-      <c r="H36" t="s">
-        <v>17</v>
-      </c>
-      <c r="I36" t="s">
+      <c r="K36" t="s">
         <v>154</v>
       </c>
-      <c r="J36" t="s">
-        <v>43</v>
-      </c>
-      <c r="K36" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="37" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="B37" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="C37" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D37" t="s">
         <v>67</v>
       </c>
       <c r="E37" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="F37" t="s">
         <v>12</v>
       </c>
       <c r="G37" t="s">
+        <v>12</v>
+      </c>
+      <c r="H37" t="s">
+        <v>12</v>
+      </c>
+      <c r="I37" t="s">
+        <v>69</v>
+      </c>
+      <c r="J37" t="s">
         <v>68</v>
       </c>
-      <c r="H37" t="s">
-        <v>69</v>
-      </c>
-      <c r="I37" t="s">
+      <c r="K37" t="s">
         <v>70</v>
-      </c>
-      <c r="J37" t="s">
-        <v>19</v>
-      </c>
-      <c r="K37" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="38" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>63</v>
+        <v>43</v>
       </c>
       <c r="B38" t="s">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="C38" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D38" t="s">
         <v>67</v>
       </c>
       <c r="E38" t="s">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="F38" t="s">
         <v>12</v>
       </c>
       <c r="G38" t="s">
+        <v>12</v>
+      </c>
+      <c r="H38" t="s">
+        <v>63</v>
+      </c>
+      <c r="I38" t="s">
+        <v>46</v>
+      </c>
+      <c r="J38" t="s">
         <v>150</v>
       </c>
-      <c r="H38" t="s">
-        <v>46</v>
-      </c>
-      <c r="I38" t="s">
+      <c r="K38" t="s">
         <v>175</v>
-      </c>
-      <c r="J38" t="s">
-        <v>43</v>
-      </c>
-      <c r="K38" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="39" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>12</v>
+        <v>43</v>
       </c>
       <c r="B39" t="s">
-        <v>12</v>
+        <v>60</v>
       </c>
       <c r="C39" t="s">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="D39" t="s">
         <v>67</v>
       </c>
       <c r="E39" t="s">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="F39" t="s">
         <v>12</v>
       </c>
       <c r="G39" t="s">
+        <v>12</v>
+      </c>
+      <c r="H39" t="s">
+        <v>12</v>
+      </c>
+      <c r="I39" t="s">
+        <v>65</v>
+      </c>
+      <c r="J39" t="s">
         <v>152</v>
       </c>
-      <c r="H39" t="s">
-        <v>65</v>
-      </c>
-      <c r="I39" t="s">
+      <c r="K39" t="s">
         <v>176</v>
-      </c>
-      <c r="J39" t="s">
-        <v>43</v>
-      </c>
-      <c r="K39" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="40" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="B40" t="s">
-        <v>12</v>
+        <v>60</v>
       </c>
       <c r="C40" t="s">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="D40" t="s">
         <v>67</v>
       </c>
       <c r="E40" t="s">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="F40" t="s">
         <v>12</v>
       </c>
       <c r="G40" t="s">
+        <v>12</v>
+      </c>
+      <c r="H40" t="s">
+        <v>52</v>
+      </c>
+      <c r="I40" t="s">
+        <v>105</v>
+      </c>
+      <c r="J40" t="s">
         <v>152</v>
       </c>
-      <c r="H40" t="s">
-        <v>105</v>
-      </c>
-      <c r="I40" t="s">
+      <c r="K40" t="s">
         <v>177</v>
-      </c>
-      <c r="J40" t="s">
-        <v>43</v>
-      </c>
-      <c r="K40" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="41" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>59</v>
+        <v>43</v>
       </c>
       <c r="B41" t="s">
-        <v>12</v>
+        <v>60</v>
       </c>
       <c r="C41" t="s">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="D41" t="s">
         <v>67</v>
       </c>
       <c r="E41" t="s">
-        <v>45</v>
+        <v>12</v>
       </c>
       <c r="F41" t="s">
         <v>12</v>
       </c>
       <c r="G41" t="s">
+        <v>12</v>
+      </c>
+      <c r="H41" t="s">
+        <v>59</v>
+      </c>
+      <c r="I41" t="s">
+        <v>61</v>
+      </c>
+      <c r="J41" t="s">
         <v>152</v>
       </c>
-      <c r="H41" t="s">
-        <v>61</v>
-      </c>
-      <c r="I41" t="s">
+      <c r="K41" t="s">
         <v>178</v>
-      </c>
-      <c r="J41" t="s">
-        <v>43</v>
-      </c>
-      <c r="K41" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="42" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>12</v>
+        <v>43</v>
       </c>
       <c r="B42" t="s">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="C42" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D42" t="s">
         <v>67</v>
       </c>
       <c r="E42" t="s">
-        <v>49</v>
+        <v>12</v>
       </c>
       <c r="F42" t="s">
         <v>12</v>
       </c>
       <c r="G42" t="s">
+        <v>12</v>
+      </c>
+      <c r="H42" t="s">
+        <v>12</v>
+      </c>
+      <c r="I42" t="s">
+        <v>50</v>
+      </c>
+      <c r="J42" t="s">
         <v>152</v>
       </c>
-      <c r="H42" t="s">
-        <v>50</v>
-      </c>
-      <c r="I42" t="s">
+      <c r="K42" t="s">
         <v>179</v>
       </c>
-      <c r="J42" t="s">
-        <v>43</v>
-      </c>
-      <c r="K42" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="43" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="B43" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C43" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D43" t="s">
         <v>31</v>
       </c>
       <c r="E43" t="s">
+        <v>12</v>
+      </c>
+      <c r="F43" t="s">
+        <v>12</v>
+      </c>
+      <c r="G43" t="s">
+        <v>52</v>
+      </c>
+      <c r="H43" t="s">
+        <v>11</v>
+      </c>
+      <c r="I43" t="s">
+        <v>54</v>
+      </c>
+      <c r="J43" t="s">
+        <v>53</v>
+      </c>
+      <c r="K43" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>19</v>
+      </c>
+      <c r="B44" t="s">
+        <v>21</v>
+      </c>
+      <c r="C44" t="s">
         <v>15</v>
-      </c>
-      <c r="F43" t="s">
-        <v>52</v>
-      </c>
-      <c r="G43" t="s">
-        <v>53</v>
-      </c>
-      <c r="H43" t="s">
-        <v>54</v>
-      </c>
-      <c r="I43" t="s">
-        <v>55</v>
-      </c>
-      <c r="J43" t="s">
-        <v>19</v>
-      </c>
-      <c r="K43" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
-        <v>20</v>
-      </c>
-      <c r="B44" t="s">
-        <v>12</v>
-      </c>
-      <c r="C44" t="s">
-        <v>21</v>
       </c>
       <c r="D44" t="s">
         <v>31</v>
       </c>
       <c r="E44" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F44" t="s">
         <v>12</v>
       </c>
       <c r="G44" t="s">
+        <v>12</v>
+      </c>
+      <c r="H44" t="s">
+        <v>20</v>
+      </c>
+      <c r="I44" t="s">
+        <v>27</v>
+      </c>
+      <c r="J44" t="s">
         <v>36</v>
       </c>
-      <c r="H44" t="s">
-        <v>27</v>
-      </c>
-      <c r="I44" t="s">
+      <c r="K44" t="s">
         <v>37</v>
-      </c>
-      <c r="J44" t="s">
-        <v>19</v>
-      </c>
-      <c r="K44" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="45" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="B45" t="s">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="C45" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D45" t="s">
         <v>31</v>
       </c>
       <c r="E45" t="s">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="F45" t="s">
+        <v>12</v>
+      </c>
+      <c r="G45" t="s">
         <v>29</v>
       </c>
-      <c r="G45" t="s">
+      <c r="H45" t="s">
+        <v>38</v>
+      </c>
+      <c r="I45" t="s">
+        <v>41</v>
+      </c>
+      <c r="J45" t="s">
         <v>36</v>
       </c>
-      <c r="H45" t="s">
-        <v>41</v>
-      </c>
-      <c r="I45" t="s">
+      <c r="K45" t="s">
         <v>42</v>
       </c>
-      <c r="J45" t="s">
-        <v>43</v>
-      </c>
-      <c r="K45" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="46" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="B46" t="s">
-        <v>12</v>
+        <v>44</v>
       </c>
       <c r="C46" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D46" t="s">
         <v>31</v>
       </c>
       <c r="E46" t="s">
-        <v>45</v>
+        <v>12</v>
       </c>
       <c r="F46" t="s">
         <v>12</v>
       </c>
       <c r="G46" t="s">
+        <v>12</v>
+      </c>
+      <c r="H46" t="s">
+        <v>20</v>
+      </c>
+      <c r="I46" t="s">
+        <v>46</v>
+      </c>
+      <c r="J46" t="s">
         <v>36</v>
       </c>
-      <c r="H46" t="s">
-        <v>46</v>
-      </c>
-      <c r="I46" t="s">
+      <c r="K46" t="s">
         <v>47</v>
-      </c>
-      <c r="J46" t="s">
-        <v>43</v>
-      </c>
-      <c r="K46" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="47" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>12</v>
+        <v>43</v>
       </c>
       <c r="B47" t="s">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="C47" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D47" t="s">
         <v>31</v>
       </c>
       <c r="E47" t="s">
-        <v>49</v>
+        <v>12</v>
       </c>
       <c r="F47" t="s">
         <v>12</v>
       </c>
       <c r="G47" t="s">
+        <v>12</v>
+      </c>
+      <c r="H47" t="s">
+        <v>12</v>
+      </c>
+      <c r="I47" t="s">
+        <v>50</v>
+      </c>
+      <c r="J47" t="s">
         <v>36</v>
       </c>
-      <c r="H47" t="s">
-        <v>50</v>
-      </c>
-      <c r="I47" t="s">
+      <c r="K47" t="s">
         <v>51</v>
       </c>
-      <c r="J47" t="s">
-        <v>43</v>
-      </c>
-      <c r="K47" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="48" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="B48" t="s">
-        <v>12</v>
+        <v>125</v>
       </c>
       <c r="C48" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="D48" t="s">
         <v>31</v>
       </c>
       <c r="E48" t="s">
-        <v>123</v>
+        <v>12</v>
       </c>
       <c r="F48" t="s">
+        <v>12</v>
+      </c>
+      <c r="G48" t="s">
         <v>29</v>
       </c>
-      <c r="G48" t="s">
+      <c r="H48" t="s">
+        <v>38</v>
+      </c>
+      <c r="I48" t="s">
+        <v>108</v>
+      </c>
+      <c r="J48" t="s">
         <v>33</v>
       </c>
-      <c r="H48" t="s">
-        <v>108</v>
-      </c>
-      <c r="I48" t="s">
+      <c r="K48" t="s">
         <v>126</v>
-      </c>
-      <c r="J48" t="s">
-        <v>19</v>
-      </c>
-      <c r="K48" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="49" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>12</v>
+        <v>43</v>
       </c>
       <c r="B49" t="s">
-        <v>12</v>
+        <v>56</v>
       </c>
       <c r="C49" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="D49" t="s">
         <v>31</v>
       </c>
       <c r="E49" t="s">
-        <v>49</v>
+        <v>12</v>
       </c>
       <c r="F49" t="s">
         <v>12</v>
       </c>
       <c r="G49" t="s">
+        <v>12</v>
+      </c>
+      <c r="H49" t="s">
+        <v>12</v>
+      </c>
+      <c r="I49" t="s">
+        <v>57</v>
+      </c>
+      <c r="J49" t="s">
         <v>33</v>
       </c>
-      <c r="H49" t="s">
-        <v>57</v>
-      </c>
-      <c r="I49" t="s">
+      <c r="K49" t="s">
         <v>58</v>
-      </c>
-      <c r="J49" t="s">
-        <v>43</v>
-      </c>
-      <c r="K49" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="50" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>59</v>
+        <v>43</v>
       </c>
       <c r="B50" t="s">
-        <v>12</v>
+        <v>60</v>
       </c>
       <c r="C50" t="s">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="D50" t="s">
         <v>31</v>
       </c>
       <c r="E50" t="s">
-        <v>45</v>
+        <v>12</v>
       </c>
       <c r="F50" t="s">
         <v>12</v>
       </c>
       <c r="G50" t="s">
+        <v>12</v>
+      </c>
+      <c r="H50" t="s">
+        <v>59</v>
+      </c>
+      <c r="I50" t="s">
+        <v>61</v>
+      </c>
+      <c r="J50" t="s">
         <v>53</v>
       </c>
-      <c r="H50" t="s">
-        <v>61</v>
-      </c>
-      <c r="I50" t="s">
+      <c r="K50" t="s">
         <v>62</v>
-      </c>
-      <c r="J50" t="s">
-        <v>43</v>
-      </c>
-      <c r="K50" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="51" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>63</v>
+        <v>43</v>
       </c>
       <c r="B51" t="s">
-        <v>12</v>
+        <v>60</v>
       </c>
       <c r="C51" t="s">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="D51" t="s">
         <v>31</v>
       </c>
       <c r="E51" t="s">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="F51" t="s">
         <v>12</v>
       </c>
       <c r="G51" t="s">
+        <v>12</v>
+      </c>
+      <c r="H51" t="s">
+        <v>63</v>
+      </c>
+      <c r="I51" t="s">
+        <v>61</v>
+      </c>
+      <c r="J51" t="s">
         <v>53</v>
       </c>
-      <c r="H51" t="s">
-        <v>61</v>
-      </c>
-      <c r="I51" t="s">
+      <c r="K51" t="s">
         <v>64</v>
-      </c>
-      <c r="J51" t="s">
-        <v>43</v>
-      </c>
-      <c r="K51" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="52" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>12</v>
+        <v>43</v>
       </c>
       <c r="B52" t="s">
-        <v>12</v>
+        <v>60</v>
       </c>
       <c r="C52" t="s">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="D52" t="s">
         <v>31</v>
       </c>
       <c r="E52" t="s">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="F52" t="s">
         <v>12</v>
       </c>
       <c r="G52" t="s">
+        <v>12</v>
+      </c>
+      <c r="H52" t="s">
+        <v>12</v>
+      </c>
+      <c r="I52" t="s">
+        <v>65</v>
+      </c>
+      <c r="J52" t="s">
         <v>53</v>
       </c>
-      <c r="H52" t="s">
-        <v>65</v>
-      </c>
-      <c r="I52" t="s">
+      <c r="K52" t="s">
         <v>66</v>
       </c>
-      <c r="J52" t="s">
-        <v>43</v>
-      </c>
-      <c r="K52" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="53" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="B53" t="s">
-        <v>12</v>
+        <v>103</v>
       </c>
       <c r="C53" t="s">
-        <v>103</v>
+        <v>32</v>
       </c>
       <c r="D53" t="s">
         <v>31</v>
       </c>
       <c r="E53" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="F53" t="s">
         <v>12</v>
       </c>
       <c r="G53" t="s">
+        <v>12</v>
+      </c>
+      <c r="H53" t="s">
+        <v>12</v>
+      </c>
+      <c r="I53" t="s">
+        <v>61</v>
+      </c>
+      <c r="J53" t="s">
         <v>33</v>
       </c>
-      <c r="H53" t="s">
-        <v>61</v>
-      </c>
-      <c r="I53" t="s">
+      <c r="K53" t="s">
         <v>104</v>
       </c>
-      <c r="J53" t="s">
-        <v>19</v>
-      </c>
-      <c r="K53" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="54" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>121</v>
+        <v>19</v>
       </c>
       <c r="B54" t="s">
-        <v>12</v>
+        <v>122</v>
       </c>
       <c r="C54" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D54" t="s">
         <v>31</v>
       </c>
       <c r="E54" t="s">
-        <v>123</v>
+        <v>12</v>
       </c>
       <c r="F54" t="s">
+        <v>12</v>
+      </c>
+      <c r="G54" t="s">
         <v>29</v>
       </c>
-      <c r="G54" t="s">
+      <c r="H54" t="s">
+        <v>121</v>
+      </c>
+      <c r="I54" t="s">
+        <v>101</v>
+      </c>
+      <c r="J54" t="s">
         <v>53</v>
       </c>
-      <c r="H54" t="s">
-        <v>101</v>
-      </c>
-      <c r="I54" t="s">
+      <c r="K54" t="s">
         <v>124</v>
       </c>
-      <c r="J54" t="s">
-        <v>19</v>
-      </c>
-      <c r="K54" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="55" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="B55" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="C55" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D55" t="s">
         <v>31</v>
       </c>
       <c r="E55" t="s">
+        <v>12</v>
+      </c>
+      <c r="F55" t="s">
+        <v>12</v>
+      </c>
+      <c r="G55" t="s">
+        <v>12</v>
+      </c>
+      <c r="H55" t="s">
+        <v>29</v>
+      </c>
+      <c r="I55" t="s">
+        <v>34</v>
+      </c>
+      <c r="J55" t="s">
+        <v>33</v>
+      </c>
+      <c r="K55" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="56" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>19</v>
+      </c>
+      <c r="B56" t="s">
+        <v>30</v>
+      </c>
+      <c r="C56" t="s">
         <v>32</v>
-      </c>
-      <c r="F55" t="s">
-        <v>12</v>
-      </c>
-      <c r="G55" t="s">
-        <v>33</v>
-      </c>
-      <c r="H55" t="s">
-        <v>34</v>
-      </c>
-      <c r="I55" t="s">
-        <v>35</v>
-      </c>
-      <c r="J55" t="s">
-        <v>19</v>
-      </c>
-      <c r="K55" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A56" t="s">
-        <v>59</v>
-      </c>
-      <c r="B56" t="s">
-        <v>12</v>
-      </c>
-      <c r="C56" t="s">
-        <v>30</v>
       </c>
       <c r="D56" t="s">
         <v>31</v>
       </c>
       <c r="E56" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="F56" t="s">
+        <v>12</v>
+      </c>
+      <c r="G56" t="s">
         <v>29</v>
       </c>
-      <c r="G56" t="s">
+      <c r="H56" t="s">
+        <v>59</v>
+      </c>
+      <c r="I56" t="s">
+        <v>101</v>
+      </c>
+      <c r="J56" t="s">
         <v>100</v>
       </c>
-      <c r="H56" t="s">
-        <v>101</v>
-      </c>
-      <c r="I56" t="s">
+      <c r="K56" t="s">
         <v>102</v>
       </c>
-      <c r="J56" t="s">
-        <v>19</v>
-      </c>
-      <c r="K56" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="57" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>140</v>
+        <v>19</v>
       </c>
       <c r="B57" t="s">
-        <v>52</v>
+        <v>145</v>
       </c>
       <c r="C57" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D57" t="s">
         <v>96</v>
       </c>
       <c r="E57" t="s">
-        <v>146</v>
+        <v>12</v>
       </c>
       <c r="F57" t="s">
+        <v>52</v>
+      </c>
+      <c r="G57" t="s">
         <v>38</v>
       </c>
-      <c r="G57" t="s">
+      <c r="H57" t="s">
+        <v>140</v>
+      </c>
+      <c r="I57" t="s">
+        <v>133</v>
+      </c>
+      <c r="J57" t="s">
         <v>77</v>
       </c>
-      <c r="H57" t="s">
-        <v>133</v>
-      </c>
-      <c r="I57" t="s">
+      <c r="K57" t="s">
         <v>246</v>
       </c>
-      <c r="J57" t="s">
-        <v>19</v>
-      </c>
-      <c r="K57" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="58" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="B58" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C58" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D58" t="s">
         <v>96</v>
       </c>
       <c r="E58" t="s">
+        <v>12</v>
+      </c>
+      <c r="F58" t="s">
+        <v>12</v>
+      </c>
+      <c r="G58" t="s">
+        <v>12</v>
+      </c>
+      <c r="H58" t="s">
+        <v>29</v>
+      </c>
+      <c r="I58" t="s">
+        <v>193</v>
+      </c>
+      <c r="J58" t="s">
+        <v>171</v>
+      </c>
+      <c r="K58" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="59" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>19</v>
+      </c>
+      <c r="B59" t="s">
+        <v>21</v>
+      </c>
+      <c r="C59" t="s">
         <v>15</v>
-      </c>
-      <c r="F58" t="s">
-        <v>12</v>
-      </c>
-      <c r="G58" t="s">
-        <v>171</v>
-      </c>
-      <c r="H58" t="s">
-        <v>193</v>
-      </c>
-      <c r="I58" t="s">
-        <v>194</v>
-      </c>
-      <c r="J58" t="s">
-        <v>19</v>
-      </c>
-      <c r="K58" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A59" t="s">
-        <v>38</v>
-      </c>
-      <c r="B59" t="s">
-        <v>52</v>
-      </c>
-      <c r="C59" t="s">
-        <v>21</v>
       </c>
       <c r="D59" t="s">
         <v>96</v>
       </c>
       <c r="E59" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F59" t="s">
-        <v>12</v>
+        <v>52</v>
       </c>
       <c r="G59" t="s">
+        <v>12</v>
+      </c>
+      <c r="H59" t="s">
+        <v>38</v>
+      </c>
+      <c r="I59" t="s">
+        <v>121</v>
+      </c>
+      <c r="J59" t="s">
         <v>97</v>
       </c>
-      <c r="H59" t="s">
-        <v>121</v>
-      </c>
-      <c r="I59" t="s">
+      <c r="K59" t="s">
         <v>207</v>
       </c>
-      <c r="J59" t="s">
-        <v>19</v>
-      </c>
-      <c r="K59" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="60" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>140</v>
+        <v>19</v>
       </c>
       <c r="B60" t="s">
-        <v>12</v>
+        <v>125</v>
       </c>
       <c r="C60" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="D60" t="s">
         <v>96</v>
       </c>
       <c r="E60" t="s">
-        <v>123</v>
+        <v>12</v>
       </c>
       <c r="F60" t="s">
         <v>12</v>
       </c>
       <c r="G60" t="s">
+        <v>12</v>
+      </c>
+      <c r="H60" t="s">
+        <v>140</v>
+      </c>
+      <c r="I60" t="s">
+        <v>119</v>
+      </c>
+      <c r="J60" t="s">
         <v>97</v>
       </c>
-      <c r="H60" t="s">
-        <v>119</v>
-      </c>
-      <c r="I60" t="s">
+      <c r="K60" t="s">
         <v>141</v>
       </c>
-      <c r="J60" t="s">
-        <v>19</v>
-      </c>
-      <c r="K60" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="61" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B61" t="s">
-        <v>12</v>
+        <v>103</v>
       </c>
       <c r="C61" t="s">
-        <v>103</v>
+        <v>32</v>
       </c>
       <c r="D61" t="s">
         <v>96</v>
       </c>
       <c r="E61" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F61" t="s">
+        <v>12</v>
+      </c>
+      <c r="G61" t="s">
         <v>29</v>
       </c>
-      <c r="G61" t="s">
+      <c r="H61" t="s">
+        <v>20</v>
+      </c>
+      <c r="I61" t="s">
+        <v>108</v>
+      </c>
+      <c r="J61" t="s">
         <v>97</v>
       </c>
-      <c r="H61" t="s">
-        <v>108</v>
-      </c>
-      <c r="I61" t="s">
+      <c r="K61" t="s">
         <v>117</v>
       </c>
-      <c r="J61" t="s">
-        <v>19</v>
-      </c>
-      <c r="K61" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="62" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="B62" t="s">
-        <v>12</v>
+        <v>122</v>
       </c>
       <c r="C62" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D62" t="s">
         <v>96</v>
       </c>
       <c r="E62" t="s">
-        <v>123</v>
+        <v>12</v>
       </c>
       <c r="F62" t="s">
         <v>12</v>
       </c>
       <c r="G62" t="s">
+        <v>12</v>
+      </c>
+      <c r="H62" t="s">
+        <v>24</v>
+      </c>
+      <c r="I62" t="s">
+        <v>105</v>
+      </c>
+      <c r="J62" t="s">
         <v>171</v>
       </c>
-      <c r="H62" t="s">
-        <v>105</v>
-      </c>
-      <c r="I62" t="s">
+      <c r="K62" t="s">
         <v>172</v>
-      </c>
-      <c r="J62" t="s">
-        <v>19</v>
-      </c>
-      <c r="K62" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="63" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>119</v>
+        <v>43</v>
       </c>
       <c r="B63" t="s">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="C63" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D63" t="s">
         <v>96</v>
       </c>
       <c r="E63" t="s">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="F63" t="s">
         <v>12</v>
       </c>
       <c r="G63" t="s">
+        <v>12</v>
+      </c>
+      <c r="H63" t="s">
+        <v>119</v>
+      </c>
+      <c r="I63" t="s">
+        <v>38</v>
+      </c>
+      <c r="J63" t="s">
         <v>215</v>
       </c>
-      <c r="H63" t="s">
-        <v>38</v>
-      </c>
-      <c r="I63" t="s">
+      <c r="K63" t="s">
         <v>216</v>
-      </c>
-      <c r="J63" t="s">
-        <v>43</v>
-      </c>
-      <c r="K63" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="64" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="B64" t="s">
-        <v>12</v>
+        <v>60</v>
       </c>
       <c r="C64" t="s">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="D64" t="s">
         <v>96</v>
       </c>
       <c r="E64" t="s">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="F64" t="s">
         <v>12</v>
       </c>
       <c r="G64" t="s">
+        <v>12</v>
+      </c>
+      <c r="H64" t="s">
+        <v>52</v>
+      </c>
+      <c r="I64" t="s">
+        <v>46</v>
+      </c>
+      <c r="J64" t="s">
         <v>220</v>
       </c>
-      <c r="H64" t="s">
-        <v>46</v>
-      </c>
-      <c r="I64" t="s">
+      <c r="K64" t="s">
         <v>221</v>
-      </c>
-      <c r="J64" t="s">
-        <v>43</v>
-      </c>
-      <c r="K64" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="65" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>12</v>
+        <v>43</v>
       </c>
       <c r="B65" t="s">
-        <v>12</v>
+        <v>60</v>
       </c>
       <c r="C65" t="s">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="D65" t="s">
         <v>96</v>
       </c>
       <c r="E65" t="s">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="F65" t="s">
         <v>12</v>
       </c>
       <c r="G65" t="s">
+        <v>12</v>
+      </c>
+      <c r="H65" t="s">
+        <v>12</v>
+      </c>
+      <c r="I65" t="s">
+        <v>105</v>
+      </c>
+      <c r="J65" t="s">
         <v>171</v>
       </c>
-      <c r="H65" t="s">
-        <v>105</v>
-      </c>
-      <c r="I65" t="s">
+      <c r="K65" t="s">
         <v>228</v>
       </c>
-      <c r="J65" t="s">
-        <v>43</v>
-      </c>
-      <c r="K65" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="66" spans="1:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="66" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B66" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="C66" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D66" t="s">
         <v>96</v>
       </c>
       <c r="E66" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="F66" t="s">
         <v>12</v>
       </c>
       <c r="G66" t="s">
+        <v>12</v>
+      </c>
+      <c r="H66" t="s">
+        <v>20</v>
+      </c>
+      <c r="I66" t="s">
+        <v>98</v>
+      </c>
+      <c r="J66" t="s">
         <v>97</v>
       </c>
-      <c r="H66" t="s">
-        <v>98</v>
-      </c>
-      <c r="I66" t="s">
+      <c r="K66" t="s">
         <v>99</v>
-      </c>
-      <c r="J66" t="s">
-        <v>19</v>
-      </c>
-      <c r="K66" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="67" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="B67" t="s">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="C67" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D67" t="s">
         <v>96</v>
       </c>
       <c r="E67" t="s">
-        <v>49</v>
+        <v>12</v>
       </c>
       <c r="F67" t="s">
         <v>12</v>
       </c>
       <c r="G67" t="s">
+        <v>12</v>
+      </c>
+      <c r="H67" t="s">
+        <v>29</v>
+      </c>
+      <c r="I67" t="s">
+        <v>98</v>
+      </c>
+      <c r="J67" t="s">
         <v>159</v>
       </c>
-      <c r="H67" t="s">
-        <v>98</v>
-      </c>
-      <c r="I67" t="s">
+      <c r="K67" t="s">
         <v>268</v>
-      </c>
-      <c r="J67" t="s">
-        <v>43</v>
-      </c>
-      <c r="K67" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="68" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>12</v>
+        <v>43</v>
       </c>
       <c r="B68" t="s">
-        <v>12</v>
+        <v>56</v>
       </c>
       <c r="C68" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="D68" t="s">
         <v>96</v>
       </c>
       <c r="E68" t="s">
-        <v>49</v>
+        <v>12</v>
       </c>
       <c r="F68" t="s">
         <v>12</v>
       </c>
       <c r="G68" t="s">
+        <v>12</v>
+      </c>
+      <c r="H68" t="s">
+        <v>12</v>
+      </c>
+      <c r="I68" t="s">
+        <v>61</v>
+      </c>
+      <c r="J68" t="s">
         <v>97</v>
       </c>
-      <c r="H68" t="s">
-        <v>61</v>
-      </c>
-      <c r="I68" t="s">
+      <c r="K68" t="s">
         <v>277</v>
-      </c>
-      <c r="J68" t="s">
-        <v>43</v>
-      </c>
-      <c r="K68" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="69" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="B69" t="s">
-        <v>12</v>
+        <v>60</v>
       </c>
       <c r="C69" t="s">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="D69" t="s">
         <v>96</v>
       </c>
       <c r="E69" t="s">
+        <v>12</v>
+      </c>
+      <c r="F69" t="s">
+        <v>12</v>
+      </c>
+      <c r="G69" t="s">
+        <v>12</v>
+      </c>
+      <c r="H69" t="s">
+        <v>20</v>
+      </c>
+      <c r="I69" t="s">
+        <v>101</v>
+      </c>
+      <c r="J69" t="s">
+        <v>171</v>
+      </c>
+      <c r="K69" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="70" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>43</v>
+      </c>
+      <c r="B70" t="s">
+        <v>44</v>
+      </c>
+      <c r="C70" t="s">
         <v>45</v>
-      </c>
-      <c r="F69" t="s">
-        <v>12</v>
-      </c>
-      <c r="G69" t="s">
-        <v>171</v>
-      </c>
-      <c r="H69" t="s">
-        <v>101</v>
-      </c>
-      <c r="I69" t="s">
-        <v>285</v>
-      </c>
-      <c r="J69" t="s">
-        <v>43</v>
-      </c>
-      <c r="K69" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="70" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A70" t="s">
-        <v>20</v>
-      </c>
-      <c r="B70" t="s">
-        <v>12</v>
-      </c>
-      <c r="C70" t="s">
-        <v>44</v>
       </c>
       <c r="D70" t="s">
         <v>96</v>
       </c>
       <c r="E70" t="s">
-        <v>45</v>
+        <v>12</v>
       </c>
       <c r="F70" t="s">
         <v>12</v>
       </c>
       <c r="G70" t="s">
+        <v>12</v>
+      </c>
+      <c r="H70" t="s">
+        <v>20</v>
+      </c>
+      <c r="I70" t="s">
+        <v>193</v>
+      </c>
+      <c r="J70" t="s">
         <v>215</v>
       </c>
-      <c r="H70" t="s">
-        <v>193</v>
-      </c>
-      <c r="I70" t="s">
+      <c r="K70" t="s">
         <v>288</v>
       </c>
-      <c r="J70" t="s">
-        <v>43</v>
-      </c>
-      <c r="K70" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="71" spans="1:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="71" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>121</v>
+        <v>19</v>
       </c>
       <c r="B71" t="s">
-        <v>63</v>
+        <v>145</v>
       </c>
       <c r="C71" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D71" t="s">
         <v>93</v>
       </c>
       <c r="E71" t="s">
-        <v>146</v>
+        <v>12</v>
       </c>
       <c r="F71" t="s">
+        <v>63</v>
+      </c>
+      <c r="G71" t="s">
         <v>59</v>
       </c>
-      <c r="G71" t="s">
+      <c r="H71" t="s">
+        <v>121</v>
+      </c>
+      <c r="I71" t="s">
+        <v>133</v>
+      </c>
+      <c r="J71" t="s">
         <v>77</v>
       </c>
-      <c r="H71" t="s">
-        <v>133</v>
-      </c>
-      <c r="I71" t="s">
+      <c r="K71" t="s">
         <v>245</v>
       </c>
-      <c r="J71" t="s">
-        <v>19</v>
-      </c>
-      <c r="K71" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="72" spans="1:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="72" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>140</v>
+        <v>19</v>
       </c>
       <c r="B72" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C72" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D72" t="s">
         <v>93</v>
       </c>
       <c r="E72" t="s">
+        <v>12</v>
+      </c>
+      <c r="F72" t="s">
+        <v>12</v>
+      </c>
+      <c r="G72" t="s">
+        <v>29</v>
+      </c>
+      <c r="H72" t="s">
+        <v>140</v>
+      </c>
+      <c r="I72" t="s">
+        <v>24</v>
+      </c>
+      <c r="J72" t="s">
+        <v>191</v>
+      </c>
+      <c r="K72" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="73" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>19</v>
+      </c>
+      <c r="B73" t="s">
+        <v>200</v>
+      </c>
+      <c r="C73" t="s">
         <v>15</v>
-      </c>
-      <c r="F72" t="s">
-        <v>29</v>
-      </c>
-      <c r="G72" t="s">
-        <v>191</v>
-      </c>
-      <c r="H72" t="s">
-        <v>24</v>
-      </c>
-      <c r="I72" t="s">
-        <v>192</v>
-      </c>
-      <c r="J72" t="s">
-        <v>19</v>
-      </c>
-      <c r="K72" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="73" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A73" t="s">
-        <v>63</v>
-      </c>
-      <c r="B73" t="s">
-        <v>12</v>
-      </c>
-      <c r="C73" t="s">
-        <v>200</v>
       </c>
       <c r="D73" t="s">
         <v>93</v>
       </c>
       <c r="E73" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F73" t="s">
         <v>12</v>
       </c>
       <c r="G73" t="s">
+        <v>12</v>
+      </c>
+      <c r="H73" t="s">
+        <v>63</v>
+      </c>
+      <c r="I73" t="s">
+        <v>54</v>
+      </c>
+      <c r="J73" t="s">
         <v>94</v>
       </c>
-      <c r="H73" t="s">
-        <v>54</v>
-      </c>
-      <c r="I73" t="s">
+      <c r="K73" t="s">
         <v>206</v>
       </c>
-      <c r="J73" t="s">
-        <v>19</v>
-      </c>
-      <c r="K73" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="74" spans="1:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="74" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B74" t="s">
-        <v>12</v>
+        <v>125</v>
       </c>
       <c r="C74" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="D74" t="s">
         <v>93</v>
       </c>
       <c r="E74" t="s">
-        <v>123</v>
+        <v>12</v>
       </c>
       <c r="F74" t="s">
         <v>12</v>
       </c>
       <c r="G74" t="s">
+        <v>12</v>
+      </c>
+      <c r="H74" t="s">
+        <v>17</v>
+      </c>
+      <c r="I74" t="s">
+        <v>54</v>
+      </c>
+      <c r="J74" t="s">
         <v>94</v>
       </c>
-      <c r="H74" t="s">
-        <v>54</v>
-      </c>
-      <c r="I74" t="s">
+      <c r="K74" t="s">
         <v>139</v>
       </c>
-      <c r="J74" t="s">
-        <v>19</v>
-      </c>
-      <c r="K74" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="75" spans="1:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="75" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="B75" t="s">
-        <v>12</v>
+        <v>103</v>
       </c>
       <c r="C75" t="s">
-        <v>103</v>
+        <v>32</v>
       </c>
       <c r="D75" t="s">
         <v>93</v>
       </c>
       <c r="E75" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="F75" t="s">
+        <v>12</v>
+      </c>
+      <c r="G75" t="s">
         <v>29</v>
       </c>
-      <c r="G75" t="s">
+      <c r="H75" t="s">
+        <v>11</v>
+      </c>
+      <c r="I75" t="s">
+        <v>46</v>
+      </c>
+      <c r="J75" t="s">
         <v>94</v>
       </c>
-      <c r="H75" t="s">
-        <v>46</v>
-      </c>
-      <c r="I75" t="s">
+      <c r="K75" t="s">
         <v>116</v>
       </c>
-      <c r="J75" t="s">
-        <v>19</v>
-      </c>
-      <c r="K75" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="76" spans="1:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="76" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="B76" t="s">
-        <v>12</v>
+        <v>122</v>
       </c>
       <c r="C76" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D76" t="s">
         <v>93</v>
       </c>
       <c r="E76" t="s">
-        <v>123</v>
+        <v>12</v>
       </c>
       <c r="F76" t="s">
         <v>12</v>
       </c>
       <c r="G76" t="s">
+        <v>12</v>
+      </c>
+      <c r="H76" t="s">
+        <v>24</v>
+      </c>
+      <c r="I76" t="s">
+        <v>61</v>
+      </c>
+      <c r="J76" t="s">
         <v>161</v>
       </c>
-      <c r="H76" t="s">
-        <v>61</v>
-      </c>
-      <c r="I76" t="s">
+      <c r="K76" t="s">
         <v>170</v>
-      </c>
-      <c r="J76" t="s">
-        <v>19</v>
-      </c>
-      <c r="K76" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="77" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>12</v>
+        <v>43</v>
       </c>
       <c r="B77" t="s">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="C77" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D77" t="s">
         <v>93</v>
       </c>
       <c r="E77" t="s">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="F77" t="s">
         <v>12</v>
       </c>
       <c r="G77" t="s">
+        <v>12</v>
+      </c>
+      <c r="H77" t="s">
+        <v>12</v>
+      </c>
+      <c r="I77" t="s">
+        <v>101</v>
+      </c>
+      <c r="J77" t="s">
         <v>211</v>
       </c>
-      <c r="H77" t="s">
-        <v>101</v>
-      </c>
-      <c r="I77" t="s">
+      <c r="K77" t="s">
         <v>212</v>
-      </c>
-      <c r="J77" t="s">
-        <v>43</v>
-      </c>
-      <c r="K77" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="78" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>12</v>
+        <v>43</v>
       </c>
       <c r="B78" t="s">
-        <v>12</v>
+        <v>60</v>
       </c>
       <c r="C78" t="s">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="D78" t="s">
         <v>93</v>
       </c>
       <c r="E78" t="s">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="F78" t="s">
         <v>12</v>
       </c>
       <c r="G78" t="s">
+        <v>12</v>
+      </c>
+      <c r="H78" t="s">
+        <v>12</v>
+      </c>
+      <c r="I78" t="s">
+        <v>162</v>
+      </c>
+      <c r="J78" t="s">
         <v>161</v>
       </c>
-      <c r="H78" t="s">
-        <v>162</v>
-      </c>
-      <c r="I78" t="s">
+      <c r="K78" t="s">
         <v>219</v>
-      </c>
-      <c r="J78" t="s">
-        <v>43</v>
-      </c>
-      <c r="K78" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="79" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>12</v>
+        <v>43</v>
       </c>
       <c r="B79" t="s">
-        <v>12</v>
+        <v>60</v>
       </c>
       <c r="C79" t="s">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="D79" t="s">
         <v>93</v>
       </c>
       <c r="E79" t="s">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="F79" t="s">
         <v>12</v>
       </c>
       <c r="G79" t="s">
+        <v>12</v>
+      </c>
+      <c r="H79" t="s">
+        <v>12</v>
+      </c>
+      <c r="I79" t="s">
+        <v>226</v>
+      </c>
+      <c r="J79" t="s">
         <v>191</v>
       </c>
-      <c r="H79" t="s">
-        <v>226</v>
-      </c>
-      <c r="I79" t="s">
+      <c r="K79" t="s">
         <v>227</v>
       </c>
-      <c r="J79" t="s">
-        <v>43</v>
-      </c>
-      <c r="K79" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="80" spans="1:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="80" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="B80" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="C80" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D80" t="s">
         <v>93</v>
       </c>
       <c r="E80" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="F80" t="s">
         <v>12</v>
       </c>
       <c r="G80" t="s">
+        <v>12</v>
+      </c>
+      <c r="H80" t="s">
+        <v>29</v>
+      </c>
+      <c r="I80" t="s">
+        <v>81</v>
+      </c>
+      <c r="J80" t="s">
         <v>94</v>
       </c>
-      <c r="H80" t="s">
-        <v>81</v>
-      </c>
-      <c r="I80" t="s">
+      <c r="K80" t="s">
         <v>95</v>
-      </c>
-      <c r="J80" t="s">
-        <v>19</v>
-      </c>
-      <c r="K80" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="81" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>12</v>
+        <v>43</v>
       </c>
       <c r="B81" t="s">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="C81" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D81" t="s">
         <v>93</v>
       </c>
       <c r="E81" t="s">
-        <v>49</v>
+        <v>12</v>
       </c>
       <c r="F81" t="s">
         <v>12</v>
       </c>
       <c r="G81" t="s">
+        <v>12</v>
+      </c>
+      <c r="H81" t="s">
+        <v>12</v>
+      </c>
+      <c r="I81" t="s">
+        <v>98</v>
+      </c>
+      <c r="J81" t="s">
         <v>159</v>
       </c>
-      <c r="H81" t="s">
-        <v>98</v>
-      </c>
-      <c r="I81" t="s">
+      <c r="K81" t="s">
         <v>267</v>
-      </c>
-      <c r="J81" t="s">
-        <v>43</v>
-      </c>
-      <c r="K81" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="82" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>12</v>
+        <v>43</v>
       </c>
       <c r="B82" t="s">
-        <v>12</v>
+        <v>56</v>
       </c>
       <c r="C82" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="D82" t="s">
         <v>93</v>
       </c>
       <c r="E82" t="s">
-        <v>49</v>
+        <v>12</v>
       </c>
       <c r="F82" t="s">
         <v>12</v>
       </c>
       <c r="G82" t="s">
+        <v>12</v>
+      </c>
+      <c r="H82" t="s">
+        <v>12</v>
+      </c>
+      <c r="I82" t="s">
+        <v>57</v>
+      </c>
+      <c r="J82" t="s">
         <v>94</v>
       </c>
-      <c r="H82" t="s">
-        <v>57</v>
-      </c>
-      <c r="I82" t="s">
+      <c r="K82" t="s">
         <v>276</v>
-      </c>
-      <c r="J82" t="s">
-        <v>43</v>
-      </c>
-      <c r="K82" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="83" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>11</v>
+        <v>43</v>
       </c>
       <c r="B83" t="s">
-        <v>12</v>
+        <v>60</v>
       </c>
       <c r="C83" t="s">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="D83" t="s">
         <v>93</v>
       </c>
       <c r="E83" t="s">
+        <v>12</v>
+      </c>
+      <c r="F83" t="s">
+        <v>12</v>
+      </c>
+      <c r="G83" t="s">
+        <v>12</v>
+      </c>
+      <c r="H83" t="s">
+        <v>11</v>
+      </c>
+      <c r="I83" t="s">
+        <v>193</v>
+      </c>
+      <c r="J83" t="s">
+        <v>191</v>
+      </c>
+      <c r="K83" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="84" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>43</v>
+      </c>
+      <c r="B84" t="s">
+        <v>44</v>
+      </c>
+      <c r="C84" t="s">
         <v>45</v>
-      </c>
-      <c r="F83" t="s">
-        <v>12</v>
-      </c>
-      <c r="G83" t="s">
-        <v>191</v>
-      </c>
-      <c r="H83" t="s">
-        <v>193</v>
-      </c>
-      <c r="I83" t="s">
-        <v>286</v>
-      </c>
-      <c r="J83" t="s">
-        <v>43</v>
-      </c>
-      <c r="K83" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="84" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A84" t="s">
-        <v>52</v>
-      </c>
-      <c r="B84" t="s">
-        <v>12</v>
-      </c>
-      <c r="C84" t="s">
-        <v>44</v>
       </c>
       <c r="D84" t="s">
         <v>93</v>
       </c>
       <c r="E84" t="s">
-        <v>45</v>
+        <v>12</v>
       </c>
       <c r="F84" t="s">
         <v>12</v>
       </c>
       <c r="G84" t="s">
+        <v>12</v>
+      </c>
+      <c r="H84" t="s">
+        <v>52</v>
+      </c>
+      <c r="I84" t="s">
+        <v>17</v>
+      </c>
+      <c r="J84" t="s">
         <v>211</v>
       </c>
-      <c r="H84" t="s">
-        <v>17</v>
-      </c>
-      <c r="I84" t="s">
+      <c r="K84" t="s">
         <v>289</v>
       </c>
-      <c r="J84" t="s">
-        <v>43</v>
-      </c>
-      <c r="K84" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="85" spans="1:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="85" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>121</v>
+        <v>19</v>
       </c>
       <c r="B85" t="s">
-        <v>52</v>
+        <v>145</v>
       </c>
       <c r="C85" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D85" t="s">
         <v>90</v>
       </c>
       <c r="E85" t="s">
-        <v>146</v>
+        <v>12</v>
       </c>
       <c r="F85" t="s">
         <v>52</v>
       </c>
       <c r="G85" t="s">
+        <v>52</v>
+      </c>
+      <c r="H85" t="s">
+        <v>121</v>
+      </c>
+      <c r="I85" t="s">
+        <v>133</v>
+      </c>
+      <c r="J85" t="s">
         <v>77</v>
       </c>
-      <c r="H85" t="s">
-        <v>133</v>
-      </c>
-      <c r="I85" t="s">
+      <c r="K85" t="s">
         <v>244</v>
       </c>
-      <c r="J85" t="s">
-        <v>19</v>
-      </c>
-      <c r="K85" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="86" spans="1:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="86" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>54</v>
+        <v>19</v>
       </c>
       <c r="B86" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C86" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D86" t="s">
         <v>90</v>
       </c>
       <c r="E86" t="s">
+        <v>12</v>
+      </c>
+      <c r="F86" t="s">
+        <v>12</v>
+      </c>
+      <c r="G86" t="s">
+        <v>12</v>
+      </c>
+      <c r="H86" t="s">
+        <v>54</v>
+      </c>
+      <c r="I86" t="s">
+        <v>27</v>
+      </c>
+      <c r="J86" t="s">
+        <v>168</v>
+      </c>
+      <c r="K86" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="87" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>19</v>
+      </c>
+      <c r="B87" t="s">
+        <v>21</v>
+      </c>
+      <c r="C87" t="s">
         <v>15</v>
-      </c>
-      <c r="F86" t="s">
-        <v>12</v>
-      </c>
-      <c r="G86" t="s">
-        <v>168</v>
-      </c>
-      <c r="H86" t="s">
-        <v>27</v>
-      </c>
-      <c r="I86" t="s">
-        <v>190</v>
-      </c>
-      <c r="J86" t="s">
-        <v>19</v>
-      </c>
-      <c r="K86" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="87" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A87" t="s">
-        <v>59</v>
-      </c>
-      <c r="B87" t="s">
-        <v>12</v>
-      </c>
-      <c r="C87" t="s">
-        <v>21</v>
       </c>
       <c r="D87" t="s">
         <v>90</v>
       </c>
       <c r="E87" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F87" t="s">
+        <v>12</v>
+      </c>
+      <c r="G87" t="s">
         <v>29</v>
       </c>
-      <c r="G87" t="s">
+      <c r="H87" t="s">
+        <v>59</v>
+      </c>
+      <c r="I87" t="s">
+        <v>27</v>
+      </c>
+      <c r="J87" t="s">
         <v>91</v>
       </c>
-      <c r="H87" t="s">
-        <v>27</v>
-      </c>
-      <c r="I87" t="s">
+      <c r="K87" t="s">
         <v>205</v>
       </c>
-      <c r="J87" t="s">
-        <v>19</v>
-      </c>
-      <c r="K87" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="88" spans="1:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="88" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="B88" t="s">
-        <v>12</v>
+        <v>125</v>
       </c>
       <c r="C88" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="D88" t="s">
         <v>90</v>
       </c>
       <c r="E88" t="s">
-        <v>123</v>
+        <v>12</v>
       </c>
       <c r="F88" t="s">
         <v>12</v>
       </c>
       <c r="G88" t="s">
+        <v>12</v>
+      </c>
+      <c r="H88" t="s">
+        <v>11</v>
+      </c>
+      <c r="I88" t="s">
+        <v>46</v>
+      </c>
+      <c r="J88" t="s">
         <v>91</v>
       </c>
-      <c r="H88" t="s">
-        <v>46</v>
-      </c>
-      <c r="I88" t="s">
+      <c r="K88" t="s">
         <v>138</v>
       </c>
-      <c r="J88" t="s">
-        <v>19</v>
-      </c>
-      <c r="K88" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="89" spans="1:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="89" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>52</v>
+        <v>19</v>
       </c>
       <c r="B89" t="s">
-        <v>12</v>
+        <v>103</v>
       </c>
       <c r="C89" t="s">
-        <v>103</v>
+        <v>32</v>
       </c>
       <c r="D89" t="s">
         <v>90</v>
       </c>
       <c r="E89" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="F89" t="s">
         <v>12</v>
       </c>
       <c r="G89" t="s">
+        <v>12</v>
+      </c>
+      <c r="H89" t="s">
+        <v>52</v>
+      </c>
+      <c r="I89" t="s">
+        <v>105</v>
+      </c>
+      <c r="J89" t="s">
         <v>91</v>
       </c>
-      <c r="H89" t="s">
-        <v>105</v>
-      </c>
-      <c r="I89" t="s">
+      <c r="K89" t="s">
         <v>115</v>
       </c>
-      <c r="J89" t="s">
-        <v>19</v>
-      </c>
-      <c r="K89" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="90" spans="1:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="90" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="B90" t="s">
-        <v>12</v>
+        <v>122</v>
       </c>
       <c r="C90" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D90" t="s">
         <v>90</v>
       </c>
       <c r="E90" t="s">
-        <v>123</v>
+        <v>12</v>
       </c>
       <c r="F90" t="s">
         <v>12</v>
       </c>
       <c r="G90" t="s">
+        <v>12</v>
+      </c>
+      <c r="H90" t="s">
+        <v>27</v>
+      </c>
+      <c r="I90" t="s">
+        <v>65</v>
+      </c>
+      <c r="J90" t="s">
         <v>168</v>
       </c>
-      <c r="H90" t="s">
-        <v>65</v>
-      </c>
-      <c r="I90" t="s">
+      <c r="K90" t="s">
         <v>169</v>
-      </c>
-      <c r="J90" t="s">
-        <v>19</v>
-      </c>
-      <c r="K90" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="91" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>59</v>
+        <v>43</v>
       </c>
       <c r="B91" t="s">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="C91" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D91" t="s">
         <v>90</v>
       </c>
       <c r="E91" t="s">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="F91" t="s">
         <v>12</v>
       </c>
       <c r="G91" t="s">
+        <v>12</v>
+      </c>
+      <c r="H91" t="s">
+        <v>59</v>
+      </c>
+      <c r="I91" t="s">
+        <v>133</v>
+      </c>
+      <c r="J91" t="s">
         <v>213</v>
       </c>
-      <c r="H91" t="s">
-        <v>133</v>
-      </c>
-      <c r="I91" t="s">
+      <c r="K91" t="s">
         <v>214</v>
-      </c>
-      <c r="J91" t="s">
-        <v>43</v>
-      </c>
-      <c r="K91" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="92" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="B92" t="s">
-        <v>12</v>
+        <v>60</v>
       </c>
       <c r="C92" t="s">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="D92" t="s">
         <v>90</v>
       </c>
       <c r="E92" t="s">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="F92" t="s">
         <v>12</v>
       </c>
       <c r="G92" t="s">
+        <v>12</v>
+      </c>
+      <c r="H92" t="s">
+        <v>29</v>
+      </c>
+      <c r="I92" t="s">
+        <v>193</v>
+      </c>
+      <c r="J92" t="s">
         <v>168</v>
       </c>
-      <c r="H92" t="s">
-        <v>193</v>
-      </c>
-      <c r="I92" t="s">
+      <c r="K92" t="s">
         <v>224</v>
-      </c>
-      <c r="J92" t="s">
-        <v>43</v>
-      </c>
-      <c r="K92" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="93" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>12</v>
+        <v>43</v>
       </c>
       <c r="B93" t="s">
-        <v>12</v>
+        <v>60</v>
       </c>
       <c r="C93" t="s">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="D93" t="s">
         <v>90</v>
       </c>
       <c r="E93" t="s">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="F93" t="s">
         <v>12</v>
       </c>
       <c r="G93" t="s">
+        <v>12</v>
+      </c>
+      <c r="H93" t="s">
+        <v>12</v>
+      </c>
+      <c r="I93" t="s">
+        <v>57</v>
+      </c>
+      <c r="J93" t="s">
         <v>168</v>
       </c>
-      <c r="H93" t="s">
-        <v>57</v>
-      </c>
-      <c r="I93" t="s">
+      <c r="K93" t="s">
         <v>225</v>
       </c>
-      <c r="J93" t="s">
-        <v>43</v>
-      </c>
-      <c r="K93" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="94" spans="1:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="94" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="B94" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="C94" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D94" t="s">
         <v>90</v>
       </c>
       <c r="E94" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="F94" t="s">
         <v>12</v>
       </c>
       <c r="G94" t="s">
+        <v>12</v>
+      </c>
+      <c r="H94" t="s">
+        <v>12</v>
+      </c>
+      <c r="I94" t="s">
+        <v>34</v>
+      </c>
+      <c r="J94" t="s">
         <v>91</v>
       </c>
-      <c r="H94" t="s">
-        <v>34</v>
-      </c>
-      <c r="I94" t="s">
+      <c r="K94" t="s">
         <v>92</v>
-      </c>
-      <c r="J94" t="s">
-        <v>19</v>
-      </c>
-      <c r="K94" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="95" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>121</v>
+        <v>43</v>
       </c>
       <c r="B95" t="s">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="C95" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D95" t="s">
         <v>90</v>
       </c>
       <c r="E95" t="s">
-        <v>49</v>
+        <v>12</v>
       </c>
       <c r="F95" t="s">
         <v>12</v>
       </c>
       <c r="G95" t="s">
+        <v>12</v>
+      </c>
+      <c r="H95" t="s">
+        <v>121</v>
+      </c>
+      <c r="I95" t="s">
+        <v>46</v>
+      </c>
+      <c r="J95" t="s">
         <v>159</v>
       </c>
-      <c r="H95" t="s">
-        <v>46</v>
-      </c>
-      <c r="I95" t="s">
+      <c r="K95" t="s">
         <v>266</v>
-      </c>
-      <c r="J95" t="s">
-        <v>43</v>
-      </c>
-      <c r="K95" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="96" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>12</v>
+        <v>43</v>
       </c>
       <c r="B96" t="s">
-        <v>12</v>
+        <v>56</v>
       </c>
       <c r="C96" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="D96" t="s">
         <v>90</v>
       </c>
       <c r="E96" t="s">
-        <v>49</v>
+        <v>12</v>
       </c>
       <c r="F96" t="s">
         <v>12</v>
       </c>
       <c r="G96" t="s">
+        <v>12</v>
+      </c>
+      <c r="H96" t="s">
+        <v>12</v>
+      </c>
+      <c r="I96" t="s">
+        <v>65</v>
+      </c>
+      <c r="J96" t="s">
         <v>91</v>
       </c>
-      <c r="H96" t="s">
-        <v>65</v>
-      </c>
-      <c r="I96" t="s">
+      <c r="K96" t="s">
         <v>275</v>
-      </c>
-      <c r="J96" t="s">
-        <v>43</v>
-      </c>
-      <c r="K96" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="97" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>11</v>
+        <v>43</v>
       </c>
       <c r="B97" t="s">
-        <v>12</v>
+        <v>60</v>
       </c>
       <c r="C97" t="s">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="D97" t="s">
         <v>90</v>
       </c>
       <c r="E97" t="s">
+        <v>12</v>
+      </c>
+      <c r="F97" t="s">
+        <v>12</v>
+      </c>
+      <c r="G97" t="s">
+        <v>12</v>
+      </c>
+      <c r="H97" t="s">
+        <v>11</v>
+      </c>
+      <c r="I97" t="s">
+        <v>162</v>
+      </c>
+      <c r="J97" t="s">
+        <v>168</v>
+      </c>
+      <c r="K97" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="98" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>43</v>
+      </c>
+      <c r="B98" t="s">
+        <v>44</v>
+      </c>
+      <c r="C98" t="s">
         <v>45</v>
-      </c>
-      <c r="F97" t="s">
-        <v>12</v>
-      </c>
-      <c r="G97" t="s">
-        <v>168</v>
-      </c>
-      <c r="H97" t="s">
-        <v>162</v>
-      </c>
-      <c r="I97" t="s">
-        <v>287</v>
-      </c>
-      <c r="J97" t="s">
-        <v>43</v>
-      </c>
-      <c r="K97" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="98" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A98" t="s">
-        <v>24</v>
-      </c>
-      <c r="B98" t="s">
-        <v>12</v>
-      </c>
-      <c r="C98" t="s">
-        <v>44</v>
       </c>
       <c r="D98" t="s">
         <v>90</v>
       </c>
       <c r="E98" t="s">
-        <v>45</v>
+        <v>12</v>
       </c>
       <c r="F98" t="s">
         <v>12</v>
       </c>
       <c r="G98" t="s">
+        <v>12</v>
+      </c>
+      <c r="H98" t="s">
+        <v>24</v>
+      </c>
+      <c r="I98" t="s">
+        <v>41</v>
+      </c>
+      <c r="J98" t="s">
         <v>112</v>
       </c>
-      <c r="H98" t="s">
-        <v>41</v>
-      </c>
-      <c r="I98" t="s">
+      <c r="K98" t="s">
         <v>292</v>
       </c>
-      <c r="J98" t="s">
-        <v>43</v>
-      </c>
-      <c r="K98" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="99" spans="1:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="99" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="B99" t="s">
-        <v>63</v>
+        <v>145</v>
       </c>
       <c r="C99" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D99" t="s">
         <v>86</v>
       </c>
       <c r="E99" t="s">
-        <v>146</v>
+        <v>12</v>
       </c>
       <c r="F99" t="s">
+        <v>63</v>
+      </c>
+      <c r="G99" t="s">
         <v>52</v>
       </c>
-      <c r="G99" t="s">
+      <c r="H99" t="s">
+        <v>24</v>
+      </c>
+      <c r="I99" t="s">
+        <v>119</v>
+      </c>
+      <c r="J99" t="s">
         <v>77</v>
       </c>
-      <c r="H99" t="s">
-        <v>119</v>
-      </c>
-      <c r="I99" t="s">
+      <c r="K99" t="s">
         <v>243</v>
       </c>
-      <c r="J99" t="s">
-        <v>19</v>
-      </c>
-      <c r="K99" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="100" spans="1:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="100" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>140</v>
+        <v>19</v>
       </c>
       <c r="B100" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C100" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D100" t="s">
         <v>86</v>
       </c>
       <c r="E100" t="s">
+        <v>12</v>
+      </c>
+      <c r="F100" t="s">
+        <v>12</v>
+      </c>
+      <c r="G100" t="s">
+        <v>12</v>
+      </c>
+      <c r="H100" t="s">
+        <v>140</v>
+      </c>
+      <c r="I100" t="s">
+        <v>24</v>
+      </c>
+      <c r="J100" t="s">
+        <v>166</v>
+      </c>
+      <c r="K100" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="101" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>19</v>
+      </c>
+      <c r="B101" t="s">
+        <v>21</v>
+      </c>
+      <c r="C101" t="s">
         <v>15</v>
-      </c>
-      <c r="F100" t="s">
-        <v>12</v>
-      </c>
-      <c r="G100" t="s">
-        <v>166</v>
-      </c>
-      <c r="H100" t="s">
-        <v>24</v>
-      </c>
-      <c r="I100" t="s">
-        <v>189</v>
-      </c>
-      <c r="J100" t="s">
-        <v>19</v>
-      </c>
-      <c r="K100" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="101" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A101" t="s">
-        <v>63</v>
-      </c>
-      <c r="B101" t="s">
-        <v>12</v>
-      </c>
-      <c r="C101" t="s">
-        <v>21</v>
       </c>
       <c r="D101" t="s">
         <v>86</v>
       </c>
       <c r="E101" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F101" t="s">
         <v>12</v>
       </c>
       <c r="G101" t="s">
+        <v>12</v>
+      </c>
+      <c r="H101" t="s">
+        <v>63</v>
+      </c>
+      <c r="I101" t="s">
+        <v>11</v>
+      </c>
+      <c r="J101" t="s">
         <v>87</v>
       </c>
-      <c r="H101" t="s">
-        <v>11</v>
-      </c>
-      <c r="I101" t="s">
+      <c r="K101" t="s">
         <v>204</v>
       </c>
-      <c r="J101" t="s">
-        <v>19</v>
-      </c>
-      <c r="K101" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="102" spans="1:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="102" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>63</v>
+        <v>19</v>
       </c>
       <c r="B102" t="s">
-        <v>12</v>
+        <v>125</v>
       </c>
       <c r="C102" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="D102" t="s">
         <v>86</v>
       </c>
       <c r="E102" t="s">
-        <v>123</v>
+        <v>12</v>
       </c>
       <c r="F102" t="s">
         <v>12</v>
       </c>
       <c r="G102" t="s">
+        <v>12</v>
+      </c>
+      <c r="H102" t="s">
+        <v>63</v>
+      </c>
+      <c r="I102" t="s">
+        <v>105</v>
+      </c>
+      <c r="J102" t="s">
         <v>87</v>
       </c>
-      <c r="H102" t="s">
-        <v>105</v>
-      </c>
-      <c r="I102" t="s">
+      <c r="K102" t="s">
         <v>137</v>
       </c>
-      <c r="J102" t="s">
-        <v>19</v>
-      </c>
-      <c r="K102" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="103" spans="1:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="103" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="B103" t="s">
-        <v>12</v>
+        <v>103</v>
       </c>
       <c r="C103" t="s">
-        <v>103</v>
+        <v>32</v>
       </c>
       <c r="D103" t="s">
         <v>86</v>
       </c>
       <c r="E103" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="F103" t="s">
         <v>12</v>
       </c>
       <c r="G103" t="s">
+        <v>12</v>
+      </c>
+      <c r="H103" t="s">
+        <v>29</v>
+      </c>
+      <c r="I103" t="s">
+        <v>105</v>
+      </c>
+      <c r="J103" t="s">
         <v>87</v>
       </c>
-      <c r="H103" t="s">
-        <v>105</v>
-      </c>
-      <c r="I103" t="s">
+      <c r="K103" t="s">
         <v>114</v>
       </c>
-      <c r="J103" t="s">
-        <v>19</v>
-      </c>
-      <c r="K103" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="104" spans="1:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="104" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="B104" t="s">
-        <v>12</v>
+        <v>122</v>
       </c>
       <c r="C104" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D104" t="s">
         <v>86</v>
       </c>
       <c r="E104" t="s">
-        <v>123</v>
+        <v>12</v>
       </c>
       <c r="F104" t="s">
         <v>12</v>
       </c>
       <c r="G104" t="s">
+        <v>12</v>
+      </c>
+      <c r="H104" t="s">
+        <v>27</v>
+      </c>
+      <c r="I104" t="s">
+        <v>101</v>
+      </c>
+      <c r="J104" t="s">
         <v>166</v>
       </c>
-      <c r="H104" t="s">
-        <v>101</v>
-      </c>
-      <c r="I104" t="s">
+      <c r="K104" t="s">
         <v>167</v>
       </c>
-      <c r="J104" t="s">
-        <v>19</v>
-      </c>
-      <c r="K104" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="105" spans="1:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="105" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>59</v>
+        <v>19</v>
       </c>
       <c r="B105" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="C105" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D105" t="s">
         <v>86</v>
       </c>
       <c r="E105" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="F105" t="s">
         <v>12</v>
       </c>
       <c r="G105" t="s">
+        <v>12</v>
+      </c>
+      <c r="H105" t="s">
+        <v>59</v>
+      </c>
+      <c r="I105" t="s">
+        <v>88</v>
+      </c>
+      <c r="J105" t="s">
         <v>87</v>
       </c>
-      <c r="H105" t="s">
-        <v>88</v>
-      </c>
-      <c r="I105" t="s">
+      <c r="K105" t="s">
         <v>89</v>
-      </c>
-      <c r="J105" t="s">
-        <v>19</v>
-      </c>
-      <c r="K105" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="106" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>59</v>
+        <v>43</v>
       </c>
       <c r="B106" t="s">
-        <v>12</v>
+        <v>60</v>
       </c>
       <c r="C106" t="s">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="D106" t="s">
         <v>86</v>
       </c>
       <c r="E106" t="s">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="F106" t="s">
         <v>12</v>
       </c>
       <c r="G106" t="s">
+        <v>12</v>
+      </c>
+      <c r="H106" t="s">
+        <v>59</v>
+      </c>
+      <c r="I106" t="s">
+        <v>101</v>
+      </c>
+      <c r="J106" t="s">
         <v>166</v>
       </c>
-      <c r="H106" t="s">
-        <v>101</v>
-      </c>
-      <c r="I106" t="s">
+      <c r="K106" t="s">
         <v>256</v>
-      </c>
-      <c r="J106" t="s">
-        <v>43</v>
-      </c>
-      <c r="K106" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="107" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="B107" t="s">
-        <v>12</v>
+        <v>60</v>
       </c>
       <c r="C107" t="s">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="D107" t="s">
         <v>86</v>
       </c>
       <c r="E107" t="s">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="F107" t="s">
         <v>12</v>
       </c>
       <c r="G107" t="s">
+        <v>12</v>
+      </c>
+      <c r="H107" t="s">
+        <v>52</v>
+      </c>
+      <c r="I107" t="s">
+        <v>108</v>
+      </c>
+      <c r="J107" t="s">
         <v>166</v>
       </c>
-      <c r="H107" t="s">
-        <v>108</v>
-      </c>
-      <c r="I107" t="s">
+      <c r="K107" t="s">
         <v>257</v>
-      </c>
-      <c r="J107" t="s">
-        <v>43</v>
-      </c>
-      <c r="K107" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="108" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="B108" t="s">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="C108" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D108" t="s">
         <v>86</v>
       </c>
       <c r="E108" t="s">
-        <v>49</v>
+        <v>12</v>
       </c>
       <c r="F108" t="s">
         <v>12</v>
       </c>
       <c r="G108" t="s">
+        <v>12</v>
+      </c>
+      <c r="H108" t="s">
+        <v>38</v>
+      </c>
+      <c r="I108" t="s">
+        <v>46</v>
+      </c>
+      <c r="J108" t="s">
         <v>159</v>
       </c>
-      <c r="H108" t="s">
-        <v>46</v>
-      </c>
-      <c r="I108" t="s">
+      <c r="K108" t="s">
         <v>265</v>
-      </c>
-      <c r="J108" t="s">
-        <v>43</v>
-      </c>
-      <c r="K108" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="109" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>12</v>
+        <v>43</v>
       </c>
       <c r="B109" t="s">
-        <v>12</v>
+        <v>56</v>
       </c>
       <c r="C109" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="D109" t="s">
         <v>86</v>
       </c>
       <c r="E109" t="s">
-        <v>49</v>
+        <v>12</v>
       </c>
       <c r="F109" t="s">
         <v>12</v>
       </c>
       <c r="G109" t="s">
+        <v>12</v>
+      </c>
+      <c r="H109" t="s">
+        <v>12</v>
+      </c>
+      <c r="I109" t="s">
+        <v>57</v>
+      </c>
+      <c r="J109" t="s">
         <v>87</v>
       </c>
-      <c r="H109" t="s">
-        <v>57</v>
-      </c>
-      <c r="I109" t="s">
+      <c r="K109" t="s">
         <v>274</v>
       </c>
-      <c r="J109" t="s">
-        <v>43</v>
-      </c>
-      <c r="K109" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="110" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="110" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="B110" t="s">
-        <v>12</v>
+        <v>44</v>
       </c>
       <c r="C110" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D110" t="s">
         <v>86</v>
       </c>
       <c r="E110" t="s">
-        <v>45</v>
+        <v>12</v>
       </c>
       <c r="F110" t="s">
         <v>12</v>
       </c>
       <c r="G110" t="s">
+        <v>12</v>
+      </c>
+      <c r="H110" t="s">
+        <v>38</v>
+      </c>
+      <c r="I110" t="s">
+        <v>193</v>
+      </c>
+      <c r="J110" t="s">
         <v>132</v>
       </c>
-      <c r="H110" t="s">
-        <v>193</v>
-      </c>
-      <c r="I110" t="s">
+      <c r="K110" t="s">
         <v>279</v>
-      </c>
-      <c r="J110" t="s">
-        <v>43</v>
-      </c>
-      <c r="K110" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="111" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="B111" t="s">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="C111" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D111" t="s">
         <v>86</v>
       </c>
       <c r="E111" t="s">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="F111" t="s">
         <v>12</v>
       </c>
       <c r="G111" t="s">
+        <v>12</v>
+      </c>
+      <c r="H111" t="s">
+        <v>20</v>
+      </c>
+      <c r="I111" t="s">
+        <v>119</v>
+      </c>
+      <c r="J111" t="s">
         <v>283</v>
       </c>
-      <c r="H111" t="s">
-        <v>119</v>
-      </c>
-      <c r="I111" t="s">
+      <c r="K111" t="s">
         <v>284</v>
-      </c>
-      <c r="J111" t="s">
-        <v>43</v>
-      </c>
-      <c r="K111" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="112" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="B112" t="s">
-        <v>12</v>
+        <v>60</v>
       </c>
       <c r="C112" t="s">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="D112" t="s">
         <v>86</v>
       </c>
       <c r="E112" t="s">
-        <v>45</v>
+        <v>12</v>
       </c>
       <c r="F112" t="s">
         <v>12</v>
       </c>
       <c r="G112" t="s">
+        <v>12</v>
+      </c>
+      <c r="H112" t="s">
+        <v>27</v>
+      </c>
+      <c r="I112" t="s">
+        <v>108</v>
+      </c>
+      <c r="J112" t="s">
         <v>166</v>
       </c>
-      <c r="H112" t="s">
-        <v>108</v>
-      </c>
-      <c r="I112" t="s">
+      <c r="K112" t="s">
         <v>290</v>
       </c>
-      <c r="J112" t="s">
-        <v>43</v>
-      </c>
-      <c r="K112" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="113" spans="1:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="113" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="B113" t="s">
-        <v>52</v>
+        <v>145</v>
       </c>
       <c r="C113" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D113" t="s">
         <v>83</v>
       </c>
       <c r="E113" t="s">
-        <v>146</v>
+        <v>12</v>
       </c>
       <c r="F113" t="s">
         <v>52</v>
       </c>
       <c r="G113" t="s">
+        <v>52</v>
+      </c>
+      <c r="H113" t="s">
+        <v>24</v>
+      </c>
+      <c r="I113" t="s">
+        <v>193</v>
+      </c>
+      <c r="J113" t="s">
         <v>77</v>
       </c>
-      <c r="H113" t="s">
-        <v>193</v>
-      </c>
-      <c r="I113" t="s">
+      <c r="K113" t="s">
         <v>242</v>
       </c>
-      <c r="J113" t="s">
-        <v>19</v>
-      </c>
-      <c r="K113" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="114" spans="1:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="114" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>63</v>
+        <v>19</v>
       </c>
       <c r="B114" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C114" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D114" t="s">
         <v>83</v>
       </c>
       <c r="E114" t="s">
+        <v>12</v>
+      </c>
+      <c r="F114" t="s">
+        <v>12</v>
+      </c>
+      <c r="G114" t="s">
+        <v>52</v>
+      </c>
+      <c r="H114" t="s">
+        <v>63</v>
+      </c>
+      <c r="I114" t="s">
+        <v>54</v>
+      </c>
+      <c r="J114" t="s">
+        <v>164</v>
+      </c>
+      <c r="K114" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="115" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>19</v>
+      </c>
+      <c r="B115" t="s">
+        <v>21</v>
+      </c>
+      <c r="C115" t="s">
         <v>15</v>
-      </c>
-      <c r="F114" t="s">
-        <v>52</v>
-      </c>
-      <c r="G114" t="s">
-        <v>164</v>
-      </c>
-      <c r="H114" t="s">
-        <v>54</v>
-      </c>
-      <c r="I114" t="s">
-        <v>188</v>
-      </c>
-      <c r="J114" t="s">
-        <v>19</v>
-      </c>
-      <c r="K114" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="115" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A115" t="s">
-        <v>38</v>
-      </c>
-      <c r="B115" t="s">
-        <v>12</v>
-      </c>
-      <c r="C115" t="s">
-        <v>21</v>
       </c>
       <c r="D115" t="s">
         <v>83</v>
       </c>
       <c r="E115" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F115" t="s">
+        <v>12</v>
+      </c>
+      <c r="G115" t="s">
         <v>52</v>
       </c>
-      <c r="G115" t="s">
+      <c r="H115" t="s">
+        <v>38</v>
+      </c>
+      <c r="I115" t="s">
+        <v>59</v>
+      </c>
+      <c r="J115" t="s">
         <v>135</v>
       </c>
-      <c r="H115" t="s">
-        <v>59</v>
-      </c>
-      <c r="I115" t="s">
+      <c r="K115" t="s">
         <v>203</v>
       </c>
-      <c r="J115" t="s">
-        <v>19</v>
-      </c>
-      <c r="K115" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="116" spans="1:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="116" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="B116" t="s">
-        <v>12</v>
+        <v>125</v>
       </c>
       <c r="C116" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="D116" t="s">
         <v>83</v>
       </c>
       <c r="E116" t="s">
-        <v>123</v>
+        <v>12</v>
       </c>
       <c r="F116" t="s">
+        <v>12</v>
+      </c>
+      <c r="G116" t="s">
         <v>29</v>
       </c>
-      <c r="G116" t="s">
+      <c r="H116" t="s">
+        <v>29</v>
+      </c>
+      <c r="I116" t="s">
+        <v>65</v>
+      </c>
+      <c r="J116" t="s">
         <v>135</v>
       </c>
-      <c r="H116" t="s">
-        <v>65</v>
-      </c>
-      <c r="I116" t="s">
+      <c r="K116" t="s">
         <v>136</v>
       </c>
-      <c r="J116" t="s">
-        <v>19</v>
-      </c>
-      <c r="K116" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="117" spans="1:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="117" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="B117" t="s">
-        <v>12</v>
+        <v>103</v>
       </c>
       <c r="C117" t="s">
-        <v>103</v>
+        <v>32</v>
       </c>
       <c r="D117" t="s">
         <v>83</v>
       </c>
       <c r="E117" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="F117" t="s">
         <v>12</v>
       </c>
       <c r="G117" t="s">
+        <v>12</v>
+      </c>
+      <c r="H117" t="s">
+        <v>12</v>
+      </c>
+      <c r="I117" t="s">
+        <v>65</v>
+      </c>
+      <c r="J117" t="s">
         <v>112</v>
       </c>
-      <c r="H117" t="s">
-        <v>65</v>
-      </c>
-      <c r="I117" t="s">
+      <c r="K117" t="s">
         <v>113</v>
       </c>
-      <c r="J117" t="s">
-        <v>19</v>
-      </c>
-      <c r="K117" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="118" spans="1:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="118" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="B118" t="s">
-        <v>12</v>
+        <v>122</v>
       </c>
       <c r="C118" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D118" t="s">
         <v>83</v>
       </c>
       <c r="E118" t="s">
-        <v>123</v>
+        <v>12</v>
       </c>
       <c r="F118" t="s">
         <v>12</v>
       </c>
       <c r="G118" t="s">
+        <v>12</v>
+      </c>
+      <c r="H118" t="s">
+        <v>11</v>
+      </c>
+      <c r="I118" t="s">
+        <v>61</v>
+      </c>
+      <c r="J118" t="s">
         <v>164</v>
       </c>
-      <c r="H118" t="s">
-        <v>61</v>
-      </c>
-      <c r="I118" t="s">
+      <c r="K118" t="s">
         <v>165</v>
       </c>
-      <c r="J118" t="s">
-        <v>19</v>
-      </c>
-      <c r="K118" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="119" spans="1:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="119" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="B119" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="C119" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D119" t="s">
         <v>83</v>
       </c>
       <c r="E119" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="F119" t="s">
         <v>12</v>
       </c>
       <c r="G119" t="s">
+        <v>12</v>
+      </c>
+      <c r="H119" t="s">
+        <v>12</v>
+      </c>
+      <c r="I119" t="s">
+        <v>81</v>
+      </c>
+      <c r="J119" t="s">
         <v>84</v>
       </c>
-      <c r="H119" t="s">
-        <v>81</v>
-      </c>
-      <c r="I119" t="s">
+      <c r="K119" t="s">
         <v>85</v>
-      </c>
-      <c r="J119" t="s">
-        <v>19</v>
-      </c>
-      <c r="K119" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="120" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>59</v>
+        <v>43</v>
       </c>
       <c r="B120" t="s">
-        <v>12</v>
+        <v>60</v>
       </c>
       <c r="C120" t="s">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="D120" t="s">
         <v>83</v>
       </c>
       <c r="E120" t="s">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="F120" t="s">
         <v>12</v>
       </c>
       <c r="G120" t="s">
+        <v>12</v>
+      </c>
+      <c r="H120" t="s">
+        <v>59</v>
+      </c>
+      <c r="I120" t="s">
+        <v>108</v>
+      </c>
+      <c r="J120" t="s">
         <v>161</v>
       </c>
-      <c r="H120" t="s">
-        <v>108</v>
-      </c>
-      <c r="I120" t="s">
+      <c r="K120" t="s">
         <v>255</v>
       </c>
-      <c r="J120" t="s">
-        <v>43</v>
-      </c>
-      <c r="K120" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="121" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="121" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>63</v>
+        <v>43</v>
       </c>
       <c r="B121" t="s">
-        <v>12</v>
+        <v>44</v>
       </c>
       <c r="C121" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D121" t="s">
         <v>83</v>
       </c>
       <c r="E121" t="s">
-        <v>45</v>
+        <v>12</v>
       </c>
       <c r="F121" t="s">
         <v>12</v>
       </c>
       <c r="G121" t="s">
+        <v>12</v>
+      </c>
+      <c r="H121" t="s">
+        <v>63</v>
+      </c>
+      <c r="I121" t="s">
+        <v>46</v>
+      </c>
+      <c r="J121" t="s">
         <v>258</v>
       </c>
-      <c r="H121" t="s">
-        <v>46</v>
-      </c>
-      <c r="I121" t="s">
+      <c r="K121" t="s">
         <v>261</v>
-      </c>
-      <c r="J121" t="s">
-        <v>43</v>
-      </c>
-      <c r="K121" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="122" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>121</v>
+        <v>43</v>
       </c>
       <c r="B122" t="s">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="C122" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D122" t="s">
         <v>83</v>
       </c>
       <c r="E122" t="s">
-        <v>49</v>
+        <v>12</v>
       </c>
       <c r="F122" t="s">
         <v>12</v>
       </c>
       <c r="G122" t="s">
+        <v>12</v>
+      </c>
+      <c r="H122" t="s">
+        <v>121</v>
+      </c>
+      <c r="I122" t="s">
+        <v>133</v>
+      </c>
+      <c r="J122" t="s">
         <v>157</v>
       </c>
-      <c r="H122" t="s">
-        <v>133</v>
-      </c>
-      <c r="I122" t="s">
+      <c r="K122" t="s">
         <v>264</v>
-      </c>
-      <c r="J122" t="s">
-        <v>43</v>
-      </c>
-      <c r="K122" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="123" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>12</v>
+        <v>43</v>
       </c>
       <c r="B123" t="s">
-        <v>12</v>
+        <v>56</v>
       </c>
       <c r="C123" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="D123" t="s">
         <v>83</v>
       </c>
       <c r="E123" t="s">
-        <v>49</v>
+        <v>12</v>
       </c>
       <c r="F123" t="s">
         <v>12</v>
       </c>
       <c r="G123" t="s">
+        <v>12</v>
+      </c>
+      <c r="H123" t="s">
+        <v>12</v>
+      </c>
+      <c r="I123" t="s">
+        <v>65</v>
+      </c>
+      <c r="J123" t="s">
         <v>135</v>
       </c>
-      <c r="H123" t="s">
-        <v>65</v>
-      </c>
-      <c r="I123" t="s">
+      <c r="K123" t="s">
         <v>273</v>
-      </c>
-      <c r="J123" t="s">
-        <v>43</v>
-      </c>
-      <c r="K123" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="124" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>59</v>
+        <v>43</v>
       </c>
       <c r="B124" t="s">
-        <v>12</v>
+        <v>60</v>
       </c>
       <c r="C124" t="s">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="D124" t="s">
         <v>83</v>
       </c>
       <c r="E124" t="s">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="F124" t="s">
         <v>12</v>
       </c>
       <c r="G124" t="s">
+        <v>12</v>
+      </c>
+      <c r="H124" t="s">
+        <v>59</v>
+      </c>
+      <c r="I124" t="s">
+        <v>133</v>
+      </c>
+      <c r="J124" t="s">
         <v>161</v>
       </c>
-      <c r="H124" t="s">
-        <v>133</v>
-      </c>
-      <c r="I124" t="s">
+      <c r="K124" t="s">
         <v>281</v>
-      </c>
-      <c r="J124" t="s">
-        <v>43</v>
-      </c>
-      <c r="K124" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="125" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>59</v>
+        <v>43</v>
       </c>
       <c r="B125" t="s">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="C125" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D125" t="s">
         <v>83</v>
       </c>
       <c r="E125" t="s">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="F125" t="s">
         <v>12</v>
       </c>
       <c r="G125" t="s">
+        <v>12</v>
+      </c>
+      <c r="H125" t="s">
+        <v>59</v>
+      </c>
+      <c r="I125" t="s">
+        <v>193</v>
+      </c>
+      <c r="J125" t="s">
         <v>112</v>
       </c>
-      <c r="H125" t="s">
-        <v>193</v>
-      </c>
-      <c r="I125" t="s">
+      <c r="K125" t="s">
         <v>282</v>
-      </c>
-      <c r="J125" t="s">
-        <v>43</v>
-      </c>
-      <c r="K125" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="126" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>12</v>
+        <v>43</v>
       </c>
       <c r="B126" t="s">
-        <v>12</v>
+        <v>60</v>
       </c>
       <c r="C126" t="s">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="D126" t="s">
         <v>83</v>
       </c>
       <c r="E126" t="s">
-        <v>45</v>
+        <v>12</v>
       </c>
       <c r="F126" t="s">
         <v>12</v>
       </c>
       <c r="G126" t="s">
+        <v>12</v>
+      </c>
+      <c r="H126" t="s">
+        <v>12</v>
+      </c>
+      <c r="I126" t="s">
+        <v>226</v>
+      </c>
+      <c r="J126" t="s">
         <v>135</v>
       </c>
-      <c r="H126" t="s">
-        <v>226</v>
-      </c>
-      <c r="I126" t="s">
+      <c r="K126" t="s">
         <v>291</v>
       </c>
-      <c r="J126" t="s">
-        <v>43</v>
-      </c>
-      <c r="K126" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="127" spans="1:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="127" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="B127" t="s">
-        <v>63</v>
+        <v>145</v>
       </c>
       <c r="C127" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D127" t="s">
         <v>79</v>
       </c>
       <c r="E127" t="s">
-        <v>146</v>
+        <v>12</v>
       </c>
       <c r="F127" t="s">
+        <v>63</v>
+      </c>
+      <c r="G127" t="s">
         <v>52</v>
       </c>
-      <c r="G127" t="s">
+      <c r="H127" t="s">
+        <v>24</v>
+      </c>
+      <c r="I127" t="s">
+        <v>193</v>
+      </c>
+      <c r="J127" t="s">
         <v>77</v>
       </c>
-      <c r="H127" t="s">
-        <v>193</v>
-      </c>
-      <c r="I127" t="s">
+      <c r="K127" t="s">
         <v>241</v>
       </c>
-      <c r="J127" t="s">
-        <v>19</v>
-      </c>
-      <c r="K127" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="128" spans="1:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="128" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>52</v>
+        <v>19</v>
       </c>
       <c r="B128" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C128" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D128" t="s">
         <v>79</v>
       </c>
       <c r="E128" t="s">
+        <v>12</v>
+      </c>
+      <c r="F128" t="s">
+        <v>12</v>
+      </c>
+      <c r="G128" t="s">
+        <v>29</v>
+      </c>
+      <c r="H128" t="s">
+        <v>52</v>
+      </c>
+      <c r="I128" t="s">
+        <v>41</v>
+      </c>
+      <c r="J128" t="s">
+        <v>161</v>
+      </c>
+      <c r="K128" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="129" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A129" t="s">
+        <v>19</v>
+      </c>
+      <c r="B129" t="s">
+        <v>21</v>
+      </c>
+      <c r="C129" t="s">
         <v>15</v>
-      </c>
-      <c r="F128" t="s">
-        <v>29</v>
-      </c>
-      <c r="G128" t="s">
-        <v>161</v>
-      </c>
-      <c r="H128" t="s">
-        <v>41</v>
-      </c>
-      <c r="I128" t="s">
-        <v>187</v>
-      </c>
-      <c r="J128" t="s">
-        <v>19</v>
-      </c>
-      <c r="K128" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="129" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A129" t="s">
-        <v>63</v>
-      </c>
-      <c r="B129" t="s">
-        <v>12</v>
-      </c>
-      <c r="C129" t="s">
-        <v>21</v>
       </c>
       <c r="D129" t="s">
         <v>79</v>
       </c>
       <c r="E129" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F129" t="s">
         <v>12</v>
       </c>
       <c r="G129" t="s">
+        <v>12</v>
+      </c>
+      <c r="H129" t="s">
+        <v>63</v>
+      </c>
+      <c r="I129" t="s">
+        <v>24</v>
+      </c>
+      <c r="J129" t="s">
         <v>80</v>
       </c>
-      <c r="H129" t="s">
-        <v>24</v>
-      </c>
-      <c r="I129" t="s">
+      <c r="K129" t="s">
         <v>202</v>
       </c>
-      <c r="J129" t="s">
-        <v>19</v>
-      </c>
-      <c r="K129" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="130" spans="1:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="130" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>121</v>
+        <v>19</v>
       </c>
       <c r="B130" t="s">
-        <v>12</v>
+        <v>125</v>
       </c>
       <c r="C130" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="D130" t="s">
         <v>79</v>
       </c>
       <c r="E130" t="s">
-        <v>123</v>
+        <v>12</v>
       </c>
       <c r="F130" t="s">
         <v>12</v>
       </c>
       <c r="G130" t="s">
+        <v>12</v>
+      </c>
+      <c r="H130" t="s">
+        <v>121</v>
+      </c>
+      <c r="I130" t="s">
+        <v>133</v>
+      </c>
+      <c r="J130" t="s">
         <v>132</v>
       </c>
-      <c r="H130" t="s">
-        <v>133</v>
-      </c>
-      <c r="I130" t="s">
+      <c r="K130" t="s">
         <v>134</v>
       </c>
-      <c r="J130" t="s">
-        <v>19</v>
-      </c>
-      <c r="K130" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="131" spans="1:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="131" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="B131" t="s">
-        <v>12</v>
+        <v>103</v>
       </c>
       <c r="C131" t="s">
-        <v>103</v>
+        <v>32</v>
       </c>
       <c r="D131" t="s">
         <v>79</v>
       </c>
       <c r="E131" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="F131" t="s">
         <v>12</v>
       </c>
       <c r="G131" t="s">
+        <v>12</v>
+      </c>
+      <c r="H131" t="s">
+        <v>12</v>
+      </c>
+      <c r="I131" t="s">
+        <v>65</v>
+      </c>
+      <c r="J131" t="s">
         <v>80</v>
       </c>
-      <c r="H131" t="s">
-        <v>65</v>
-      </c>
-      <c r="I131" t="s">
+      <c r="K131" t="s">
         <v>111</v>
       </c>
-      <c r="J131" t="s">
-        <v>19</v>
-      </c>
-      <c r="K131" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="132" spans="1:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="132" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="B132" t="s">
-        <v>12</v>
+        <v>122</v>
       </c>
       <c r="C132" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D132" t="s">
         <v>79</v>
       </c>
       <c r="E132" t="s">
-        <v>123</v>
+        <v>12</v>
       </c>
       <c r="F132" t="s">
         <v>12</v>
       </c>
       <c r="G132" t="s">
+        <v>12</v>
+      </c>
+      <c r="H132" t="s">
+        <v>24</v>
+      </c>
+      <c r="I132" t="s">
+        <v>162</v>
+      </c>
+      <c r="J132" t="s">
         <v>161</v>
       </c>
-      <c r="H132" t="s">
-        <v>162</v>
-      </c>
-      <c r="I132" t="s">
+      <c r="K132" t="s">
         <v>163</v>
       </c>
-      <c r="J132" t="s">
-        <v>19</v>
-      </c>
-      <c r="K132" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="133" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="133" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="B133" t="s">
-        <v>12</v>
+        <v>44</v>
       </c>
       <c r="C133" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D133" t="s">
         <v>79</v>
       </c>
       <c r="E133" t="s">
-        <v>45</v>
+        <v>12</v>
       </c>
       <c r="F133" t="s">
         <v>12</v>
       </c>
       <c r="G133" t="s">
+        <v>12</v>
+      </c>
+      <c r="H133" t="s">
+        <v>38</v>
+      </c>
+      <c r="I133" t="s">
+        <v>193</v>
+      </c>
+      <c r="J133" t="s">
         <v>74</v>
       </c>
-      <c r="H133" t="s">
-        <v>193</v>
-      </c>
-      <c r="I133" t="s">
+      <c r="K133" t="s">
         <v>238</v>
       </c>
-      <c r="J133" t="s">
-        <v>43</v>
-      </c>
-      <c r="K133" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="134" spans="1:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="134" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="B134" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="C134" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D134" t="s">
         <v>79</v>
       </c>
       <c r="E134" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="F134" t="s">
         <v>12</v>
       </c>
       <c r="G134" t="s">
+        <v>12</v>
+      </c>
+      <c r="H134" t="s">
+        <v>12</v>
+      </c>
+      <c r="I134" t="s">
+        <v>81</v>
+      </c>
+      <c r="J134" t="s">
         <v>80</v>
       </c>
-      <c r="H134" t="s">
-        <v>81</v>
-      </c>
-      <c r="I134" t="s">
+      <c r="K134" t="s">
         <v>82</v>
-      </c>
-      <c r="J134" t="s">
-        <v>19</v>
-      </c>
-      <c r="K134" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="135" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>12</v>
+        <v>43</v>
       </c>
       <c r="B135" t="s">
-        <v>12</v>
+        <v>60</v>
       </c>
       <c r="C135" t="s">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="D135" t="s">
         <v>79</v>
       </c>
       <c r="E135" t="s">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="F135" t="s">
         <v>12</v>
       </c>
       <c r="G135" t="s">
+        <v>12</v>
+      </c>
+      <c r="H135" t="s">
+        <v>12</v>
+      </c>
+      <c r="I135" t="s">
+        <v>101</v>
+      </c>
+      <c r="J135" t="s">
         <v>252</v>
       </c>
-      <c r="H135" t="s">
-        <v>101</v>
-      </c>
-      <c r="I135" t="s">
+      <c r="K135" t="s">
         <v>253</v>
-      </c>
-      <c r="J135" t="s">
-        <v>43</v>
-      </c>
-      <c r="K135" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="136" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>63</v>
+        <v>43</v>
       </c>
       <c r="B136" t="s">
-        <v>12</v>
+        <v>60</v>
       </c>
       <c r="C136" t="s">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="D136" t="s">
         <v>79</v>
       </c>
       <c r="E136" t="s">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="F136" t="s">
         <v>12</v>
       </c>
       <c r="G136" t="s">
+        <v>12</v>
+      </c>
+      <c r="H136" t="s">
+        <v>63</v>
+      </c>
+      <c r="I136" t="s">
+        <v>61</v>
+      </c>
+      <c r="J136" t="s">
         <v>161</v>
       </c>
-      <c r="H136" t="s">
-        <v>61</v>
-      </c>
-      <c r="I136" t="s">
+      <c r="K136" t="s">
         <v>254</v>
-      </c>
-      <c r="J136" t="s">
-        <v>43</v>
-      </c>
-      <c r="K136" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="137" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="B137" t="s">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="C137" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D137" t="s">
         <v>79</v>
       </c>
       <c r="E137" t="s">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="F137" t="s">
         <v>12</v>
       </c>
       <c r="G137" t="s">
+        <v>12</v>
+      </c>
+      <c r="H137" t="s">
+        <v>52</v>
+      </c>
+      <c r="I137" t="s">
+        <v>41</v>
+      </c>
+      <c r="J137" t="s">
         <v>258</v>
       </c>
-      <c r="H137" t="s">
-        <v>41</v>
-      </c>
-      <c r="I137" t="s">
+      <c r="K137" t="s">
         <v>259</v>
-      </c>
-      <c r="J137" t="s">
-        <v>43</v>
-      </c>
-      <c r="K137" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="138" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="B138" t="s">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="C138" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D138" t="s">
         <v>79</v>
       </c>
       <c r="E138" t="s">
-        <v>49</v>
+        <v>12</v>
       </c>
       <c r="F138" t="s">
         <v>12</v>
       </c>
       <c r="G138" t="s">
+        <v>12</v>
+      </c>
+      <c r="H138" t="s">
+        <v>29</v>
+      </c>
+      <c r="I138" t="s">
+        <v>226</v>
+      </c>
+      <c r="J138" t="s">
         <v>159</v>
       </c>
-      <c r="H138" t="s">
-        <v>226</v>
-      </c>
-      <c r="I138" t="s">
+      <c r="K138" t="s">
         <v>263</v>
-      </c>
-      <c r="J138" t="s">
-        <v>43</v>
-      </c>
-      <c r="K138" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="139" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>12</v>
+        <v>43</v>
       </c>
       <c r="B139" t="s">
-        <v>12</v>
+        <v>56</v>
       </c>
       <c r="C139" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="D139" t="s">
         <v>79</v>
       </c>
       <c r="E139" t="s">
-        <v>49</v>
+        <v>12</v>
       </c>
       <c r="F139" t="s">
         <v>12</v>
       </c>
       <c r="G139" t="s">
+        <v>12</v>
+      </c>
+      <c r="H139" t="s">
+        <v>12</v>
+      </c>
+      <c r="I139" t="s">
+        <v>57</v>
+      </c>
+      <c r="J139" t="s">
         <v>80</v>
       </c>
-      <c r="H139" t="s">
-        <v>57</v>
-      </c>
-      <c r="I139" t="s">
+      <c r="K139" t="s">
         <v>272</v>
-      </c>
-      <c r="J139" t="s">
-        <v>43</v>
-      </c>
-      <c r="K139" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="140" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>59</v>
+        <v>43</v>
       </c>
       <c r="B140" t="s">
-        <v>12</v>
+        <v>60</v>
       </c>
       <c r="C140" t="s">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="D140" t="s">
         <v>79</v>
       </c>
       <c r="E140" t="s">
-        <v>45</v>
+        <v>12</v>
       </c>
       <c r="F140" t="s">
         <v>12</v>
       </c>
       <c r="G140" t="s">
+        <v>12</v>
+      </c>
+      <c r="H140" t="s">
+        <v>59</v>
+      </c>
+      <c r="I140" t="s">
+        <v>101</v>
+      </c>
+      <c r="J140" t="s">
         <v>161</v>
       </c>
-      <c r="H140" t="s">
-        <v>101</v>
-      </c>
-      <c r="I140" t="s">
+      <c r="K140" t="s">
         <v>280</v>
       </c>
-      <c r="J140" t="s">
-        <v>43</v>
-      </c>
-      <c r="K140" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="141" spans="1:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="141" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>121</v>
+        <v>19</v>
       </c>
       <c r="B141" t="s">
-        <v>29</v>
+        <v>145</v>
       </c>
       <c r="C141" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D141" t="s">
         <v>76</v>
       </c>
       <c r="E141" t="s">
-        <v>146</v>
+        <v>12</v>
       </c>
       <c r="F141" t="s">
+        <v>29</v>
+      </c>
+      <c r="G141" t="s">
         <v>59</v>
       </c>
-      <c r="G141" t="s">
+      <c r="H141" t="s">
+        <v>121</v>
+      </c>
+      <c r="I141" t="s">
+        <v>108</v>
+      </c>
+      <c r="J141" t="s">
         <v>77</v>
       </c>
-      <c r="H141" t="s">
-        <v>108</v>
-      </c>
-      <c r="I141" t="s">
+      <c r="K141" t="s">
         <v>240</v>
       </c>
-      <c r="J141" t="s">
-        <v>19</v>
-      </c>
-      <c r="K141" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="142" spans="1:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="142" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>63</v>
+        <v>19</v>
       </c>
       <c r="B142" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C142" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D142" t="s">
         <v>76</v>
       </c>
       <c r="E142" t="s">
+        <v>12</v>
+      </c>
+      <c r="F142" t="s">
+        <v>12</v>
+      </c>
+      <c r="G142" t="s">
+        <v>12</v>
+      </c>
+      <c r="H142" t="s">
+        <v>63</v>
+      </c>
+      <c r="I142" t="s">
+        <v>46</v>
+      </c>
+      <c r="J142" t="s">
+        <v>159</v>
+      </c>
+      <c r="K142" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="143" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A143" t="s">
+        <v>19</v>
+      </c>
+      <c r="B143" t="s">
+        <v>200</v>
+      </c>
+      <c r="C143" t="s">
         <v>15</v>
-      </c>
-      <c r="F142" t="s">
-        <v>12</v>
-      </c>
-      <c r="G142" t="s">
-        <v>159</v>
-      </c>
-      <c r="H142" t="s">
-        <v>46</v>
-      </c>
-      <c r="I142" t="s">
-        <v>186</v>
-      </c>
-      <c r="J142" t="s">
-        <v>19</v>
-      </c>
-      <c r="K142" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="143" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A143" t="s">
-        <v>52</v>
-      </c>
-      <c r="B143" t="s">
-        <v>12</v>
-      </c>
-      <c r="C143" t="s">
-        <v>200</v>
       </c>
       <c r="D143" t="s">
         <v>76</v>
       </c>
       <c r="E143" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F143" t="s">
         <v>12</v>
       </c>
       <c r="G143" t="s">
+        <v>12</v>
+      </c>
+      <c r="H143" t="s">
+        <v>52</v>
+      </c>
+      <c r="I143" t="s">
+        <v>140</v>
+      </c>
+      <c r="J143" t="s">
         <v>77</v>
       </c>
-      <c r="H143" t="s">
-        <v>140</v>
-      </c>
-      <c r="I143" t="s">
+      <c r="K143" t="s">
         <v>201</v>
       </c>
-      <c r="J143" t="s">
-        <v>19</v>
-      </c>
-      <c r="K143" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="144" spans="1:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="144" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>59</v>
+        <v>19</v>
       </c>
       <c r="B144" t="s">
-        <v>12</v>
+        <v>125</v>
       </c>
       <c r="C144" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="D144" t="s">
         <v>76</v>
       </c>
       <c r="E144" t="s">
-        <v>123</v>
+        <v>12</v>
       </c>
       <c r="F144" t="s">
         <v>12</v>
       </c>
       <c r="G144" t="s">
+        <v>12</v>
+      </c>
+      <c r="H144" t="s">
+        <v>59</v>
+      </c>
+      <c r="I144" t="s">
+        <v>61</v>
+      </c>
+      <c r="J144" t="s">
         <v>77</v>
       </c>
-      <c r="H144" t="s">
-        <v>61</v>
-      </c>
-      <c r="I144" t="s">
+      <c r="K144" t="s">
         <v>131</v>
       </c>
-      <c r="J144" t="s">
-        <v>19</v>
-      </c>
-      <c r="K144" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="145" spans="1:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="145" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="B145" t="s">
-        <v>12</v>
+        <v>103</v>
       </c>
       <c r="C145" t="s">
-        <v>103</v>
+        <v>32</v>
       </c>
       <c r="D145" t="s">
         <v>76</v>
       </c>
       <c r="E145" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="F145" t="s">
         <v>12</v>
       </c>
       <c r="G145" t="s">
+        <v>12</v>
+      </c>
+      <c r="H145" t="s">
+        <v>12</v>
+      </c>
+      <c r="I145" t="s">
+        <v>65</v>
+      </c>
+      <c r="J145" t="s">
         <v>77</v>
       </c>
-      <c r="H145" t="s">
-        <v>65</v>
-      </c>
-      <c r="I145" t="s">
+      <c r="K145" t="s">
         <v>110</v>
       </c>
-      <c r="J145" t="s">
-        <v>19</v>
-      </c>
-      <c r="K145" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="146" spans="1:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="146" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="B146" t="s">
-        <v>12</v>
+        <v>122</v>
       </c>
       <c r="C146" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D146" t="s">
         <v>76</v>
       </c>
       <c r="E146" t="s">
-        <v>123</v>
+        <v>12</v>
       </c>
       <c r="F146" t="s">
         <v>12</v>
       </c>
       <c r="G146" t="s">
+        <v>12</v>
+      </c>
+      <c r="H146" t="s">
+        <v>27</v>
+      </c>
+      <c r="I146" t="s">
+        <v>105</v>
+      </c>
+      <c r="J146" t="s">
         <v>159</v>
       </c>
-      <c r="H146" t="s">
-        <v>105</v>
-      </c>
-      <c r="I146" t="s">
+      <c r="K146" t="s">
         <v>160</v>
       </c>
-      <c r="J146" t="s">
-        <v>19</v>
-      </c>
-      <c r="K146" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="147" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="147" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>59</v>
+        <v>43</v>
       </c>
       <c r="B147" t="s">
-        <v>12</v>
+        <v>44</v>
       </c>
       <c r="C147" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D147" t="s">
         <v>76</v>
       </c>
       <c r="E147" t="s">
-        <v>45</v>
+        <v>12</v>
       </c>
       <c r="F147" t="s">
         <v>12</v>
       </c>
       <c r="G147" t="s">
+        <v>12</v>
+      </c>
+      <c r="H147" t="s">
+        <v>59</v>
+      </c>
+      <c r="I147" t="s">
+        <v>193</v>
+      </c>
+      <c r="J147" t="s">
         <v>233</v>
       </c>
-      <c r="H147" t="s">
-        <v>193</v>
-      </c>
-      <c r="I147" t="s">
+      <c r="K147" t="s">
         <v>234</v>
       </c>
-      <c r="J147" t="s">
-        <v>43</v>
-      </c>
-      <c r="K147" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="148" spans="1:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="148" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="B148" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="C148" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D148" t="s">
         <v>76</v>
       </c>
       <c r="E148" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="F148" t="s">
         <v>12</v>
       </c>
       <c r="G148" t="s">
+        <v>12</v>
+      </c>
+      <c r="H148" t="s">
+        <v>12</v>
+      </c>
+      <c r="I148" t="s">
+        <v>72</v>
+      </c>
+      <c r="J148" t="s">
         <v>77</v>
       </c>
-      <c r="H148" t="s">
-        <v>72</v>
-      </c>
-      <c r="I148" t="s">
+      <c r="K148" t="s">
         <v>78</v>
-      </c>
-      <c r="J148" t="s">
-        <v>19</v>
-      </c>
-      <c r="K148" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="149" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="B149" t="s">
-        <v>12</v>
+        <v>60</v>
       </c>
       <c r="C149" t="s">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="D149" t="s">
         <v>76</v>
       </c>
       <c r="E149" t="s">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="F149" t="s">
         <v>12</v>
       </c>
       <c r="G149" t="s">
+        <v>12</v>
+      </c>
+      <c r="H149" t="s">
+        <v>29</v>
+      </c>
+      <c r="I149" t="s">
+        <v>101</v>
+      </c>
+      <c r="J149" t="s">
         <v>157</v>
       </c>
-      <c r="H149" t="s">
-        <v>101</v>
-      </c>
-      <c r="I149" t="s">
+      <c r="K149" t="s">
         <v>249</v>
-      </c>
-      <c r="J149" t="s">
-        <v>43</v>
-      </c>
-      <c r="K149" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="150" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>12</v>
+        <v>43</v>
       </c>
       <c r="B150" t="s">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="C150" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D150" t="s">
         <v>76</v>
       </c>
       <c r="E150" t="s">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="F150" t="s">
         <v>12</v>
       </c>
       <c r="G150" t="s">
+        <v>12</v>
+      </c>
+      <c r="H150" t="s">
+        <v>12</v>
+      </c>
+      <c r="I150" t="s">
+        <v>133</v>
+      </c>
+      <c r="J150" t="s">
         <v>74</v>
       </c>
-      <c r="H150" t="s">
-        <v>133</v>
-      </c>
-      <c r="I150" t="s">
+      <c r="K150" t="s">
         <v>250</v>
-      </c>
-      <c r="J150" t="s">
-        <v>43</v>
-      </c>
-      <c r="K150" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="151" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>12</v>
+        <v>43</v>
       </c>
       <c r="B151" t="s">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="C151" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D151" t="s">
         <v>76</v>
       </c>
       <c r="E151" t="s">
-        <v>49</v>
+        <v>12</v>
       </c>
       <c r="F151" t="s">
         <v>12</v>
       </c>
       <c r="G151" t="s">
+        <v>12</v>
+      </c>
+      <c r="H151" t="s">
+        <v>12</v>
+      </c>
+      <c r="I151" t="s">
+        <v>226</v>
+      </c>
+      <c r="J151" t="s">
         <v>258</v>
       </c>
-      <c r="H151" t="s">
-        <v>226</v>
-      </c>
-      <c r="I151" t="s">
+      <c r="K151" t="s">
         <v>260</v>
-      </c>
-      <c r="J151" t="s">
-        <v>43</v>
-      </c>
-      <c r="K151" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="152" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="B152" t="s">
-        <v>12</v>
+        <v>60</v>
       </c>
       <c r="C152" t="s">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="D152" t="s">
         <v>76</v>
       </c>
       <c r="E152" t="s">
-        <v>45</v>
+        <v>12</v>
       </c>
       <c r="F152" t="s">
         <v>12</v>
       </c>
       <c r="G152" t="s">
+        <v>12</v>
+      </c>
+      <c r="H152" t="s">
+        <v>27</v>
+      </c>
+      <c r="I152" t="s">
+        <v>46</v>
+      </c>
+      <c r="J152" t="s">
         <v>159</v>
       </c>
-      <c r="H152" t="s">
-        <v>46</v>
-      </c>
-      <c r="I152" t="s">
+      <c r="K152" t="s">
         <v>262</v>
-      </c>
-      <c r="J152" t="s">
-        <v>43</v>
-      </c>
-      <c r="K152" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="153" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>12</v>
+        <v>43</v>
       </c>
       <c r="B153" t="s">
-        <v>12</v>
+        <v>56</v>
       </c>
       <c r="C153" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="D153" t="s">
         <v>76</v>
       </c>
       <c r="E153" t="s">
-        <v>49</v>
+        <v>12</v>
       </c>
       <c r="F153" t="s">
         <v>12</v>
       </c>
       <c r="G153" t="s">
+        <v>12</v>
+      </c>
+      <c r="H153" t="s">
+        <v>12</v>
+      </c>
+      <c r="I153" t="s">
+        <v>61</v>
+      </c>
+      <c r="J153" t="s">
         <v>77</v>
       </c>
-      <c r="H153" t="s">
-        <v>61</v>
-      </c>
-      <c r="I153" t="s">
+      <c r="K153" t="s">
         <v>270</v>
-      </c>
-      <c r="J153" t="s">
-        <v>43</v>
-      </c>
-      <c r="K153" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="154" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>63</v>
+        <v>43</v>
       </c>
       <c r="B154" t="s">
-        <v>12</v>
+        <v>60</v>
       </c>
       <c r="C154" t="s">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="D154" t="s">
         <v>76</v>
       </c>
       <c r="E154" t="s">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="F154" t="s">
         <v>12</v>
       </c>
       <c r="G154" t="s">
+        <v>12</v>
+      </c>
+      <c r="H154" t="s">
+        <v>63</v>
+      </c>
+      <c r="I154" t="s">
+        <v>46</v>
+      </c>
+      <c r="J154" t="s">
         <v>159</v>
       </c>
-      <c r="H154" t="s">
-        <v>46</v>
-      </c>
-      <c r="I154" t="s">
+      <c r="K154" t="s">
         <v>271</v>
       </c>
-      <c r="J154" t="s">
-        <v>43</v>
-      </c>
-      <c r="K154" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="155" spans="1:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="155" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>41</v>
+        <v>19</v>
       </c>
       <c r="B155" t="s">
-        <v>12</v>
+        <v>145</v>
       </c>
       <c r="C155" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D155" t="s">
         <v>14</v>
       </c>
       <c r="E155" t="s">
-        <v>146</v>
+        <v>12</v>
       </c>
       <c r="F155" t="s">
         <v>12</v>
       </c>
       <c r="G155" t="s">
+        <v>12</v>
+      </c>
+      <c r="H155" t="s">
+        <v>41</v>
+      </c>
+      <c r="I155" t="s">
+        <v>69</v>
+      </c>
+      <c r="J155" t="s">
         <v>68</v>
       </c>
-      <c r="H155" t="s">
-        <v>69</v>
-      </c>
-      <c r="I155" t="s">
+      <c r="K155" t="s">
         <v>149</v>
       </c>
-      <c r="J155" t="s">
-        <v>19</v>
-      </c>
-      <c r="K155" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="156" spans="1:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="156" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="B156" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C156" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D156" t="s">
         <v>14</v>
       </c>
       <c r="E156" t="s">
+        <v>12</v>
+      </c>
+      <c r="F156" t="s">
+        <v>12</v>
+      </c>
+      <c r="G156" t="s">
+        <v>12</v>
+      </c>
+      <c r="H156" t="s">
+        <v>11</v>
+      </c>
+      <c r="I156" t="s">
+        <v>17</v>
+      </c>
+      <c r="J156" t="s">
+        <v>16</v>
+      </c>
+      <c r="K156" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="157" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A157" t="s">
+        <v>19</v>
+      </c>
+      <c r="B157" t="s">
+        <v>13</v>
+      </c>
+      <c r="C157" t="s">
         <v>15</v>
-      </c>
-      <c r="F156" t="s">
-        <v>12</v>
-      </c>
-      <c r="G156" t="s">
-        <v>16</v>
-      </c>
-      <c r="H156" t="s">
-        <v>17</v>
-      </c>
-      <c r="I156" t="s">
-        <v>18</v>
-      </c>
-      <c r="J156" t="s">
-        <v>19</v>
-      </c>
-      <c r="K156" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="157" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A157" t="s">
-        <v>52</v>
-      </c>
-      <c r="B157" t="s">
-        <v>12</v>
-      </c>
-      <c r="C157" t="s">
-        <v>13</v>
       </c>
       <c r="D157" t="s">
         <v>14</v>
       </c>
       <c r="E157" t="s">
+        <v>12</v>
+      </c>
+      <c r="F157" t="s">
+        <v>12</v>
+      </c>
+      <c r="G157" t="s">
+        <v>12</v>
+      </c>
+      <c r="H157" t="s">
+        <v>52</v>
+      </c>
+      <c r="I157" t="s">
+        <v>41</v>
+      </c>
+      <c r="J157" t="s">
+        <v>157</v>
+      </c>
+      <c r="K157" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="158" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A158" t="s">
+        <v>19</v>
+      </c>
+      <c r="B158" t="s">
+        <v>21</v>
+      </c>
+      <c r="C158" t="s">
         <v>15</v>
-      </c>
-      <c r="F157" t="s">
-        <v>12</v>
-      </c>
-      <c r="G157" t="s">
-        <v>157</v>
-      </c>
-      <c r="H157" t="s">
-        <v>41</v>
-      </c>
-      <c r="I157" t="s">
-        <v>185</v>
-      </c>
-      <c r="J157" t="s">
-        <v>19</v>
-      </c>
-      <c r="K157" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="158" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A158" t="s">
-        <v>20</v>
-      </c>
-      <c r="B158" t="s">
-        <v>12</v>
-      </c>
-      <c r="C158" t="s">
-        <v>21</v>
       </c>
       <c r="D158" t="s">
         <v>14</v>
       </c>
       <c r="E158" t="s">
+        <v>12</v>
+      </c>
+      <c r="F158" t="s">
+        <v>12</v>
+      </c>
+      <c r="G158" t="s">
+        <v>12</v>
+      </c>
+      <c r="H158" t="s">
+        <v>20</v>
+      </c>
+      <c r="I158" t="s">
+        <v>27</v>
+      </c>
+      <c r="J158" t="s">
+        <v>26</v>
+      </c>
+      <c r="K158" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="159" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A159" t="s">
+        <v>19</v>
+      </c>
+      <c r="B159" t="s">
+        <v>21</v>
+      </c>
+      <c r="C159" t="s">
         <v>15</v>
-      </c>
-      <c r="F158" t="s">
-        <v>12</v>
-      </c>
-      <c r="G158" t="s">
-        <v>26</v>
-      </c>
-      <c r="H158" t="s">
-        <v>27</v>
-      </c>
-      <c r="I158" t="s">
-        <v>28</v>
-      </c>
-      <c r="J158" t="s">
-        <v>19</v>
-      </c>
-      <c r="K158" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="159" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A159" t="s">
-        <v>24</v>
-      </c>
-      <c r="B159" t="s">
-        <v>52</v>
-      </c>
-      <c r="C159" t="s">
-        <v>21</v>
       </c>
       <c r="D159" t="s">
         <v>14</v>
       </c>
       <c r="E159" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="F159" t="s">
-        <v>12</v>
+        <v>52</v>
       </c>
       <c r="G159" t="s">
+        <v>12</v>
+      </c>
+      <c r="H159" t="s">
+        <v>24</v>
+      </c>
+      <c r="I159" t="s">
+        <v>29</v>
+      </c>
+      <c r="J159" t="s">
         <v>74</v>
       </c>
-      <c r="H159" t="s">
-        <v>29</v>
-      </c>
-      <c r="I159" t="s">
+      <c r="K159" t="s">
         <v>199</v>
       </c>
-      <c r="J159" t="s">
-        <v>19</v>
-      </c>
-      <c r="K159" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="160" spans="1:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="160" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>54</v>
+        <v>19</v>
       </c>
       <c r="B160" t="s">
-        <v>12</v>
+        <v>125</v>
       </c>
       <c r="C160" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="D160" t="s">
         <v>14</v>
       </c>
       <c r="E160" t="s">
-        <v>123</v>
+        <v>12</v>
       </c>
       <c r="F160" t="s">
+        <v>12</v>
+      </c>
+      <c r="G160" t="s">
         <v>20</v>
       </c>
-      <c r="G160" t="s">
+      <c r="H160" t="s">
+        <v>54</v>
+      </c>
+      <c r="I160" t="s">
+        <v>121</v>
+      </c>
+      <c r="J160" t="s">
         <v>74</v>
       </c>
-      <c r="H160" t="s">
-        <v>121</v>
-      </c>
-      <c r="I160" t="s">
+      <c r="K160" t="s">
         <v>130</v>
       </c>
-      <c r="J160" t="s">
-        <v>19</v>
-      </c>
-      <c r="K160" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="161" spans="1:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="161" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>63</v>
+        <v>19</v>
       </c>
       <c r="B161" t="s">
-        <v>12</v>
+        <v>103</v>
       </c>
       <c r="C161" t="s">
-        <v>103</v>
+        <v>32</v>
       </c>
       <c r="D161" t="s">
         <v>14</v>
       </c>
       <c r="E161" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="F161" t="s">
         <v>12</v>
       </c>
       <c r="G161" t="s">
+        <v>12</v>
+      </c>
+      <c r="H161" t="s">
+        <v>63</v>
+      </c>
+      <c r="I161" t="s">
+        <v>108</v>
+      </c>
+      <c r="J161" t="s">
         <v>74</v>
       </c>
-      <c r="H161" t="s">
-        <v>108</v>
-      </c>
-      <c r="I161" t="s">
+      <c r="K161" t="s">
         <v>109</v>
-      </c>
-      <c r="J161" t="s">
-        <v>19</v>
-      </c>
-      <c r="K161" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="162" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>12</v>
+        <v>43</v>
       </c>
       <c r="B162" t="s">
-        <v>12</v>
+        <v>60</v>
       </c>
       <c r="C162" t="s">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="D162" t="s">
         <v>14</v>
       </c>
       <c r="E162" t="s">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="F162" t="s">
         <v>12</v>
       </c>
       <c r="G162" t="s">
+        <v>12</v>
+      </c>
+      <c r="H162" t="s">
+        <v>12</v>
+      </c>
+      <c r="I162" t="s">
+        <v>105</v>
+      </c>
+      <c r="J162" t="s">
         <v>71</v>
       </c>
-      <c r="H162" t="s">
-        <v>105</v>
-      </c>
-      <c r="I162" t="s">
+      <c r="K162" t="s">
         <v>181</v>
       </c>
-      <c r="J162" t="s">
-        <v>43</v>
-      </c>
-      <c r="K162" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="163" spans="1:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="163" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="B163" t="s">
-        <v>12</v>
+        <v>122</v>
       </c>
       <c r="C163" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D163" t="s">
         <v>14</v>
       </c>
       <c r="E163" t="s">
-        <v>123</v>
+        <v>12</v>
       </c>
       <c r="F163" t="s">
         <v>12</v>
       </c>
       <c r="G163" t="s">
+        <v>12</v>
+      </c>
+      <c r="H163" t="s">
+        <v>38</v>
+      </c>
+      <c r="I163" t="s">
+        <v>108</v>
+      </c>
+      <c r="J163" t="s">
         <v>157</v>
       </c>
-      <c r="H163" t="s">
-        <v>108</v>
-      </c>
-      <c r="I163" t="s">
+      <c r="K163" t="s">
         <v>158</v>
       </c>
-      <c r="J163" t="s">
-        <v>19</v>
-      </c>
-      <c r="K163" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="164" spans="1:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="164" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="B164" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="C164" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D164" t="s">
         <v>14</v>
       </c>
       <c r="E164" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="F164" t="s">
         <v>12</v>
       </c>
       <c r="G164" t="s">
+        <v>12</v>
+      </c>
+      <c r="H164" t="s">
+        <v>12</v>
+      </c>
+      <c r="I164" t="s">
+        <v>34</v>
+      </c>
+      <c r="J164" t="s">
         <v>74</v>
       </c>
-      <c r="H164" t="s">
-        <v>34</v>
-      </c>
-      <c r="I164" t="s">
+      <c r="K164" t="s">
         <v>75</v>
-      </c>
-      <c r="J164" t="s">
-        <v>19</v>
-      </c>
-      <c r="K164" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="165" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>12</v>
+        <v>43</v>
       </c>
       <c r="B165" t="s">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="C165" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D165" t="s">
         <v>14</v>
       </c>
       <c r="E165" t="s">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="F165" t="s">
         <v>12</v>
       </c>
       <c r="G165" t="s">
+        <v>12</v>
+      </c>
+      <c r="H165" t="s">
+        <v>12</v>
+      </c>
+      <c r="I165" t="s">
+        <v>46</v>
+      </c>
+      <c r="J165" t="s">
         <v>197</v>
       </c>
-      <c r="H165" t="s">
-        <v>46</v>
-      </c>
-      <c r="I165" t="s">
+      <c r="K165" t="s">
         <v>230</v>
       </c>
-      <c r="J165" t="s">
-        <v>43</v>
-      </c>
-      <c r="K165" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="166" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="166" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="B166" t="s">
-        <v>12</v>
+        <v>44</v>
       </c>
       <c r="C166" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D166" t="s">
         <v>14</v>
       </c>
       <c r="E166" t="s">
-        <v>45</v>
+        <v>12</v>
       </c>
       <c r="F166" t="s">
         <v>12</v>
       </c>
       <c r="G166" t="s">
+        <v>12</v>
+      </c>
+      <c r="H166" t="s">
+        <v>38</v>
+      </c>
+      <c r="I166" t="s">
+        <v>193</v>
+      </c>
+      <c r="J166" t="s">
         <v>197</v>
       </c>
-      <c r="H166" t="s">
-        <v>193</v>
-      </c>
-      <c r="I166" t="s">
+      <c r="K166" t="s">
         <v>232</v>
-      </c>
-      <c r="J166" t="s">
-        <v>43</v>
-      </c>
-      <c r="K166" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="167" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="B167" t="s">
-        <v>12</v>
+        <v>60</v>
       </c>
       <c r="C167" t="s">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="D167" t="s">
         <v>14</v>
       </c>
       <c r="E167" t="s">
-        <v>45</v>
+        <v>12</v>
       </c>
       <c r="F167" t="s">
         <v>12</v>
       </c>
       <c r="G167" t="s">
+        <v>12</v>
+      </c>
+      <c r="H167" t="s">
+        <v>38</v>
+      </c>
+      <c r="I167" t="s">
+        <v>193</v>
+      </c>
+      <c r="J167" t="s">
         <v>157</v>
       </c>
-      <c r="H167" t="s">
-        <v>193</v>
-      </c>
-      <c r="I167" t="s">
+      <c r="K167" t="s">
         <v>236</v>
-      </c>
-      <c r="J167" t="s">
-        <v>43</v>
-      </c>
-      <c r="K167" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="168" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>12</v>
+        <v>43</v>
       </c>
       <c r="B168" t="s">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="C168" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D168" t="s">
         <v>14</v>
       </c>
       <c r="E168" t="s">
-        <v>49</v>
+        <v>12</v>
       </c>
       <c r="F168" t="s">
         <v>12</v>
       </c>
       <c r="G168" t="s">
+        <v>12</v>
+      </c>
+      <c r="H168" t="s">
+        <v>12</v>
+      </c>
+      <c r="I168" t="s">
+        <v>226</v>
+      </c>
+      <c r="J168" t="s">
         <v>74</v>
       </c>
-      <c r="H168" t="s">
-        <v>226</v>
-      </c>
-      <c r="I168" t="s">
+      <c r="K168" t="s">
         <v>239</v>
-      </c>
-      <c r="J168" t="s">
-        <v>43</v>
-      </c>
-      <c r="K168" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="169" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>12</v>
+        <v>43</v>
       </c>
       <c r="B169" t="s">
-        <v>12</v>
+        <v>56</v>
       </c>
       <c r="C169" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="D169" t="s">
         <v>14</v>
       </c>
       <c r="E169" t="s">
-        <v>49</v>
+        <v>12</v>
       </c>
       <c r="F169" t="s">
         <v>12</v>
       </c>
       <c r="G169" t="s">
+        <v>12</v>
+      </c>
+      <c r="H169" t="s">
+        <v>12</v>
+      </c>
+      <c r="I169" t="s">
+        <v>61</v>
+      </c>
+      <c r="J169" t="s">
         <v>157</v>
       </c>
-      <c r="H169" t="s">
-        <v>61</v>
-      </c>
-      <c r="I169" t="s">
+      <c r="K169" t="s">
         <v>248</v>
-      </c>
-      <c r="J169" t="s">
-        <v>43</v>
-      </c>
-      <c r="K169" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="170" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>59</v>
+        <v>43</v>
       </c>
       <c r="B170" t="s">
-        <v>12</v>
+        <v>60</v>
       </c>
       <c r="C170" t="s">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="D170" t="s">
         <v>14</v>
       </c>
       <c r="E170" t="s">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="F170" t="s">
         <v>12</v>
       </c>
       <c r="G170" t="s">
+        <v>12</v>
+      </c>
+      <c r="H170" t="s">
+        <v>59</v>
+      </c>
+      <c r="I170" t="s">
+        <v>41</v>
+      </c>
+      <c r="J170" t="s">
         <v>233</v>
       </c>
-      <c r="H170" t="s">
-        <v>41</v>
-      </c>
-      <c r="I170" t="s">
+      <c r="K170" t="s">
         <v>251</v>
-      </c>
-      <c r="J170" t="s">
-        <v>43</v>
-      </c>
-      <c r="K170" t="s">
-        <v>12</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:K170" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <filterColumn colId="9">
+    <filterColumn colId="0">
       <filters>
-        <filter val="Nacala Porto"/>
+        <filter val="Monapo"/>
       </filters>
     </filterColumn>
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K164">
-      <sortCondition ref="D1:D170"/>
-    </sortState>
+    <filterColumn colId="1">
+      <filters>
+        <filter val="RAMIANE"/>
+      </filters>
+    </filterColumn>
   </autoFilter>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K170">
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:K170">
     <sortCondition ref="D1:D170"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7251,6 +7254,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="54c5ab46-7543-4aba-b0fa-79d6a199bef5" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="20d57abc-823c-4051-a81a-1a0a01a8f39e">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100DC8BB5B596CFDD4794B3344F0E8F53A4" ma:contentTypeVersion="15" ma:contentTypeDescription="Criar um novo documento." ma:contentTypeScope="" ma:versionID="9a7078cd21229583650f2264465a1c40">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="20d57abc-823c-4051-a81a-1a0a01a8f39e" xmlns:ns3="54c5ab46-7543-4aba-b0fa-79d6a199bef5" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4e45437c47114f519c494620e3e4bb67" ns2:_="" ns3:_="">
     <xsd:import namespace="20d57abc-823c-4051-a81a-1a0a01a8f39e"/>
@@ -7485,27 +7508,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="54c5ab46-7543-4aba-b0fa-79d6a199bef5" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="20d57abc-823c-4051-a81a-1a0a01a8f39e">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FB788E5D-2D79-4363-AF59-D9AE6FBE16C9}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{73DE38E5-A439-4DFE-870D-009DEC8E8546}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="54c5ab46-7543-4aba-b0fa-79d6a199bef5"/>
+    <ds:schemaRef ds:uri="20d57abc-823c-4051-a81a-1a0a01a8f39e"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{03C74B1E-6305-431E-B65A-AECD2878EEED}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -7522,23 +7544,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{73DE38E5-A439-4DFE-870D-009DEC8E8546}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="54c5ab46-7543-4aba-b0fa-79d6a199bef5"/>
-    <ds:schemaRef ds:uri="20d57abc-823c-4051-a81a-1a0a01a8f39e"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FB788E5D-2D79-4363-AF59-D9AE6FBE16C9}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>